--- a/tu_dien_500.xlsx
+++ b/tu_dien_500.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nguồn &amp; giấy phép" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Từ điển'!$A$1:$I$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Từ điển'!$A$1:$J$501</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I501"/>
+  <dimension ref="A1:J501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,8 @@
     <col width="70" customWidth="1" min="6" max="6"/>
     <col width="70" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,7 +489,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Theo Wikipedia tiếng Việt</t>
+          <t>Trích Wikipedia</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -497,6 +498,11 @@
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Ngôn ngữ bài</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Thuật ngữ liên quan</t>
         </is>
@@ -537,7 +543,12 @@
           <t>https://vi.wikipedia.org/wiki/B%E1%BA%ABy_thu_nh%E1%BA%ADp_trung_b%C3%ACnh</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>GDP bình quân đầu người, Năng suất lao động, Tổng thu nhập quốc gia, Tăng trưởng kinh tế</t>
         </is>
@@ -570,7 +581,8 @@
       </c>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Tỷ giá trung tâm, Tỷ giá hối đoái, Ngân hàng Nhà nước Việt Nam</t>
         </is>
@@ -611,7 +623,12 @@
           <t>https://vi.wikipedia.org/wiki/B%E1%BB%99_ba_b%E1%BA%A5t_kh%E1%BA%A3_thi</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Tỷ giá hối đoái, Chính sách tiền tệ, Cục Dự trữ Liên bang Mỹ, Đầu tư gián tiếp nước ngoài</t>
         </is>
@@ -656,7 +673,12 @@
           <t>https://vi.wikipedia.org/wiki/C%C3%A1n_c%C3%A2n_thanh_to%C3%A1n</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Cán cân vãng lai, Cán cân thương mại, Dự trữ ngoại hối, Đầu tư trực tiếp nước ngoài, Đầu tư gián tiếp nước ngoài</t>
         </is>
@@ -697,7 +719,12 @@
           <t>https://vi.wikipedia.org/wiki/C%C3%A1n_c%C3%A2n_th%C6%B0%C6%A1ng_m%E1%BA%A1i</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Xuất siêu, Nhập siêu, Cán cân vãng lai, Cán cân thanh toán quốc tế, Tỷ giá hối đoái</t>
         </is>
@@ -738,7 +765,12 @@
           <t>https://vi.wikipedia.org/wiki/T%C3%A0i_kho%E1%BA%A3n_v%C3%A3ng_lai</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Cán cân thanh toán quốc tế, Cán cân thương mại, Kiều hối, Tổng thu nhập quốc gia</t>
         </is>
@@ -779,7 +811,12 @@
           <t>https://vi.wikipedia.org/wiki/C%E1%BA%A1nh_tranh_ho%C3%A0n_h%E1%BA%A3o</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Độc quyền, Độc quyền nhóm, Quy luật cung cầu, Thặng dư sản xuất</t>
         </is>
@@ -810,9 +847,22 @@
           <t>Lượng hàng hóa, dịch vụ mà người mua sẵn sàng và có khả năng chi trả ở mỗi mức giá trong một khoảng thời gian, khi các yếu tố khác không đổi. Theo quy luật cầu, giá càng cao thì lượng cầu càng giảm; đường cầu dịch chuyển khi thu nhập, giá hàng hóa liên quan, thị hiếu hoặc kỳ vọng thay đổi.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>In economics, demand is the quantity of a good consumers are willing and able to purchase at various prices over a given period. In economics, "demand" for a commodity is not the same thing as "desire" for it. It refers to both the desire to purchase and the ability to pay for a commodity. Demand is always expressed in relation to a range of prices and a particular time period since demand is a flow concept. A flow is any variable expressed per unit of time. Demand refers not to a single isolated purchase, but to a continuous flow of purchases.</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Demand</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>Cung, Quy luật cung cầu, Độ co giãn của cầu theo giá, Thặng dư tiêu dùng</t>
         </is>
@@ -853,7 +903,12 @@
           <t>https://vi.wikipedia.org/wiki/Chi_ph%C3%AD_c%C6%A1_h%E1%BB%99i</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Lợi thế so sánh, Lãi suất thực, Lãi suất danh nghĩa</t>
         </is>
@@ -898,7 +953,12 @@
           <t>https://vi.wikipedia.org/wiki/Ch%E1%BB%89_s%E1%BB%91_gi%C3%A1_s%E1%BA%A3n_xu%E1%BA%A5t</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Chỉ số giá tiêu dùng, Lạm phát do chi phí đẩy, Lạm phát</t>
         </is>
@@ -943,7 +1003,12 @@
           <t>https://vi.wikipedia.org/wiki/Ch%E1%BB%89_s%E1%BB%91_gi%C3%A1_ti%C3%AAu_d%C3%B9ng</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>Lạm phát, Lạm phát cơ bản, Chỉ số giá sản xuất, Chỉ số giảm phát GDP</t>
         </is>
@@ -984,7 +1049,12 @@
           <t>https://vi.wikipedia.org/wiki/Ch%E1%BB%89_s%E1%BB%91_gi%E1%BA%A3m_ph%C3%A1t_GDP</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>GDP danh nghĩa, GDP thực tế, Chỉ số giá tiêu dùng, Lạm phát</t>
         </is>
@@ -1019,9 +1089,22 @@
           <t>Chỉ số tổng hợp từ khảo sát các nhà quản lý mua hàng về đơn đặt hàng mới, sản lượng, việc làm, thời gian giao hàng và tồn kho; mức trên 50 điểm cho thấy ngành sản xuất mở rộng, dưới 50 là thu hẹp. PMI ngành sản xuất Việt Nam do S&amp;P Global công bố vào đầu mỗi tháng và được thị trường theo dõi như một chỉ báo sớm.</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Purchasing managers' indexes (PMI) are economic indicators derived from monthly surveys of private sector companies. The three principal producers of PMIs are S&amp;P Global (from 2022 merger with IHS Markit), which produces PMIs for over 30 countries worldwide and developed the first service sector PMIs, and the Institute for Supply Management (ISM), which originated the manufacturing surveys produced for the United States.</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Purchasing_Managers%27_Index</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>Chỉ số sản xuất công nghiệp, Chu kỳ kinh tế, Tăng trưởng kinh tế</t>
         </is>
@@ -1058,7 +1141,8 @@
       </c>
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>Chỉ số nhà quản trị mua hàng, Tăng trưởng kinh tế, Tổng sản phẩm quốc nội</t>
         </is>
@@ -1099,7 +1183,12 @@
           <t>https://vi.wikipedia.org/wiki/Ch%C3%ADnh_s%C3%A1ch_t%C3%A0i_kh%C3%B3a</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>Chính sách tài khóa mở rộng, Chính sách tài khóa thắt chặt, Ngân sách nhà nước, Chính sách tiền tệ, Đầu tư công</t>
         </is>
@@ -1130,9 +1219,22 @@
           <t>Chính sách tăng chi tiêu công và/hoặc giảm thuế nhằm kích cầu, hỗ trợ tăng trưởng khi nền kinh tế suy giảm, đổi lại thâm hụt ngân sách và nợ công có thể tăng. Ví dụ Việt Nam giảm 2% thuế suất thuế giá trị gia tăng từ năm 2022 (nhiều lần gia hạn) và đẩy mạnh đầu tư công vào hạ tầng.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Chính sách tài khóa (fiscal policy) trong kinh tế học vĩ mô là chính sách được điều khiển bởi chính phủ thông qua thu ngân sách (bao gồm chế độ thuế, phí và lệ phí,...) và/hoặc chi ngân sách (trong đó có đầu tư công, những dịch vụ - hàng hóa cung cấp như trợ cấp xã hội, v.v.) để tác động (còn gọi là can thiệp) tới nền kinh tế với mục đích ổn định thị trường. Chính sách tài khóa cùng với chính sách tiền tệ là các chính sách kinh tế vĩ mô quan trọng, nhằm ổn định thị trường, xây dựng niềm tin bền vững và phát triển kinh tế theo hướng vĩ mô.</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Ch%C3%ADnh_s%C3%A1ch_t%C3%A0i_kh%C3%B3a</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Chính sách tài khóa, Gói kích thích kinh tế, Đầu tư công, Thâm hụt ngân sách, Hiệu ứng lấn át</t>
         </is>
@@ -1163,9 +1265,22 @@
           <t>Chính sách cắt giảm chi tiêu công và/hoặc tăng thuế để hạ nhiệt tổng cầu, kiềm chế lạm phát hoặc giảm thâm hụt ngân sách, nợ công. Ví dụ năm 2011 Chính phủ ban hành Nghị quyết 11/NQ-CP, cắt giảm đầu tư công và chi thường xuyên để chống lạm phát cao.</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Chính sách tài khóa (fiscal policy) trong kinh tế học vĩ mô là chính sách được điều khiển bởi chính phủ thông qua thu ngân sách (bao gồm chế độ thuế, phí và lệ phí,...) và/hoặc chi ngân sách (trong đó có đầu tư công, những dịch vụ - hàng hóa cung cấp như trợ cấp xã hội, v.v.) để tác động (còn gọi là can thiệp) tới nền kinh tế với mục đích ổn định thị trường. Chính sách tài khóa cùng với chính sách tiền tệ là các chính sách kinh tế vĩ mô quan trọng, nhằm ổn định thị trường, xây dựng niềm tin bền vững và phát triển kinh tế theo hướng vĩ mô.</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Ch%C3%ADnh_s%C3%A1ch_t%C3%A0i_kh%C3%B3a</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>Chính sách tài khóa, Chính sách tài khóa mở rộng, Thâm hụt ngân sách, Nợ công</t>
         </is>
@@ -1206,7 +1321,12 @@
           <t>https://vi.wikipedia.org/wiki/Ch%C3%ADnh_s%C3%A1ch_ti%E1%BB%81n_t%E1%BB%87</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>Chính sách tiền tệ nới lỏng, Chính sách tiền tệ thắt chặt, Lãi suất điều hành, Ngân hàng Nhà nước Việt Nam, Chính sách tài khóa</t>
         </is>
@@ -1237,9 +1357,22 @@
           <t>Định hướng chính sách mà ngân hàng trung ương hạ lãi suất, bơm thêm tiền và nới điều kiện tín dụng để kích thích vay vốn, đầu tư và tiêu dùng khi kinh tế suy yếu. Ví dụ năm 2023 NHNN đã giảm lãi suất điều hành bốn lần; chính sách này thường hỗ trợ thị trường chứng khoán nhưng có thể làm tăng áp lực lạm phát và tỷ giá.</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Chính sách lưu thông tiền tệ hay chính sách tiền tệ (monetary policy) là quá trình quản lý cung tiền (money supply) của cơ quan quản lý tiền tệ (có thể là ngân hàng trung ương), thường là hướng tới một lãi suất mong muốn (targeting interest rate) để đạt được những mục đích ổn định và tăng trưởng kinh tế - như kiềm chế lạm phát, duy trì ổn định tỷ giá hối đoái, đạt được toàn dụng lao động hay tăng trưởng kinh tế.</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Ch%C3%ADnh_s%C3%A1ch_ti%E1%BB%81n_t%E1%BB%87</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>Chính sách tiền tệ, Chính sách tiền tệ thắt chặt, Lãi suất điều hành, Nới lỏng định lượng, Cung tiền</t>
         </is>
@@ -1270,9 +1403,22 @@
           <t>Định hướng chính sách mà ngân hàng trung ương tăng lãi suất, hút bớt tiền và hạn chế tín dụng nhằm kiềm chế lạm phát hoặc ổn định tỷ giá. Ví dụ tháng 9 và tháng 10/2022, NHNN hai lần tăng các mức lãi suất điều hành, mỗi lần 1 điểm phần trăm, khi Fed tăng lãi suất mạnh và tỷ giá chịu áp lực.</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Chính sách lưu thông tiền tệ hay chính sách tiền tệ (monetary policy) là quá trình quản lý cung tiền (money supply) của cơ quan quản lý tiền tệ (có thể là ngân hàng trung ương), thường là hướng tới một lãi suất mong muốn (targeting interest rate) để đạt được những mục đích ổn định và tăng trưởng kinh tế - như kiềm chế lạm phát, duy trì ổn định tỷ giá hối đoái, đạt được toàn dụng lao động hay tăng trưởng kinh tế.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Ch%C3%ADnh_s%C3%A1ch_ti%E1%BB%81n_t%E1%BB%87</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>Chính sách tiền tệ, Chính sách tiền tệ nới lỏng, Lãi suất điều hành, Tín phiếu Ngân hàng Nhà nước, Lạm phát</t>
         </is>
@@ -1313,7 +1459,12 @@
           <t>https://vi.wikipedia.org/wiki/Chu_k%E1%BB%B3_kinh_t%E1%BA%BF</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>Suy thoái kinh tế, Tăng trưởng kinh tế, Khủng hoảng kinh tế, Tổng cầu</t>
         </is>
@@ -1358,7 +1509,12 @@
           <t>https://vi.wikipedia.org/wiki/C%E1%BB%A5c_D%E1%BB%B1_tr%E1%BB%AF_Li%C3%AAn_bang</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng trung ương, Lạm phát mục tiêu, Tỷ giá hối đoái, Nới lỏng định lượng, Bộ ba bất khả thi</t>
         </is>
@@ -1391,7 +1547,8 @@
       </c>
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>Cầu, Quy luật cung cầu, Giá cân bằng, Thặng dư sản xuất</t>
         </is>
@@ -1432,7 +1589,12 @@
           <t>https://vi.wikipedia.org/wiki/Cung_%E1%BB%A9ng_ti%E1%BB%81n_t%E1%BB%87</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>Tiền cơ sở, Khối tiền M1, Khối tiền M2, Số nhân tiền, Lạm phát</t>
         </is>
@@ -1473,7 +1635,12 @@
           <t>https://vi.wikipedia.org/wiki/Chi_ti%C3%AAu_ch%C3%ADnh_ph%E1%BB%A7</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>Giải ngân vốn đầu tư công, Chính sách tài khóa mở rộng, Ngân sách nhà nước, Vốn đầu tư toàn xã hội, Hiệu ứng lấn át</t>
         </is>
@@ -1518,7 +1685,12 @@
           <t>https://vi.wikipedia.org/wiki/%C4%90%E1%BA%A7u_t%C6%B0_gi%C3%A1n_ti%E1%BA%BFp_n%C6%B0%E1%BB%9Bc_ngo%C3%A0i</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>Đầu tư trực tiếp nước ngoài, Cán cân thanh toán quốc tế, Tỷ giá hối đoái, Bộ ba bất khả thi</t>
         </is>
@@ -1563,7 +1735,12 @@
           <t>https://vi.wikipedia.org/wiki/%C4%90%E1%BA%A7u_t%C6%B0_tr%E1%BB%B1c_ti%E1%BA%BFp_n%C6%B0%E1%BB%9Bc_ngo%C3%A0i</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>Đầu tư gián tiếp nước ngoài, Cán cân thanh toán quốc tế, Xuất siêu, Vốn đầu tư toàn xã hội</t>
         </is>
@@ -1604,7 +1781,12 @@
           <t>https://vi.wikipedia.org/wiki/%C4%90%C3%ACnh_l%E1%BA%A1m</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>Lạm phát do chi phí đẩy, Suy thoái kinh tế, Tỷ lệ thất nghiệp, Đường cong Phillips</t>
         </is>
@@ -1635,9 +1817,22 @@
           <t>Thước đo mức độ phản ứng của lượng cầu trước thay đổi của giá, bằng phần trăm thay đổi lượng cầu chia cho phần trăm thay đổi giá. Cầu co giãn mạnh (giá trị tuyệt đối lớn hơn 1) với hàng có nhiều sản phẩm thay thế, và kém co giãn với hàng thiết yếu như xăng, điện, thuốc; doanh nghiệp bán hàng kém co giãn dễ chuyển chi phí tăng sang giá bán hơn.</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>A good's price elasticity of demand ( E d {\displaystyle E_{d}} , PED) is a measure of how sensitive the quantity demanded is to its price. When the price rises, quantity demanded falls for almost any good (law of demand), but it falls more for some than for others. The price elasticity gives the percentage change in quantity demanded when there is a one percent increase in price, holding everything else constant. If the elasticity is −2, that means a one percent price rise leads to a two percent decline in quantity demanded.</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Price_elasticity_of_demand</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>Cầu, Quy luật cung cầu, Độc quyền</t>
         </is>
@@ -1678,7 +1873,12 @@
           <t>https://vi.wikipedia.org/wiki/%C4%90%E1%BB%99c_quy%E1%BB%81n_(kinh_t%E1%BA%BF)</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>Độc quyền nhóm, Cạnh tranh hoàn hảo, Thặng dư tiêu dùng, Độ co giãn của cầu theo giá</t>
         </is>
@@ -1709,9 +1909,22 @@
           <t>Cấu trúc thị trường do một số ít doanh nghiệp lớn chi phối, quyết định giá và sản lượng của mỗi hãng phụ thuộc lẫn nhau, nên dễ xảy ra cạnh tranh về giá hoặc cấu kết (cartel). Ví dụ ở Việt Nam là thị trường viễn thông di động với vài nhà mạng lớn hay ngành hàng không nội địa.</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>An oligopoly (from Ancient Greek ὀλίγος (olígos) 'few' and πωλέω (pōléō) 'to sell') is a market in which pricing control lies in the hands of a few sellers. As a result of their significant market power, firms in oligopolistic markets can influence prices through manipulating the supply function. Firms in an oligopoly are mutually interdependent, as any action by one firm is expected to affect other firms in the market and evoke a reaction or consequential action. As a result, firms in oligopolistic markets often resort to collusion as means of maximising profits.</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Oligopoly</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>Độc quyền, Cạnh tranh hoàn hảo, Giá cân bằng</t>
         </is>
@@ -1752,7 +1965,12 @@
           <t>https://vi.wikipedia.org/wiki/D%E1%BB%B1_tr%E1%BB%AF_b%E1%BA%AFt_bu%E1%BB%99c</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>Số nhân tiền, Tiền cơ sở, Chính sách tiền tệ, Cung tiền</t>
         </is>
@@ -1793,7 +2011,12 @@
           <t>https://vi.wikipedia.org/wiki/D%E1%BB%B1_tr%E1%BB%AF_ngo%E1%BA%A1i_h%E1%BB%91i_nh%C3%A0_n%C6%B0%E1%BB%9Bc</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>Tỷ giá hối đoái, Cán cân thanh toán quốc tế, Ngân hàng Nhà nước Việt Nam, Xuất siêu</t>
         </is>
@@ -1834,7 +2057,12 @@
           <t>https://vi.wikipedia.org/wiki/%C4%90%C6%B0%E1%BB%9Dng_cong_Phillips</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>Lạm phát, Tỷ lệ thất nghiệp, Thất nghiệp tự nhiên, Đình lạm</t>
         </is>
@@ -1875,7 +2103,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%95ng_s%E1%BA%A3n_ph%E1%BA%A9m_n%E1%BB%99i_%C4%91%E1%BB%8Ba</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>Tổng sản phẩm quốc nội, Bẫy thu nhập trung bình, Năng suất lao động, Tổng thu nhập quốc gia</t>
         </is>
@@ -1916,7 +2149,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%95ng_s%E1%BA%A3n_ph%E1%BA%A9m_n%E1%BB%99i_%C4%91%E1%BB%8Ba</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>GDP thực tế, Chỉ số giảm phát GDP, Tổng sản phẩm quốc nội, Lạm phát</t>
         </is>
@@ -1957,7 +2195,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%95ng_s%E1%BA%A3n_ph%E1%BA%A9m_n%E1%BB%99i_%C4%91%E1%BB%8Ba</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>GDP danh nghĩa, Chỉ số giảm phát GDP, Tăng trưởng kinh tế, Tổng sản phẩm quốc nội</t>
         </is>
@@ -1988,9 +2231,22 @@
           <t>Mức giá tại đó lượng cung bằng lượng cầu, ứng với giao điểm của đường cung và đường cầu (điểm cân bằng thị trường). Nếu Nhà nước áp giá trần thấp hơn giá cân bằng sẽ gây thiếu hụt hàng, còn giá sàn cao hơn giá cân bằng sẽ gây dư thừa.</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Trong kinh tế, cân bằng kinh tế là tình huống trong đó các lực lượng kinh tế như cung và cầu được cân bằng và khi không có ảnh hưởng bên ngoài, các giá trị (cân bằng) của các biến kinh tế sẽ không thay đổi. Ví dụ, trong văn bản tiêu chuẩn cạnh tranh hoàn hảo, trạng thái cân bằng xảy ra tại điểm mà tại đó lượng cầu và lượng cung là bằng nhau. Trạng thái cân bằng thị trường (Vùng cân bằng) trong trường hợp này là điều kiện giá thị trường được thiết lập thông qua cạnh tranh sao cho lượng hàng hóa hoặc dịch vụ mà người mua tìm kiếm bằng với lượng hàng hóa hoặc dịch vụ do người bán sản xuất.</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/%C4%90i%E1%BB%83m_c%C3%A2n_b%E1%BA%B1ng_th%E1%BB%8B_tr%C6%B0%E1%BB%9Dng</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>Quy luật cung cầu, Cung, Cầu, Thặng dư tiêu dùng</t>
         </is>
@@ -2023,7 +2279,8 @@
       </c>
       <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>Đầu tư công, Chính sách tài khóa mở rộng, Tăng trưởng kinh tế</t>
         </is>
@@ -2064,7 +2321,12 @@
           <t>https://vi.wikipedia.org/wiki/Gi%E1%BA%A3m_ph%C3%A1t</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>Lạm phát, Thiểu phát, Chỉ số giá tiêu dùng, Suy thoái kinh tế</t>
         </is>
@@ -2095,9 +2357,22 @@
           <t>Tập hợp các biện pháp tài khóa và tiền tệ quy mô lớn, triển khai trong thời gian ngắn nhằm vực dậy nền kinh tế đang suy giảm, như giảm thuế, hỗ trợ lãi suất, tăng chi đầu tư. Ví dụ năm 2009 Việt Nam hỗ trợ lãi suất 4% cho vay vốn và năm 2022 triển khai Chương trình phục hồi và phát triển kinh tế – xã hội (Nghị quyết 43/2022/QH15) quy mô khoảng 350 nghìn tỷ đồng.</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>A stimulus package is most often a government program providing economic stimulus. Examples in the United States include the Economic Stimulus Appropriations Act of 1977; the Economic Stimulus Act of 2008; the American Recovery and Reinvestment Act of 2009; the CARES Act in 2020 and American Rescue Plan Act of 2021.</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Stimulus_package</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>Chính sách tài khóa mở rộng, Chính sách tiền tệ nới lỏng, Suy thoái kinh tế, Đầu tư công</t>
         </is>
@@ -2130,7 +2405,8 @@
       </c>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>Chính sách tiền tệ, Ngân hàng Nhà nước Việt Nam, Cung tiền, Chính sách tiền tệ thắt chặt</t>
         </is>
@@ -2175,7 +2451,12 @@
           <t>https://vi.wikipedia.org/wiki/ICOR</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>Vốn đầu tư toàn xã hội, Tăng trưởng kinh tế, Đầu tư công, Năng suất lao động</t>
         </is>
@@ -2220,7 +2501,12 @@
           <t>https://vi.wikipedia.org/wiki/Hi%E1%BB%87p_%C4%91%E1%BB%8Bnh_th%C6%B0%C6%A1ng_m%E1%BA%A1i_t%E1%BB%B1_do</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>Thuế quan, Cán cân thương mại, Đầu tư trực tiếp nước ngoài, Lợi thế so sánh</t>
         </is>
@@ -2251,9 +2537,22 @@
           <t>Hiện tượng chi tiêu chính phủ tăng (thường tài trợ bằng vay nợ) làm tăng nhu cầu vốn và đẩy lãi suất lên, khiến đầu tư của khu vực tư nhân bị thu hẹp. Hiệu ứng này làm giảm tác dụng kích thích của chính sách tài khóa mở rộng, đặc biệt khi nền kinh tế đã gần mức toàn dụng.</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Theo nhận định của một số chuyên gia kinh tế học, hiệu ứng lấn át trong kinh tế là hiện tượng xảy ra khi sự tham gia của chính phủ trong một lĩnh vực nào đó của nền kinh tế thị trường có ảnh hưởng đáng kể đến cung hoặc cầu của những yếu tố khác của thị trường. Trong khi đó, một số chuyên gia kinh tế học khác lại định nghĩa “hiệu ứng lấn át” là trường hợp xảy ra khi chính phủ nới lỏng chính sách tài khoá làm giảm đầu tư khu vực tư nhân. Các khoản vay nợ tăng “lấn át” đầu tư tư nhân.</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Hi%E1%BB%87u_%E1%BB%A9ng_l%E1%BA%A5n_%C3%A1t_(kinh_t%E1%BA%BF_h%E1%BB%8Dc)</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>Chính sách tài khóa mở rộng, Thâm hụt ngân sách, Đầu tư công, Lãi suất danh nghĩa</t>
         </is>
@@ -2298,7 +2597,12 @@
           <t>https://vi.wikipedia.org/wiki/H%E1%BB%97_tr%E1%BB%A3_ph%C3%A1t_tri%E1%BB%83n_ch%C3%ADnh_th%E1%BB%A9c</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>Nợ công, Đầu tư công, Cán cân thanh toán quốc tế</t>
         </is>
@@ -2335,7 +2639,8 @@
       </c>
       <c r="G48" s="3" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>Khối tiền M2, Cung tiền, Tiền cơ sở</t>
         </is>
@@ -2372,7 +2677,8 @@
       </c>
       <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>Khối tiền M1, Cung tiền, Số nhân tiền, Chính sách tiền tệ</t>
         </is>
@@ -2413,7 +2719,12 @@
           <t>https://vi.wikipedia.org/wiki/Kh%E1%BB%A7ng_ho%E1%BA%A3ng_kinh_t%E1%BA%BF</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>Suy thoái kinh tế, Chu kỳ kinh tế, Gói kích thích kinh tế, Nới lỏng định lượng</t>
         </is>
@@ -2454,7 +2765,12 @@
           <t>https://vi.wikipedia.org/wiki/Ki%E1%BB%81u_h%E1%BB%91i</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>Cán cân vãng lai, Dự trữ ngoại hối, Tỷ giá hối đoái</t>
         </is>
@@ -2495,7 +2811,12 @@
           <t>https://vi.wikipedia.org/wiki/L%C3%A3i_su%E1%BA%A5t_danh_ngh%C4%A9a</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>Lãi suất thực, Lạm phát, Lãi suất điều hành</t>
         </is>
@@ -2528,7 +2849,8 @@
       </c>
       <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>Lãi suất tái cấp vốn, Lãi suất tái chiết khấu, Chính sách tiền tệ, Ngân hàng Nhà nước Việt Nam, Nghiệp vụ thị trường mở</t>
         </is>
@@ -2561,7 +2883,8 @@
       </c>
       <c r="G54" s="3" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>Lãi suất điều hành, Lãi suất tái chiết khấu, Ngân hàng Nhà nước Việt Nam, Chính sách tiền tệ</t>
         </is>
@@ -2592,9 +2915,22 @@
           <t>Lãi suất NHNN áp dụng khi mua lại (tái chiết khấu) các giấy tờ có giá ngắn hạn như tín phiếu, thương phiếu mà tổ chức tín dụng đã chiết khấu trước đó, qua đó cung cấp thanh khoản cho hệ thống. Mức lãi suất này thường thấp hơn lãi suất tái cấp vốn; hiện ở mức 3,0%/năm từ ngày 19/6/2023.</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Lãi suất chiết khấu là lãi suất mà ngân hàng trung ương (ngân hàng Nhà nước) đánh vào các khoản tiền cho các ngân hàng thương mại vay để đáp ứng nhu cầu tiền mặt ngắn hạn hoặc bất thường của các ngân hàng này. Quy định lãi suất chiết khấu là một trong những công cụ của chính sách tiền tệ nhằm điều tiết lượng cung tiền.</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/L%C3%A3i_su%E1%BA%A5t_chi%E1%BA%BFt_kh%E1%BA%A5u</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>Lãi suất tái cấp vốn, Lãi suất điều hành, Ngân hàng Nhà nước Việt Nam</t>
         </is>
@@ -2625,9 +2961,22 @@
           <t>Lãi suất sau khi đã loại trừ ảnh hưởng của lạm phát, xấp xỉ bằng lãi suất danh nghĩa trừ tỷ lệ lạm phát (phương trình Fisher). Ví dụ gửi tiết kiệm lãi 5%/năm trong khi lạm phát 3,3% thì lãi suất thực chỉ khoảng 1,7%; khi lãi suất thực âm, người dân có xu hướng chuyển tiền sang vàng, bất động sản hay chứng khoán.</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Lãi suất thực tế được tính xấp xỉ bằng lãi suất danh nghĩa trừ đi tỷ lệ lạm phát. Đây là lãi suất mà nhà đầu tư hy vọng nhận được sau khi trừ đi lạm phát. Đây không phải là số đơn thuần, vì các nhà đầu tư khác nhau có kỳ vọng về tỷ lệ lạm phát khác nhau. Nếu một nhà đầu tư nhận được 5% lãi trong năm tới và dự đoán rằng lạm phát là 2% thì ông ta hy vọng nhận được lãi thực là 3%.</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/L%C3%A3i_su%E1%BA%A5t_th%E1%BB%B1c_t%E1%BA%BF</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>Lãi suất danh nghĩa, Lạm phát, Chính sách tiền tệ, Lãi suất điều hành</t>
         </is>
@@ -2668,7 +3017,12 @@
           <t>https://vi.wikipedia.org/wiki/L%E1%BA%A1m_ph%C3%A1t</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>Chỉ số giá tiêu dùng, Giảm phát, Lạm phát cơ bản, Lạm phát mục tiêu, Lãi suất thực</t>
         </is>
@@ -2709,7 +3063,12 @@
           <t>https://vi.wikipedia.org/wiki/L%E1%BA%A1m_ph%C3%A1t_c%C6%A1_b%E1%BA%A3n</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>Lạm phát, Chỉ số giá tiêu dùng, Chính sách tiền tệ, Lạm phát mục tiêu</t>
         </is>
@@ -2740,9 +3099,22 @@
           <t>Lạm phát phát sinh khi tổng cầu tăng nhanh hơn khả năng sản xuất của nền kinh tế, tức “quá nhiều tiền đuổi theo quá ít hàng”. Nguyên nhân thường là tín dụng, cung tiền hoặc chi tiêu chính phủ mở rộng quá mức; ví dụ tín dụng và cung tiền tăng rất mạnh năm 2007 là một nguyên nhân dẫn đến lạm phát cao ở Việt Nam năm 2008.</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Demand-pull inflation occurs when aggregate demand in an economy is more than aggregate supply. It involves inflation rising as real gross domestic product rises and unemployment falls, as the economy moves along the Phillips curve. This is commonly described as "too much money chasing too few goods". More accurately, it should be described as involving "too much money spent chasing too few goods", since only money that is spent on goods and services can cause inflation. This would not be expected to happen, unless the economy is already at a full employment level.</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Demand-pull_inflation</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>Tổng cầu, Lạm phát, Lạm phát do chi phí đẩy, Cung tiền</t>
         </is>
@@ -2773,9 +3145,22 @@
           <t>Lạm phát xảy ra khi chi phí sản xuất như nguyên liệu, năng lượng, tiền lương hoặc giá hàng nhập khẩu tăng, buộc doanh nghiệp nâng giá bán dù nhu cầu không tăng. Ví dụ năm 2022 giá xăng dầu và nguyên liệu thế giới tăng mạnh đã đẩy giá nhiều mặt hàng trong nước đi lên.</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Cost-push inflation is a purported type of inflation caused by increases in the cost of important goods or services where no suitable alternative is available.</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Cost-push_inflation</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>Lạm phát do cầu kéo, Tổng cung, Chỉ số giá sản xuất, Đình lạm</t>
         </is>
@@ -2806,9 +3191,22 @@
           <t>Mức lạm phát mà cơ quan điều hành đặt ra và cam kết hướng tới, đồng thời cũng là tên khuôn khổ chính sách tiền tệ lấy ổn định giá làm mục tiêu hàng đầu (như Fed và nhiều ngân hàng trung ương nhắm mức 2%). Ở Việt Nam, Quốc hội giao chỉ tiêu CPI bình quân hằng năm, ví dụ khoảng 4,5% cho năm 2026.</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>In macroeconomics, inflation targeting is a monetary policy where a central bank follows an explicit target for the inflation rate for the medium-term and announces this inflation target to the public. The assumption is that the best that monetary policy can do to support long-term growth of the economy is to maintain price stability, and price stability is achieved by controlling inflation. The central bank uses short-term interest rates as its main monetary instrument.</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Inflation_targeting</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>Lạm phát, Chính sách tiền tệ, Lạm phát cơ bản, Cục Dự trữ Liên bang Mỹ</t>
         </is>
@@ -2849,7 +3247,12 @@
           <t>https://vi.wikipedia.org/wiki/L%E1%BB%A3i_th%E1%BA%BF_so_s%C3%A1nh</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>Chi phí cơ hội, Hiệp định thương mại tự do, Cán cân thương mại, Thuế quan</t>
         </is>
@@ -2890,7 +3293,12 @@
           <t>https://vi.wikipedia.org/wiki/L%E1%BB%B1c_l%C6%B0%E1%BB%A3ng_lao_%C4%91%E1%BB%99ng</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ thất nghiệp, Năng suất lao động, Thất nghiệp tự nhiên</t>
         </is>
@@ -2923,7 +3331,8 @@
       </c>
       <c r="G64" s="3" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>Lực lượng lao động, Lạm phát do chi phí đẩy, Năng suất lao động</t>
         </is>
@@ -2964,7 +3373,12 @@
           <t>https://vi.wikipedia.org/wiki/N%C4%83ng_su%E1%BA%A5t_lao_%C4%91%E1%BB%99ng</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>Tăng trưởng kinh tế, Lực lượng lao động, Bẫy thu nhập trung bình, GDP bình quân đầu người</t>
         </is>
@@ -3009,7 +3423,12 @@
           <t>https://vi.wikipedia.org/wiki/Ng%C3%A2n_h%C3%A0ng_Nh%C3%A0_n%C6%B0%E1%BB%9Bc_Vi%E1%BB%87t_Nam</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng trung ương, Chính sách tiền tệ, Lãi suất điều hành, Tỷ giá trung tâm, Nghiệp vụ thị trường mở</t>
         </is>
@@ -3050,7 +3469,12 @@
           <t>https://vi.wikipedia.org/wiki/Ng%C3%A2n_h%C3%A0ng_trung_%C6%B0%C6%A1ng</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng Nhà nước Việt Nam, Cục Dự trữ Liên bang Mỹ, Chính sách tiền tệ, Dự trữ ngoại hối</t>
         </is>
@@ -3095,7 +3519,12 @@
           <t>https://vi.wikipedia.org/wiki/Ng%C3%A2n_s%C3%A1ch_nh%C3%A0_n%C6%B0%E1%BB%9Bc</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>Thu ngân sách nhà nước, Thâm hụt ngân sách, Chính sách tài khóa, Đầu tư công</t>
         </is>
@@ -3140,7 +3569,12 @@
           <t>https://vi.wikipedia.org/wiki/Nghi%E1%BB%87p_v%E1%BB%A5_th%E1%BB%8B_tr%C6%B0%E1%BB%9Dng_m%E1%BB%9F</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>Tín phiếu Ngân hàng Nhà nước, Chính sách tiền tệ, Cung tiền, Lãi suất điều hành</t>
         </is>
@@ -3181,7 +3615,12 @@
           <t>https://vi.wikipedia.org/wiki/%E1%BA%A2nh_h%C6%B0%E1%BB%9Fng_ngo%E1%BA%A1i_lai</t>
         </is>
       </c>
-      <c r="I70" s="3" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>Chính sách tài khóa, Cạnh tranh hoàn hảo, Chi phí cơ hội</t>
         </is>
@@ -3222,7 +3661,12 @@
           <t>https://vi.wikipedia.org/wiki/Nh%E1%BA%ADp_si%C3%AAu</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
         <is>
           <t>Cán cân thương mại, Xuất siêu, Tỷ giá hối đoái, Cán cân vãng lai</t>
         </is>
@@ -3263,7 +3707,12 @@
           <t>https://vi.wikipedia.org/wiki/N%E1%BB%A3_ch%C3%ADnh_ph%E1%BB%A7</t>
         </is>
       </c>
-      <c r="I72" s="3" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>Thâm hụt ngân sách, Xếp hạng tín nhiệm quốc gia, Ngân sách nhà nước, Chính sách tài khóa</t>
         </is>
@@ -3308,7 +3757,12 @@
           <t>https://vi.wikipedia.org/wiki/N%E1%BB%9Bi_l%E1%BB%8Fng_%C4%91%E1%BB%8Bnh_l%C6%B0%E1%BB%A3ng</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>Chính sách tiền tệ nới lỏng, Cục Dự trữ Liên bang Mỹ, Cung tiền, Ngân hàng trung ương</t>
         </is>
@@ -3349,7 +3803,12 @@
           <t>https://vi.wikipedia.org/wiki/Ph%C3%A1_gi%C3%A1_ti%E1%BB%81n_t%E1%BB%87</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>Tỷ giá hối đoái, Cán cân thương mại, Xuất siêu, Tỷ giá hối đoái thực</t>
         </is>
@@ -3390,7 +3849,12 @@
           <t>https://vi.wikipedia.org/wiki/Nguy%C3%AAn_l%C3%BD_cung_-_c%E1%BA%A7u</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>Cung, Cầu, Giá cân bằng, Cạnh tranh hoàn hảo</t>
         </is>
@@ -3431,7 +3895,12 @@
           <t>https://vi.wikipedia.org/wiki/Si%C3%AAu_l%E1%BA%A1m_ph%C3%A1t</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
         <is>
           <t>Lạm phát, Cung tiền, Thâm hụt ngân sách, Phá giá tiền tệ</t>
         </is>
@@ -3462,9 +3931,22 @@
           <t>Hệ số cho biết mỗi đồng tiền cơ sở tạo ra bao nhiêu đồng cung tiền, tính bằng cung tiền chia cho tiền cơ sở. Số nhân tiền phụ thuộc vào tỷ lệ dự trữ bắt buộc, dự trữ dư thừa của ngân hàng và thói quen giữ tiền mặt của dân cư; trong mô hình đơn giản, nó bằng 1 chia cho tỷ lệ dự trữ bắt buộc.</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="3" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Số nhân tiền tệ, còn gọi là số nhân tín dụng, đo lường mức độ mà ngân hàng thương mại làm tăng cung tiền. Số nhân này bằng tỷ số giữa tổng lượng cung tiền và lượng cung tiền cơ sở.</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/S%E1%BB%91_nh%C3%A2n_ti%E1%BB%81n_t%E1%BB%87</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
         <is>
           <t>Tiền cơ sở, Cung tiền, Dự trữ bắt buộc, Khối tiền M2</t>
         </is>
@@ -3505,7 +3987,12 @@
           <t>https://vi.wikipedia.org/wiki/Suy_tho%C3%A1i_kinh_t%E1%BA%BF</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>Chu kỳ kinh tế, Khủng hoảng kinh tế, Tỷ lệ thất nghiệp, Đình lạm, Gói kích thích kinh tế</t>
         </is>
@@ -3546,7 +4033,12 @@
           <t>https://vi.wikipedia.org/wiki/T%C4%83ng_tr%C6%B0%E1%BB%9Fng_kinh_t%E1%BA%BF</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>GDP thực tế, Chu kỳ kinh tế, Năng suất lao động, Hệ số sử dụng vốn tăng thêm, Tổng sản phẩm quốc nội</t>
         </is>
@@ -3587,7 +4079,12 @@
           <t>https://vi.wikipedia.org/wiki/Th%C3%A2m_h%E1%BB%A5t_ng%C3%A2n_s%C3%A1ch</t>
         </is>
       </c>
-      <c r="I80" s="3" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
         <is>
           <t>Ngân sách nhà nước, Nợ công, Chính sách tài khóa mở rộng, Hiệu ứng lấn át</t>
         </is>
@@ -3628,7 +4125,12 @@
           <t>https://vi.wikipedia.org/wiki/Th%E1%BA%B7ng_d%C6%B0_kinh_t%E1%BA%BF</t>
         </is>
       </c>
-      <c r="I81" s="3" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
         <is>
           <t>Thặng dư tiêu dùng, Cung, Giá cân bằng, Cạnh tranh hoàn hảo</t>
         </is>
@@ -3669,7 +4171,12 @@
           <t>https://vi.wikipedia.org/wiki/Th%E1%BA%B7ng_d%C6%B0_kinh_t%E1%BA%BF</t>
         </is>
       </c>
-      <c r="I82" s="3" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
         <is>
           <t>Thặng dư sản xuất, Cầu, Giá cân bằng, Độc quyền</t>
         </is>
@@ -3710,7 +4217,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_l%E1%BB%87_th%E1%BA%A5t_nghi%E1%BB%87p_t%E1%BB%B1_nhi%C3%AAn</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ thất nghiệp, Đường cong Phillips, Lực lượng lao động, Chu kỳ kinh tế</t>
         </is>
@@ -3751,7 +4263,12 @@
           <t>https://vi.wikipedia.org/wiki/Thi%E1%BB%83u_ph%C3%A1t</t>
         </is>
       </c>
-      <c r="I84" s="3" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
         <is>
           <t>Lạm phát, Giảm phát, Lạm phát mục tiêu, Chính sách tiền tệ thắt chặt</t>
         </is>
@@ -3784,7 +4301,8 @@
       </c>
       <c r="G85" s="3" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="3" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr">
         <is>
           <t>Ngân sách nhà nước, Thâm hụt ngân sách, Chính sách tài khóa, Thuế quan</t>
         </is>
@@ -3825,7 +4343,12 @@
           <t>https://vi.wikipedia.org/wiki/Thu%E1%BA%BF_quan</t>
         </is>
       </c>
-      <c r="I86" s="3" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
         <is>
           <t>Hiệp định thương mại tự do, Cán cân thương mại, Thu ngân sách nhà nước, Lợi thế so sánh</t>
         </is>
@@ -3866,7 +4389,12 @@
           <t>https://vi.wikipedia.org/wiki/Ti%E1%BB%81n_c%C6%A1_s%E1%BB%9F</t>
         </is>
       </c>
-      <c r="I87" s="3" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>Cung tiền, Số nhân tiền, Dự trữ bắt buộc, Ngân hàng trung ương</t>
         </is>
@@ -3899,7 +4427,8 @@
       </c>
       <c r="G88" s="3" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr">
         <is>
           <t>Nghiệp vụ thị trường mở, Chính sách tiền tệ thắt chặt, Tỷ giá hối đoái, Ngân hàng Nhà nước Việt Nam</t>
         </is>
@@ -3944,7 +4473,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%95ng_c%E1%BA%A7u</t>
         </is>
       </c>
-      <c r="I89" s="3" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>Tổng cung, Chính sách tài khóa, Chính sách tiền tệ, Lạm phát do cầu kéo</t>
         </is>
@@ -3989,7 +4523,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%95ng_cung</t>
         </is>
       </c>
-      <c r="I90" s="3" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>Tổng cầu, Lạm phát do chi phí đẩy, Năng suất lao động, Đình lạm</t>
         </is>
@@ -4022,7 +4561,8 @@
       </c>
       <c r="G91" s="3" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="3" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>Tổng cầu, Tăng trưởng kinh tế, Chỉ số giá tiêu dùng</t>
         </is>
@@ -4067,7 +4607,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%95ng_s%E1%BA%A3n_l%C6%B0%E1%BB%A3ng_qu%E1%BB%91c_gia</t>
         </is>
       </c>
-      <c r="I92" s="3" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
         <is>
           <t>Tổng sản phẩm quốc nội, Tổng thu nhập quốc gia, Đầu tư trực tiếp nước ngoài</t>
         </is>
@@ -4112,7 +4657,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%95ng_s%E1%BA%A3n_ph%E1%BA%A9m_n%E1%BB%99i_%C4%91%E1%BB%8Ba</t>
         </is>
       </c>
-      <c r="I93" s="3" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
         <is>
           <t>Tăng trưởng kinh tế, GDP thực tế, GDP danh nghĩa, Tổng sản phẩm quốc dân, GDP bình quân đầu người</t>
         </is>
@@ -4157,7 +4707,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%95ng_s%E1%BA%A3n_l%C6%B0%E1%BB%A3ng_qu%E1%BB%91c_gia</t>
         </is>
       </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
         <is>
           <t>Tổng sản phẩm quốc nội, Tổng sản phẩm quốc dân, Bẫy thu nhập trung bình, Cán cân vãng lai</t>
         </is>
@@ -4198,7 +4753,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_gi%C3%A1_h%E1%BB%91i_%C4%91o%C3%A1i</t>
         </is>
       </c>
-      <c r="I95" s="3" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
         <is>
           <t>Tỷ giá trung tâm, Biên độ tỷ giá, Tỷ giá hối đoái thực, Dự trữ ngoại hối, Phá giá tiền tệ</t>
         </is>
@@ -4229,9 +4789,22 @@
           <t>Tỷ giá danh nghĩa đã được điều chỉnh theo chênh lệch mức giá giữa trong nước và nước ngoài, phản ánh sức cạnh tranh thực sự của hàng hóa một quốc gia; khi tính theo rổ các đối tác thương mại có trọng số thì gọi là tỷ giá thực đa phương (REER). Nếu lạm phát Việt Nam cao hơn đối tác mà tỷ giá danh nghĩa đứng yên, VND sẽ tăng giá thực và hàng xuất khẩu kém cạnh tranh hơn.</t>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="3" t="inlineStr">
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>Tỷ giá hối đoái (còn được gọi là tỷ giá trao đổi ngoại tệ, tỷ giá Forex, tỷ giá FX hoặc Agio) giữa hai tiền tệ là tỷ giá mà tại đó một đồng tiền này sẽ được trao đổi cho một đồng tiền khác. Nó cũng được coi là giá cả đồng tiền của một quốc gia được biểu hiện bởi một tiền tệ khác. Tiền tệ thường là đơn vị tiền của mỗi quốc gia, nhưng cũng có thể là đơn vị tiền của các khu vực cấp dưới như Hồng Kông, hoặc là đơn vị tiền siêu quốc gia như euro. Tỷ giá hối đoái còn biểu thị giá trị của tiền một nước so với tiền một nước khác.</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_gi%C3%A1_h%E1%BB%91i_%C4%91o%C3%A1i</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
         <is>
           <t>Tỷ giá hối đoái, Lạm phát, Cán cân thương mại, Phá giá tiền tệ</t>
         </is>
@@ -4264,7 +4837,8 @@
       </c>
       <c r="G97" s="3" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="3" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="3" t="inlineStr">
         <is>
           <t>Tỷ giá hối đoái, Biên độ tỷ giá, Ngân hàng Nhà nước Việt Nam</t>
         </is>
@@ -4305,7 +4879,12 @@
           <t>https://vi.wikipedia.org/wiki/Th%E1%BA%A5t_nghi%E1%BB%87p</t>
         </is>
       </c>
-      <c r="I98" s="3" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
         <is>
           <t>Lực lượng lao động, Thất nghiệp tự nhiên, Đường cong Phillips, Suy thoái kinh tế</t>
         </is>
@@ -4338,7 +4917,8 @@
       </c>
       <c r="G99" s="3" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="3" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr">
         <is>
           <t>Đầu tư công, Đầu tư trực tiếp nước ngoài, Hệ số sử dụng vốn tăng thêm, Tổng cầu</t>
         </is>
@@ -4369,9 +4949,22 @@
           <t>Đánh giá của các tổ chức xếp hạng như Moody's, S&amp;P Global và Fitch về khả năng và mức độ sẵn sàng trả nợ đúng hạn của Chính phủ một quốc gia. Hiện Việt Nam được xếp Ba2 (Moody's), BB+ (S&amp;P và Fitch), cách mức “đầu tư” 1–2 bậc; nâng hạng giúp giảm chi phí vay và thu hút thêm vốn ngoại.</t>
         </is>
       </c>
-      <c r="G100" s="3" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="3" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>A credit rating is an evaluation of the credit risk of a prospective debtor (an individual, a business, company or a government). It is the practice of predicting or forecasting the ability of a supposed debtor to pay back the debt or default. The credit rating represents an evaluation from a credit rating agency of the qualitative and quantitative information for the prospective debtor, including information provided by the prospective debtor and other non-public information obtained by the credit rating agency's analysts. Credit reporting (or credit score) is a subset of credit rating.</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Credit_rating</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
         <is>
           <t>Nợ công, Đầu tư gián tiếp nước ngoài, Thâm hụt ngân sách, Dự trữ ngoại hối</t>
         </is>
@@ -4402,9 +4995,22 @@
           <t>Tình trạng giá trị xuất khẩu lớn hơn giá trị nhập khẩu, tức cán cân thương mại thặng dư, giúp tăng nguồn cung ngoại tệ và hỗ trợ ổn định tỷ giá. Việt Nam xuất siêu hàng hóa liên tục từ năm 2016, năm 2025 khoảng 20 tỷ USD, tuy nhiên phần lớn thặng dư đến từ khu vực doanh nghiệp FDI.</t>
         </is>
       </c>
-      <c r="G101" s="3" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="3" t="inlineStr">
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>Cán cân thương mại là một mục trong tài khoản vãng lai của cán cân thanh toán quốc tế. Cán cân thương mại ghi lại những thay đổi trong xuất khẩu và nhập khẩu của một quốc gia trong một khoảng thời gian nhất định (quý hoặc năm) cũng như mức chênh lệch giữa chúng (xuất khẩu trừ đi nhập khẩu). Khi mức chênh lệch là lớn hơn 0, thì cán cân thương mại có thặng dư. Ngược lại, khi mức chênh lệch nhỏ hơn 0, thì cán cân thương mại có thâm hụt. Khi mức chênh lệch đúng bằng 0, cán cân thương mại ở trạng thái cân bằng. Cán cân thương mại còn được gọi là xuất khẩu ròng hoặc thặng dư thương mại.</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/C%C3%A1n_c%C3%A2n_th%C6%B0%C6%A1ng_m%E1%BA%A1i</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
         <is>
           <t>Cán cân thương mại, Nhập siêu, Dự trữ ngoại hối, Đầu tư trực tiếp nước ngoài</t>
         </is>
@@ -4449,7 +5055,12 @@
           <t>https://vi.wikipedia.org/wiki/B%E1%BA%A3ng_c%C3%A2n_%C4%91%E1%BB%91i_k%E1%BA%BF_to%C3%A1n</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính, Tài sản ngắn hạn, Tài sản dài hạn, Nợ phải trả, Vốn chủ sở hữu</t>
         </is>
@@ -4484,9 +5095,22 @@
           <t>Báo cáo trình bày doanh thu, chi phí và lợi nhuận (hoặc lỗ) của doanh nghiệp trong một kỳ, ví dụ một quý hay một năm. Các chỉ tiêu được sắp xếp từ doanh thu bán hàng (mã 01), qua lợi nhuận gộp (mã 20), lợi nhuận trước thuế (mã 50) đến lợi nhuận sau thuế (mã 60). Khác với Bảng cân đối kế toán, báo cáo này đo lường kết quả của cả một khoảng thời gian.</t>
         </is>
       </c>
-      <c r="G103" s="3" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="3" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Báo cáo kết quả kinh doanh, hay còn gọi là bảng báo cáo lãi lỗ, chỉ ra sự cân bằng giữa thu nhập (doanh thu) và chi phí trong từng kỳ kế toán. Bảng báo cáo này phản ánh tổng hợp tình hình và kết quả hoạt động sản xuất kinh doanh theo từng loại trong một thời kỳ kế toán và tình hình thực hiện nghĩa vụ đối với nhà nước. Báo cáo còn được sử dụng như một bảng hướng dẫn để xem xét doanh nghiệp sẽ hoạt động thế nào trong tương lai.</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/B%C3%A1o_c%C3%A1o_k%E1%BA%BFt_qu%E1%BA%A3_kinh_doanh</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
         <is>
           <t>Doanh thu thuần, Lợi nhuận gộp, Lợi nhuận trước thuế, Lợi nhuận sau thuế, Cơ sở dồn tích</t>
         </is>
@@ -4531,7 +5155,12 @@
           <t>https://vi.wikipedia.org/wiki/B%C3%A1o_c%C3%A1o_l%C6%B0u_chuy%E1%BB%83n_ti%E1%BB%81n_t%E1%BB%87</t>
         </is>
       </c>
-      <c r="I104" s="3" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần từ hoạt động kinh doanh, Lưu chuyển tiền thuần từ hoạt động đầu tư, Lưu chuyển tiền thuần từ hoạt động tài chính, Phương pháp trực tiếp, Phương pháp gián tiếp</t>
         </is>
@@ -4576,7 +5205,12 @@
           <t>https://vi.wikipedia.org/wiki/B%C3%A1o_c%C3%A1o_t%C3%A0i_ch%C3%ADnh</t>
         </is>
       </c>
-      <c r="I105" s="3" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
         <is>
           <t>Bảng cân đối kế toán, Báo cáo kết quả hoạt động kinh doanh, Báo cáo lưu chuyển tiền tệ, Thuyết minh báo cáo tài chính</t>
         </is>
@@ -4609,7 +5243,8 @@
       </c>
       <c r="G106" s="3" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="3" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính giữa niên độ, Soát xét báo cáo tài chính, Kiểm toán độc lập</t>
         </is>
@@ -4642,7 +5277,8 @@
       </c>
       <c r="G107" s="3" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="3" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính bán niên, Kỳ kế toán, Công bố thông tin, Soát xét báo cáo tài chính</t>
         </is>
@@ -4683,7 +5319,12 @@
           <t>https://vi.wikipedia.org/wiki/B%C3%A1o_c%C3%A1o_t%C3%A0i_ch%C3%ADnh_h%E1%BB%A3p_nh%E1%BA%A5t</t>
         </is>
       </c>
-      <c r="I108" s="3" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính riêng, Công ty mẹ, Công ty con, Lợi ích cổ đông không kiểm soát, Hợp nhất kinh doanh</t>
         </is>
@@ -4716,7 +5357,8 @@
       </c>
       <c r="G109" s="3" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="3" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất, Công ty mẹ, Nguyên tắc giá gốc</t>
         </is>
@@ -4753,7 +5395,8 @@
       </c>
       <c r="G110" s="3" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="3" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr">
         <is>
           <t>Tài sản dài hạn, Nguyên tắc giá gốc, Hàng tồn kho, Chuẩn mực báo cáo tài chính quốc tế</t>
         </is>
@@ -4794,7 +5437,12 @@
           <t>https://vi.wikipedia.org/wiki/B%C3%BAt_to%C3%A1n</t>
         </is>
       </c>
-      <c r="I111" s="3" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
         <is>
           <t>Nợ và Có, Tài khoản kế toán, Sổ kế toán</t>
         </is>
@@ -4827,7 +5475,8 @@
       </c>
       <c r="G112" s="3" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="3" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr">
         <is>
           <t>Doanh thu bán hàng và cung cấp dịch vụ, Doanh thu thuần</t>
         </is>
@@ -4864,7 +5513,8 @@
       </c>
       <c r="G113" s="3" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="3" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="3" t="inlineStr">
         <is>
           <t>Chi phí quản lý doanh nghiệp, Lợi nhuận thuần từ hoạt động kinh doanh, Lợi nhuận gộp</t>
         </is>
@@ -4897,7 +5547,8 @@
       </c>
       <c r="G114" s="3" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="3" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr">
         <is>
           <t>Thu nhập khác, Lợi nhuận trước thuế</t>
         </is>
@@ -4928,9 +5579,22 @@
           <t>Phần lãi doanh nghiệp phải trả cho các khoản vay và nợ thuê tài chính trong kỳ, được trình bày riêng tại mã 23 (dòng Trong đó của chi phí tài chính) trên Báo cáo kết quả hoạt động kinh doanh. Theo VAS 16, lãi vay dùng để xây dựng tài sản dở dang có thể được vốn hóa vào giá trị tài sản thay vì ghi vào chi phí trong kỳ.</t>
         </is>
       </c>
-      <c r="G115" s="3" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" s="3" t="inlineStr">
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Interest expense relates to the cost of borrowing money. It is the price that a lender charges a borrower for the use of the lender's money. On the income statement, interest expense can represent the cost of borrowing money from banks, bond investors, and other sources. Interest expense is different from operating expense and capital expense, for it relates to the capital structure of a company, and it is usually tax-deductible.</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Interest_expense</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
         <is>
           <t>Chi phí tài chính, Vay và nợ thuê tài chính, Xây dựng cơ bản dở dang</t>
         </is>
@@ -4967,7 +5631,8 @@
       </c>
       <c r="G116" s="3" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="3" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="3" t="inlineStr">
         <is>
           <t>Chi phí bán hàng, Dự phòng phải thu khó đòi, Lợi nhuận thuần từ hoạt động kinh doanh</t>
         </is>
@@ -5000,7 +5665,8 @@
       </c>
       <c r="G117" s="3" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="3" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="3" t="inlineStr">
         <is>
           <t>Chi phí lãi vay, Doanh thu hoạt động tài chính, Vay và nợ thuê tài chính</t>
         </is>
@@ -5033,7 +5699,8 @@
       </c>
       <c r="G118" s="3" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="3" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="3" t="inlineStr">
         <is>
           <t>Chi phí thuế thu nhập doanh nghiệp hoãn lại, Lợi nhuận trước thuế, Lợi nhuận sau thuế</t>
         </is>
@@ -5066,7 +5733,8 @@
       </c>
       <c r="G119" s="3" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr"/>
-      <c r="I119" s="3" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="3" t="inlineStr">
         <is>
           <t>Chi phí thuế thu nhập doanh nghiệp hiện hành, Lợi nhuận sau thuế, Nợ dài hạn</t>
         </is>
@@ -5097,9 +5765,22 @@
           <t>Các khoản chi phí đã chi ra nhưng liên quan đến nhiều kỳ kế toán nên được phân bổ dần vào chi phí, như tiền thuê đất trả trước, công cụ dụng cụ, chi phí sửa chữa lớn. Theo dõi trên TK 242; trên Bảng cân đối kế toán, phần ngắn hạn là mã 151 và phần dài hạn là mã 261.</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="3" t="inlineStr">
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>In accounting, a deferral is any account where the income or expense is not recognised until a future date. In accounting, deferral refers to the recognition of revenue or expenses at a later time than when the cash transaction occurs. This concept is used to align the reporting of financial transactions with the periods in which they are earned or incurred, according to the matching principle and revenue recognition principle. Deferrals are recorded as either assets or liabilities on the balance sheet until they are recognized in the appropriate accounting period.</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Deferral</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
         <is>
           <t>Phân bổ chi phí, Nguyên tắc phù hợp, Tài sản dài hạn</t>
         </is>
@@ -5134,9 +5815,22 @@
           <t>Bộ chuẩn mực do Hội đồng Chuẩn mực Kế toán Quốc tế (IASB) ban hành, được áp dụng tại hơn 140 quốc gia. Việt Nam có lộ trình áp dụng IFRS theo Quyết định 345/QĐ-BTC năm 2020, bắt đầu từ giai đoạn tự nguyện cho các doanh nghiệp lớn. IFRS nhấn mạnh giá trị hợp lý nhiều hơn VAS, ví dụ lợi thế thương mại không phân bổ mà chỉ kiểm tra suy giảm giá trị.</t>
         </is>
       </c>
-      <c r="G121" s="3" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="3" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>International Financial Reporting Standards (IFRS) are accounting standards issued by the IFRS Foundation and the International Accounting Standards Board (IASB). They constitute a standardised way of describing a company's financial performance and position so that company financial statements are understandable and comparable across international boundaries. They are particularly relevant for companies with publicly listed shares or securities.</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/International_Financial_Reporting_Standards</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
         <is>
           <t>Chuẩn mực kế toán Việt Nam, Lợi thế thương mại, Ghi nhận doanh thu</t>
         </is>
@@ -5173,7 +5867,8 @@
       </c>
       <c r="G122" s="3" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="3" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="3" t="inlineStr">
         <is>
           <t>Chuẩn mực báo cáo tài chính quốc tế, Thông tư 200/2014/TT-BTC, Báo cáo tài chính</t>
         </is>
@@ -5214,7 +5909,12 @@
           <t>https://vi.wikipedia.org/wiki/C%E1%BB%95_phi%E1%BA%BFu_ng%C3%A2n_qu%E1%BB%B9</t>
         </is>
       </c>
-      <c r="I123" s="3" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
         <is>
           <t>Vốn chủ sở hữu, Vốn góp của chủ sở hữu, Thặng dư vốn cổ phần</t>
         </is>
@@ -5245,9 +5945,22 @@
           <t>Nguyên tắc ghi nhận doanh thu, chi phí, tài sản và nợ vào thời điểm nghiệp vụ phát sinh, không phụ thuộc vào thời điểm thực thu hoặc thực chi tiền. Ví dụ bán chịu hàng trong quý 4 vẫn được ghi doanh thu quý 4 dù tháng sau mới thu tiền. Đây là lý do lợi nhuận và dòng tiền của doanh nghiệp thường không bằng nhau.</t>
         </is>
       </c>
-      <c r="G124" s="3" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr"/>
-      <c r="I124" s="3" t="inlineStr">
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>In accounting and finance, an accrual is an asset or liability that represents revenue or expenses that are receivable or payable but which have not yet been paid. In accrual accounting, the term accrued revenue refers to income that is recognized at the time a company delivers a service or good, even though the company has not yet been paid. Likewise, the term accrued expense refers to liabilities that are recognized when a company receives services or goods, even though the company has not yet paid the provider.</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Accrual</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
         <is>
           <t>Nguyên tắc phù hợp, Ghi nhận doanh thu, Báo cáo lưu chuyển tiền tệ, Phải thu khách hàng</t>
         </is>
@@ -5284,7 +5997,8 @@
       </c>
       <c r="G125" s="3" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr"/>
-      <c r="I125" s="3" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính giữa niên độ, Báo cáo tài chính bán niên, Giao dịch với các bên liên quan, Kiểm toán độc lập</t>
         </is>
@@ -5325,7 +6039,12 @@
           <t>https://vi.wikipedia.org/wiki/C%C3%B4ng_ty_con</t>
         </is>
       </c>
-      <c r="I126" s="3" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
         <is>
           <t>Công ty mẹ, Báo cáo tài chính hợp nhất, Lợi ích cổ đông không kiểm soát, Hợp nhất kinh doanh</t>
         </is>
@@ -5358,7 +6077,8 @@
       </c>
       <c r="G127" s="3" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr"/>
-      <c r="I127" s="3" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="3" t="inlineStr">
         <is>
           <t>Phương pháp vốn chủ sở hữu, Công ty con, Báo cáo tài chính hợp nhất</t>
         </is>
@@ -5399,7 +6119,12 @@
           <t>https://vi.wikipedia.org/wiki/C%C3%B4ng_ty_m%E1%BA%B9</t>
         </is>
       </c>
-      <c r="I128" s="3" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
         <is>
           <t>Công ty con, Báo cáo tài chính hợp nhất, Báo cáo tài chính riêng, Lợi ích cổ đông không kiểm soát</t>
         </is>
@@ -5432,7 +6157,8 @@
       </c>
       <c r="G129" s="3" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="3" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="3" t="inlineStr">
         <is>
           <t>Tiền và các khoản tương đương tiền, Tài sản ngắn hạn, Doanh thu hoạt động tài chính</t>
         </is>
@@ -5465,7 +6191,8 @@
       </c>
       <c r="G130" s="3" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
-      <c r="I130" s="3" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr">
         <is>
           <t>Nguyên tắc nhất quán, Trọng yếu, Sự kiện phát sinh sau ngày kết thúc kỳ kế toán</t>
         </is>
@@ -5498,7 +6225,8 @@
       </c>
       <c r="G131" s="3" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="3" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="3" t="inlineStr">
         <is>
           <t>Các khoản giảm trừ doanh thu, Doanh thu thuần, Ghi nhận doanh thu</t>
         </is>
@@ -5531,7 +6259,8 @@
       </c>
       <c r="G132" s="3" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr"/>
-      <c r="I132" s="3" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="3" t="inlineStr">
         <is>
           <t>Chi phí tài chính, Đầu tư tài chính ngắn hạn, Lợi nhuận thuần từ hoạt động kinh doanh</t>
         </is>
@@ -5568,7 +6297,8 @@
       </c>
       <c r="G133" s="3" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="3" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr">
         <is>
           <t>Doanh thu bán hàng và cung cấp dịch vụ, Các khoản giảm trừ doanh thu, Giá vốn hàng bán, Lợi nhuận gộp</t>
         </is>
@@ -5601,7 +6331,8 @@
       </c>
       <c r="G134" s="3" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" s="3" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="3" t="inlineStr">
         <is>
           <t>Hàng tồn kho, Giá vốn hàng bán, Nguyên tắc thận trọng</t>
         </is>
@@ -5634,7 +6365,8 @@
       </c>
       <c r="G135" s="3" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" s="3" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="3" t="inlineStr">
         <is>
           <t>Phải thu khách hàng, Chi phí quản lý doanh nghiệp, Nguyên tắc thận trọng</t>
         </is>
@@ -5665,9 +6397,22 @@
           <t>Nguyên tắc xác định thời điểm và giá trị doanh thu được ghi vào sổ sách. Theo VAS 14, doanh thu bán hàng được ghi nhận khi doanh nghiệp đã chuyển giao phần lớn rủi ro và lợi ích của hàng hóa cho người mua, không còn kiểm soát hàng hóa, doanh thu và chi phí xác định được đáng tin cậy và chắc chắn thu được lợi ích kinh tế. IFRS 15 dùng mô hình 5 bước dựa trên việc hoàn thành nghĩa vụ thực hiện hợp đồng.</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr"/>
-      <c r="I136" s="3" t="inlineStr">
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>In accounting, the revenue recognition principle states that revenues are earned and recognized when they are realized or realizable, no matter when cash is received. It is a cornerstone of accrual accounting together with the matching principle. Together, they determine the accounting period in which revenues and expenses are recognized. In contrast, the cash accounting recognizes revenues when cash is received, no matter when goods or services are sold.</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Revenue_recognition</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
         <is>
           <t>Doanh thu bán hàng và cung cấp dịch vụ, Cơ sở dồn tích, Người mua trả tiền trước, Chuẩn mực báo cáo tài chính quốc tế</t>
         </is>
@@ -5712,7 +6457,12 @@
           <t>https://vi.wikipedia.org/wiki/Gi%C3%A1_v%E1%BB%91n_h%C3%A0ng_b%C3%A1n</t>
         </is>
       </c>
-      <c r="I137" s="3" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
         <is>
           <t>Doanh thu thuần, Lợi nhuận gộp, Hàng tồn kho, Nguyên tắc phù hợp</t>
         </is>
@@ -5745,7 +6495,8 @@
       </c>
       <c r="G138" s="3" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="3" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="3" t="inlineStr">
         <is>
           <t>Thuyết minh báo cáo tài chính, Công ty mẹ, Công ty liên kết, Công bố thông tin</t>
         </is>
@@ -5790,7 +6541,12 @@
           <t>https://vi.wikipedia.org/wiki/H%C3%A0ng_t%E1%BB%93n_kho</t>
         </is>
       </c>
-      <c r="I139" s="3" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
         <is>
           <t>Dự phòng giảm giá hàng tồn kho, Giá vốn hàng bán, Tài sản ngắn hạn, Nguyên tắc giá gốc</t>
         </is>
@@ -5821,9 +6577,22 @@
           <t>Tổng số khấu hao đã trích của tài sản cố định hoặc bất động sản đầu tư tính từ khi bắt đầu sử dụng đến thời điểm báo cáo, theo dõi trên TK 214. Trên Bảng cân đối kế toán, khoản này được ghi số âm ngay dưới nguyên giá (ví dụ mã 223 với TSCĐ hữu hình). Tỷ lệ hao mòn lũy kế trên nguyên giá cao cho thấy tài sản đã cũ.</t>
         </is>
       </c>
-      <c r="G140" s="3" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="3" t="inlineStr">
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>Khấu hao tài sản cố định là việc phân bổ dần giá trị của tài sản cố định vào chi phí sản xuất, kinh doanh trong suốt thời gian tài sản đó được sử dụng (thời gian sử dụng hữu ích). Cụ thể, khái niệm này được hiểu rõ qua các điểm chính sau: 1. Bản chất Nó là cách doanh nghiệp chuyển dịch dần từng phần giá trị của tài sản (do bị hao mòn hữu hình hoặc hao mòn vô hình) vào giá thành sản phẩm hoặc chi phí vận hành hàng kỳ. 2. Mục đích Tránh biến động chi phí đột biến: Tài sản cố định thường có giá trị rất lớn.</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Kh%E1%BA%A5u_hao_t%C3%A0i_s%E1%BA%A3n_c%E1%BB%91_%C4%91%E1%BB%8Bnh</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá, Khấu hao tài sản cố định, Tài sản cố định hữu hình</t>
         </is>
@@ -5854,9 +6623,22 @@
           <t>Giả định rằng doanh nghiệp sẽ tiếp tục hoạt động bình thường trong tương lai gần, không buộc phải giải thể hay thu hẹp đáng kể quy mô; BCTC thông thường được lập dựa trên giả định này. Khi có nghi ngờ đáng kể về khả năng hoạt động liên tục (lỗ kéo dài, nợ quá hạn lớn), kiểm toán viên thường nêu trong báo cáo kiểm toán, và đây là tín hiệu cảnh báo quan trọng với nhà đầu tư.</t>
         </is>
       </c>
-      <c r="G141" s="3" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="3" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>A going concern is an accounting term for a business that is assumed will meet its financial obligations when they become due. It functions without the threat of liquidation for the foreseeable future, which is usually regarded as at least the next 12 months or the specified accounting period (the longer of the two). The presumption of going concern for the business implies the basic declaration of intention to keep operating its activities at least for the next year, which is a basic assumption for preparing financial statements that comprehend the conceptual framework of the IFRS.</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Going_concern</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
         <is>
           <t>Vấn đề cần nhấn mạnh, Kiểm toán độc lập, Nguyên tắc thận trọng</t>
         </is>
@@ -5887,9 +6669,22 @@
           <t>Việc kết hợp các doanh nghiệp hoặc hoạt động kinh doanh riêng biệt thành một đơn vị báo cáo, phổ biến nhất là khi một công ty mua quyền kiểm soát công ty khác (VAS 11, IFRS 3). Bên mua ghi nhận tài sản và nợ của bên bị mua theo giá trị hợp lý; phần giá phí vượt quá giá trị hợp lý tài sản thuần được ghi nhận là lợi thế thương mại.</t>
         </is>
       </c>
-      <c r="G142" s="3" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="3" t="inlineStr">
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>In business, consolidation or amalgamation is the merger and acquisition of many smaller companies into a few much larger ones. In the context of financial accounting, consolidation refers to the aggregation of financial statements of a group company as consolidated financial statements. The taxation term of consolidation refers to the treatment of a group of companies and other entities as one entity for tax purposes.</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Consolidation_(business)</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
         <is>
           <t>Lợi thế thương mại, Công ty mẹ, Công ty con, Báo cáo tài chính hợp nhất</t>
         </is>
@@ -5920,9 +6715,22 @@
           <t>Phương pháp khấu hao chia đều nguyên giá tài sản cố định cho số năm sử dụng: mức khấu hao năm = nguyên giá / thời gian sử dụng. Ví dụ máy móc nguyên giá 1 tỷ đồng dùng 10 năm thì mỗi năm trích 100 triệu đồng. Đây là phương pháp phổ biến nhất trên BCTC của doanh nghiệp Việt Nam.</t>
         </is>
       </c>
-      <c r="G143" s="3" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="3" t="inlineStr">
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>Khấu hao tài sản cố định là việc phân bổ dần giá trị của tài sản cố định vào chi phí sản xuất, kinh doanh trong suốt thời gian tài sản đó được sử dụng (thời gian sử dụng hữu ích). Cụ thể, khái niệm này được hiểu rõ qua các điểm chính sau: 1. Bản chất Nó là cách doanh nghiệp chuyển dịch dần từng phần giá trị của tài sản (do bị hao mòn hữu hình hoặc hao mòn vô hình) vào giá thành sản phẩm hoặc chi phí vận hành hàng kỳ. 2. Mục đích Tránh biến động chi phí đột biến: Tài sản cố định thường có giá trị rất lớn.</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Kh%E1%BA%A5u_hao_t%C3%A0i_s%E1%BA%A3n_c%E1%BB%91_%C4%91%E1%BB%8Bnh</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
         <is>
           <t>Khấu hao tài sản cố định, Khấu hao theo số dư giảm dần, Nguyên giá</t>
         </is>
@@ -5963,7 +6771,12 @@
           <t>https://vi.wikipedia.org/wiki/Kh%E1%BA%A5u_hao_t%C3%A0i_s%E1%BA%A3n_c%E1%BB%91_%C4%91%E1%BB%8Bnh</t>
         </is>
       </c>
-      <c r="I144" s="3" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
         <is>
           <t>Khấu hao đường thẳng, Khấu hao theo số dư giảm dần, Hao mòn lũy kế, Nguyên giá, Phương pháp gián tiếp</t>
         </is>
@@ -5996,7 +6809,8 @@
       </c>
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr"/>
-      <c r="I145" s="3" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="3" t="inlineStr">
         <is>
           <t>Khấu hao tài sản cố định, Khấu hao đường thẳng, Hao mòn lũy kế</t>
         </is>
@@ -6031,9 +6845,22 @@
           <t>Hệ thống quy trình, chính sách do ban lãnh đạo thiết lập nhằm đảm bảo hợp lý rằng BCTC đáng tin cậy, tài sản được bảo vệ, hoạt động hiệu quả và tuân thủ pháp luật. Theo khung COSO, kiểm soát nội bộ gồm môi trường kiểm soát, đánh giá rủi ro, hoạt động kiểm soát, thông tin và truyền thông, giám sát. Thông tư 99/2025/TT-BTC yêu cầu doanh nghiệp xây dựng hệ thống kiểm soát nội bộ.</t>
         </is>
       </c>
-      <c r="G146" s="3" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr"/>
-      <c r="I146" s="3" t="inlineStr">
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>Internal control, as defined by accounting and auditing, is a process for assuring of an organization's objectives in operational effectiveness and efficiency, reliable financial reporting, and compliance with laws, regulations and policies. A broad concept, internal control involves everything that controls risks to an organization. It is a means by which an organization's resources are directed, monitored, and measured.</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Internal_control</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
         <is>
           <t>Kiểm toán độc lập, Kiểm toán viên, Báo cáo tài chính</t>
         </is>
@@ -6066,7 +6893,8 @@
       </c>
       <c r="G147" s="3" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr"/>
-      <c r="I147" s="3" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="3" t="inlineStr">
         <is>
           <t>Kiểm toán viên, Ý kiến chấp nhận toàn phần, Soát xét báo cáo tài chính, Trọng yếu</t>
         </is>
@@ -6101,9 +6929,22 @@
           <t>Người có chứng chỉ kiểm toán viên do Bộ Tài chính cấp (hoặc chứng chỉ nước ngoài được công nhận) và đăng ký hành nghề tại một doanh nghiệp kiểm toán. Kiểm toán viên lập kế hoạch, thu thập bằng chứng và ký báo cáo kiểm toán, đồng thời phải giữ tính độc lập với doanh nghiệp được kiểm toán.</t>
         </is>
       </c>
-      <c r="G148" s="3" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr"/>
-      <c r="I148" s="3" t="inlineStr">
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>An auditor is a person or a firm appointed by a company to execute an audit. To act as an auditor, a person should be certified by the regulatory authority of accounting and auditing or possess certain specified qualifications. Generally, to act as an external auditor of the company, a person should have a certificate of practice from the regulatory authority. Audit firms are generally required to obtain official authorisation, registration, or recognition from a competent authority.</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Auditor</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
         <is>
           <t>Kiểm toán độc lập, Soát xét báo cáo tài chính, Kiểm soát nội bộ</t>
         </is>
@@ -6144,7 +6985,12 @@
           <t>https://vi.wikipedia.org/wiki/K%E1%BB%B3_k%E1%BA%BF_to%C3%A1n</t>
         </is>
       </c>
-      <c r="I149" s="3" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính giữa niên độ, Sổ kế toán, Sự kiện phát sinh sau ngày kết thúc kỳ kế toán</t>
         </is>
@@ -6177,7 +7023,8 @@
       </c>
       <c r="G150" s="3" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr"/>
-      <c r="I150" s="3" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất, Công ty con, Công ty mẹ, Vốn chủ sở hữu</t>
         </is>
@@ -6222,7 +7069,12 @@
           <t>https://vi.wikipedia.org/wiki/L%E1%BB%A3i_nhu%E1%BA%ADn_g%E1%BB%99p</t>
         </is>
       </c>
-      <c r="I151" s="3" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
         <is>
           <t>Doanh thu thuần, Giá vốn hàng bán, Lợi nhuận thuần từ hoạt động kinh doanh</t>
         </is>
@@ -6259,7 +7111,8 @@
       </c>
       <c r="G152" s="3" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr"/>
-      <c r="I152" s="3" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận trước thuế, Lợi ích cổ đông không kiểm soát, Lợi nhuận sau thuế chưa phân phối, Chi phí thuế thu nhập doanh nghiệp hiện hành</t>
         </is>
@@ -6290,9 +7143,22 @@
           <t>Phần lợi nhuận sau thuế lũy kế doanh nghiệp giữ lại, chưa chia cổ tức hay trích lập các quỹ, hoặc số lỗ lũy kế nếu mang giá trị âm. Theo dõi trên TK 421; trên Bảng cân đối kế toán là chỉ tiêu mã 421, tách thành phần lũy kế đến cuối kỳ trước (421a) và phần của kỳ này (421b). Số dư lớn cho thấy dư địa chia cổ tức hoặc tái đầu tư.</t>
         </is>
       </c>
-      <c r="G153" s="3" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr"/>
-      <c r="I153" s="3" t="inlineStr">
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>The retained earnings (also known as plowback) of a corporation is the accumulated net income of the corporation that is retained by the corporation at a particular point in time, such as at the end of the reporting period. At the end of that period, the net income (or net loss) at that point is transferred from the Profit and Loss Account to the retained earnings account. If the balance of the retained earnings account is negative it may be called accumulated losses, retained losses, accumulated deficit, or similar terminology.</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Retained_earnings</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận sau thuế, Vốn chủ sở hữu, Quỹ đầu tư phát triển</t>
         </is>
@@ -6325,7 +7191,8 @@
       </c>
       <c r="G154" s="3" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr"/>
-      <c r="I154" s="3" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận gộp, Chi phí bán hàng, Chi phí quản lý doanh nghiệp, Doanh thu hoạt động tài chính, Lợi nhuận trước thuế</t>
         </is>
@@ -6362,7 +7229,8 @@
       </c>
       <c r="G155" s="3" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr"/>
-      <c r="I155" s="3" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận thuần từ hoạt động kinh doanh, Thu nhập khác, Chi phí thuế thu nhập doanh nghiệp hiện hành, Lợi nhuận sau thuế, Phương pháp gián tiếp</t>
         </is>
@@ -6395,7 +7263,8 @@
       </c>
       <c r="G156" s="3" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr"/>
-      <c r="I156" s="3" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="3" t="inlineStr">
         <is>
           <t>Hợp nhất kinh doanh, Báo cáo tài chính hợp nhất, Phân bổ chi phí, Chuẩn mực báo cáo tài chính quốc tế</t>
         </is>
@@ -6432,7 +7301,8 @@
       </c>
       <c r="G157" s="3" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr"/>
-      <c r="I157" s="3" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="3" t="inlineStr">
         <is>
           <t>Báo cáo lưu chuyển tiền tệ, Xây dựng cơ bản dở dang, Tài sản cố định, Đầu tư tài chính ngắn hạn</t>
         </is>
@@ -6469,7 +7339,8 @@
       </c>
       <c r="G158" s="3" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr"/>
-      <c r="I158" s="3" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="3" t="inlineStr">
         <is>
           <t>Báo cáo lưu chuyển tiền tệ, Phương pháp gián tiếp, Lợi nhuận sau thuế, Phải thu khách hàng</t>
         </is>
@@ -6506,7 +7377,8 @@
       </c>
       <c r="G159" s="3" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr"/>
-      <c r="I159" s="3" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="3" t="inlineStr">
         <is>
           <t>Báo cáo lưu chuyển tiền tệ, Vay và nợ thuê tài chính, Vốn góp của chủ sở hữu, Cổ phiếu quỹ</t>
         </is>
@@ -6539,7 +7411,8 @@
       </c>
       <c r="G160" s="3" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr"/>
-      <c r="I160" s="3" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="3" t="inlineStr">
         <is>
           <t>Nợ ngắn hạn, Ghi nhận doanh thu, Phải thu khách hàng</t>
         </is>
@@ -6570,9 +7443,22 @@
           <t>Toàn bộ chi phí doanh nghiệp bỏ ra để có được tài sản cố định tính đến thời điểm đưa tài sản vào sử dụng, gồm giá mua, thuế không được hoàn lại, chi phí vận chuyển, lắp đặt, chạy thử. Nguyên giá trừ đi hao mòn lũy kế cho ra giá trị còn lại của tài sản trên sổ sách.</t>
         </is>
       </c>
-      <c r="G161" s="3" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr"/>
-      <c r="I161" s="3" t="inlineStr">
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>The historical cost of an asset at the time it is acquired or created is the value of the costs incurred in acquiring or creating the asset, comprising the consideration paid to acquire or create the asset plus transaction costs. Historical cost accounting involves reporting assets and liabilities at their historical costs, which are not updated for changes in the items' values. Consequently, the amounts reported for these balance sheet items often differ from their current economic or market values.</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Historical_cost</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
         <is>
           <t>Nguyên tắc giá gốc, Hao mòn lũy kế, Tài sản cố định, Khấu hao tài sản cố định</t>
         </is>
@@ -6605,7 +7491,8 @@
       </c>
       <c r="G162" s="3" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr"/>
-      <c r="I162" s="3" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá, Bất động sản đầu tư, Chuẩn mực báo cáo tài chính quốc tế</t>
         </is>
@@ -6638,7 +7525,8 @@
       </c>
       <c r="G163" s="3" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr"/>
-      <c r="I163" s="3" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="3" t="inlineStr">
         <is>
           <t>Điều chỉnh hồi tố, Thuyết minh báo cáo tài chính, Chuẩn mực kế toán Việt Nam</t>
         </is>
@@ -6669,9 +7557,22 @@
           <t>Nguyên tắc yêu cầu khi ghi nhận một khoản doanh thu thì phải ghi nhận đồng thời các chi phí tương ứng tạo ra doanh thu đó trong cùng kỳ. Ví dụ giá vốn của lô hàng được ghi vào kỳ bán lô hàng, còn chi phí mua máy móc được phân bổ dần qua khấu hao trong suốt thời gian máy tạo ra doanh thu.</t>
         </is>
       </c>
-      <c r="G164" s="3" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr"/>
-      <c r="I164" s="3" t="inlineStr">
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>In accrual basis accounting, the matching principle (or expense recognition principle) dictates that an expense should be reported in the same period as the corresponding revenue is earned. The revenue recognition principle states that revenues should be recorded in the period in which they are earned, regardless of when the cash is transferred. By recognising costs in the period they are incurred, a business can determine how much was spent to generate revenue, thereby reducing discrepancies between when costs are incurred and when revenue is realised.</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Matching_principle</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
         <is>
           <t>Cơ sở dồn tích, Giá vốn hàng bán, Khấu hao tài sản cố định, Phân bổ chi phí</t>
         </is>
@@ -6704,7 +7605,8 @@
       </c>
       <c r="G165" s="3" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr"/>
-      <c r="I165" s="3" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="3" t="inlineStr">
         <is>
           <t>Dự phòng giảm giá hàng tồn kho, Dự phòng phải thu khó đòi, Hoạt động liên tục, Ghi nhận doanh thu</t>
         </is>
@@ -6735,9 +7637,22 @@
           <t>Các khoản nợ có thời hạn thanh toán còn lại trên 12 tháng, như vay dài hạn, trái phiếu phát hành, nợ thuê tài chính dài hạn, thuế thu nhập hoãn lại phải trả. Trên Bảng cân đối kế toán là chỉ tiêu mã 330. Phần nợ dài hạn đến hạn trả trong 12 tháng tới được chuyển sang nợ ngắn hạn.</t>
         </is>
       </c>
-      <c r="G166" s="3" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr"/>
-      <c r="I166" s="3" t="inlineStr">
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>Long-term liabilities, or non-current liabilities, are liabilities that are due beyond a year or the normal operation period of the company. The normal operation period is the amount of time it takes for a company to turn inventory into cash. On a classified balance sheet, liabilities are separated between current and long-term liabilities to help users assess the company's financial standing in short-term and long-term periods.</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Long-term_liabilities</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
         <is>
           <t>Nợ phải trả, Nợ ngắn hạn, Vay và nợ thuê tài chính</t>
         </is>
@@ -6768,9 +7683,22 @@
           <t>Các khoản nợ phải thanh toán trong vòng 12 tháng hoặc một chu kỳ kinh doanh bình thường, như phải trả người bán, người mua trả tiền trước, thuế phải nộp, vay ngắn hạn. Trên Bảng cân đối kế toán là chỉ tiêu mã 310.</t>
         </is>
       </c>
-      <c r="G167" s="3" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr"/>
-      <c r="I167" s="3" t="inlineStr">
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>Current liabilities in accounting refer to the liabilities of a business that are expected to be settled in cash within one fiscal year or the firm's operating cycle, whichever is longer. These liabilities are typically settled using current assets or by incurring new current liabilities. Key examples of current liabilities include accounts payable, which are generally due within 30 to 60 days, though in some cases payments may be delayed. Current liabilities also include the portion of long-term loans or other debt obligations that are due within the current fiscal year.</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Current_liability</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
         <is>
           <t>Nợ phải trả, Tài sản ngắn hạn, Phải trả người bán, Người mua trả tiền trước</t>
         </is>
@@ -6815,7 +7743,12 @@
           <t>https://vi.wikipedia.org/wiki/N%E1%BB%A3_ph%E1%BA%A3i_tr%E1%BA%A3</t>
         </is>
       </c>
-      <c r="I168" s="3" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
         <is>
           <t>Nợ ngắn hạn, Nợ dài hạn, Vốn chủ sở hữu, Vay và nợ thuê tài chính</t>
         </is>
@@ -6846,9 +7779,22 @@
           <t>Hai bên của một tài khoản kế toán: bên Nợ (bên trái) và bên Có (bên phải); đây là quy ước ghi chép, không mang nghĩa vay nợ thông thường. Với tài khoản tài sản và chi phí, số tăng ghi bên Nợ, số giảm ghi bên Có; với tài khoản nợ phải trả, vốn chủ sở hữu và doanh thu thì ngược lại. Mỗi nghiệp vụ luôn ghi Nợ và ghi Có với số tiền bằng nhau (ghi sổ kép).</t>
         </is>
       </c>
-      <c r="G169" s="3" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr"/>
-      <c r="I169" s="3" t="inlineStr">
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>Debit and Credit (German: Soll und Haben, 1855) is a novel in six volumes by Gustav Freytag. It was one of the most popular and widely read German novels of the 19th century.</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Debit_and_Credit</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
         <is>
           <t>Bút toán, Tài khoản kế toán, Sổ kế toán</t>
         </is>
@@ -6879,9 +7825,22 @@
           <t>Số tiền khách hàng còn nợ doanh nghiệp do đã mua hàng hóa, dịch vụ nhưng chưa thanh toán, theo dõi trên TK 131. Trên Bảng cân đối kế toán, phần ngắn hạn là chỉ tiêu mã 131 và phần dài hạn là mã 211. Phải thu tăng nhanh hơn doanh thu có thể cho thấy doanh nghiệp nới lỏng bán chịu hoặc khó thu hồi nợ.</t>
         </is>
       </c>
-      <c r="G170" s="3" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr"/>
-      <c r="I170" s="3" t="inlineStr">
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>Các khoản phải thu, (accounts receivable, viết tắt là AR hoặc A/R) là các khiếu nại có hiệu lực pháp luật đối với khoản thanh toán do một doanh nghiệp nắm giữ đối với hàng hóa được cung cấp hoặc dịch vụ mà khách hàng đã đặt hàng nhưng chưa được thanh toán. Chúng thường ở dạng những hóa đơn do doanh nghiệp lập và được chuyển tới khách hàng để thanh toán trong một khung thời gian đã thỏa thuận. Các khoản phải thu được ghi trong bảng cân đối kế toán như một tài sản.</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/C%C3%A1c_kho%E1%BA%A3n_ph%E1%BA%A3i_thu</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
         <is>
           <t>Tài sản ngắn hạn, Dự phòng phải thu khó đòi, Doanh thu thuần, Người mua trả tiền trước</t>
         </is>
@@ -6912,9 +7871,22 @@
           <t>Số tiền doanh nghiệp còn nợ nhà cung cấp vì đã mua hàng hóa, dịch vụ, vật tư nhưng chưa thanh toán, theo dõi trên TK 331. Trên Bảng cân đối kế toán, phần ngắn hạn là mã 311 và dài hạn là mã 331. Đây là nguồn vốn chiếm dụng không mất lãi, phản ánh vị thế thương lượng của doanh nghiệp với nhà cung cấp.</t>
         </is>
       </c>
-      <c r="G171" s="3" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr"/>
-      <c r="I171" s="3" t="inlineStr">
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>Accounts payable (AP) is money owed by a business to its suppliers, shown as a liability on a company's balance sheet. It is distinct from notes payable liabilities, which are debts created by formal legal instrument documents. An accounts payable department's main responsibility is to process and review transactions between the company and its suppliers and to make sure that all outstanding invoices from their suppliers are approved, processed, and paid.</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Accounts_payable</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
         <is>
           <t>Nợ ngắn hạn, Phải thu khách hàng, Hàng tồn kho</t>
         </is>
@@ -6947,7 +7919,8 @@
       </c>
       <c r="G172" s="3" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr"/>
-      <c r="I172" s="3" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="3" t="inlineStr">
         <is>
           <t>Chi phí trả trước, Nguyên tắc phù hợp, Lợi thế thương mại, Khấu hao tài sản cố định</t>
         </is>
@@ -6980,7 +7953,8 @@
       </c>
       <c r="G173" s="3" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr"/>
-      <c r="I173" s="3" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="3" t="inlineStr">
         <is>
           <t>Báo cáo lưu chuyển tiền tệ, Phương pháp trực tiếp, Lợi nhuận trước thuế, Khấu hao tài sản cố định</t>
         </is>
@@ -7013,7 +7987,8 @@
       </c>
       <c r="G174" s="3" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr"/>
-      <c r="I174" s="3" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="3" t="inlineStr">
         <is>
           <t>Báo cáo lưu chuyển tiền tệ, Phương pháp gián tiếp, Lưu chuyển tiền thuần từ hoạt động kinh doanh</t>
         </is>
@@ -7044,9 +8019,22 @@
           <t>Phương pháp kế toán khoản đầu tư vào công ty liên kết, liên doanh: ban đầu ghi theo giá gốc, sau đó điều chỉnh tăng giảm theo phần sở hữu của nhà đầu tư trong lãi lỗ của bên nhận đầu tư và giảm khi nhận cổ tức. Trên BCTC hợp nhất, phần lãi hoặc lỗ này trình bày tại mã 24 của Báo cáo kết quả hoạt động kinh doanh.</t>
         </is>
       </c>
-      <c r="G175" s="3" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr"/>
-      <c r="I175" s="3" t="inlineStr">
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>Equity method in accounting is the process of treating investments in associate companies. Equity accounting is usually applied where an investor entity holds 20–50% of the voting shares of the associate company, and therefore has significant influence on the latter's management. Under International Financial Reporting Standards, equity method is also required in accounting for joint ventures. The investor records such investments as an asset on its balance sheet.</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Equity_method</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
         <is>
           <t>Công ty liên kết, Báo cáo tài chính hợp nhất, Lợi nhuận thuần từ hoạt động kinh doanh</t>
         </is>
@@ -7079,7 +8067,8 @@
       </c>
       <c r="G176" s="3" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr"/>
-      <c r="I176" s="3" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận sau thuế chưa phân phối, Vốn chủ sở hữu, Lợi nhuận sau thuế</t>
         </is>
@@ -7110,9 +8099,22 @@
           <t>Hệ thống sổ dùng để ghi chép, lưu giữ toàn bộ nghiệp vụ kinh tế phát sinh theo thời gian và theo từng tài khoản, gồm sổ tổng hợp (sổ Nhật ký, Sổ Cái) và sổ chi tiết. Doanh nghiệp có thể chọn các hình thức như Nhật ký chung, Chứng từ ghi sổ hay kế toán trên máy vi tính. Số liệu trên sổ kế toán là căn cứ để lập BCTC cuối kỳ.</t>
         </is>
       </c>
-      <c r="G177" s="3" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr"/>
-      <c r="I177" s="3" t="inlineStr">
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>A ledger is a book or collection of accounts in which accounting transactions are recorded. Each account has: an opening or brought-forward balance; a list of transactions, each recorded as either a debit or credit in separate columns (usually with a counter-entry on another page) and an ending or closing, or carry-forward, balance.</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ledger</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J177" s="3" t="inlineStr">
         <is>
           <t>Bút toán, Tài khoản kế toán, Kỳ kế toán, Thông tư 200/2014/TT-BTC</t>
         </is>
@@ -7145,7 +8147,8 @@
       </c>
       <c r="G178" s="3" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr"/>
-      <c r="I178" s="3" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính bán niên, Kiểm toán độc lập, Kiểm toán viên</t>
         </is>
@@ -7178,7 +8181,8 @@
       </c>
       <c r="G179" s="3" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr"/>
-      <c r="I179" s="3" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="3" t="inlineStr">
         <is>
           <t>Kỳ kế toán, Thuyết minh báo cáo tài chính, Điều chỉnh hồi tố</t>
         </is>
@@ -7213,9 +8217,22 @@
           <t>Công cụ dùng để phân loại và theo dõi riêng từng đối tượng kế toán như tiền, hàng tồn kho, doanh thu, chi phí. Hệ thống tài khoản theo Thông tư 200/2014/TT-BTC gồm 9 loại đánh số từ 1 đến 9, ví dụ TK 111 Tiền mặt, TK 131 Phải thu của khách hàng, TK 511 Doanh thu bán hàng và cung cấp dịch vụ, TK 632 Giá vốn hàng bán.</t>
         </is>
       </c>
-      <c r="G180" s="3" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr"/>
-      <c r="I180" s="3" t="inlineStr">
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>A chart of accounts (COA) is a list of financial accounts and reference numbers, grouped into categories, such as assets, liabilities, equity, revenue and expenses, and used for recording transactions in the organization's general ledger. Accounts may be associated with an identifier (account number) and a caption or header and are coded by account type. In computerized accounting systems with computable quantity accounting, the accounts can have a quantity measure definition.</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Chart_of_accounts</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
         <is>
           <t>Nợ và Có, Bút toán, Sổ kế toán, Thông tư 200/2014/TT-BTC</t>
         </is>
@@ -7260,7 +8277,12 @@
           <t>https://vi.wikipedia.org/wiki/T%C3%A0i_s%E1%BA%A3n_c%E1%BB%91_%C4%91%E1%BB%8Bnh</t>
         </is>
       </c>
-      <c r="I181" s="3" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
         <is>
           <t>Tài sản cố định hữu hình, Tài sản cố định vô hình, Tài sản cố định thuê tài chính, Khấu hao tài sản cố định, Nguyên giá</t>
         </is>
@@ -7301,7 +8323,12 @@
           <t>https://vi.wikipedia.org/wiki/T%C3%A0i_s%E1%BA%A3n_c%E1%BB%91_%C4%91%E1%BB%8Bnh</t>
         </is>
       </c>
-      <c r="I182" s="3" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J182" s="3" t="inlineStr">
         <is>
           <t>Tài sản cố định, Nguyên giá, Hao mòn lũy kế, Khấu hao tài sản cố định</t>
         </is>
@@ -7342,7 +8369,12 @@
           <t>https://vi.wikipedia.org/wiki/T%C3%A0i_s%E1%BA%A3n_c%E1%BB%91_%C4%91%E1%BB%8Bnh_thu%C3%AA_t%C3%A0i_ch%C3%ADnh</t>
         </is>
       </c>
-      <c r="I183" s="3" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J183" s="3" t="inlineStr">
         <is>
           <t>Tài sản cố định, Vay và nợ thuê tài chính, Khấu hao tài sản cố định</t>
         </is>
@@ -7375,7 +8407,8 @@
       </c>
       <c r="G184" s="3" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr"/>
-      <c r="I184" s="3" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="3" t="inlineStr">
         <is>
           <t>Tài sản cố định, Lợi thế thương mại, Khấu hao tài sản cố định</t>
         </is>
@@ -7412,7 +8445,8 @@
       </c>
       <c r="G185" s="3" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr"/>
-      <c r="I185" s="3" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="3" t="inlineStr">
         <is>
           <t>Tài sản ngắn hạn, Tài sản cố định, Bất động sản đầu tư, Xây dựng cơ bản dở dang</t>
         </is>
@@ -7449,7 +8483,8 @@
       </c>
       <c r="G186" s="3" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr"/>
-      <c r="I186" s="3" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="3" t="inlineStr">
         <is>
           <t>Tài sản dài hạn, Tiền và các khoản tương đương tiền, Hàng tồn kho, Phải thu khách hàng, Nợ ngắn hạn</t>
         </is>
@@ -7480,9 +8515,22 @@
           <t>Phần chênh lệch giữa giá phát hành cổ phiếu và mệnh giá khi công ty phát hành cổ phiếu, ví dụ phát hành giá 30.000 đồng thì 20.000 đồng mỗi cổ phiếu được ghi vào thặng dư. Theo dõi trên TK 4112; trên Bảng cân đối kế toán là chỉ tiêu mã 412. Thặng dư vốn có thể được dùng để phát hành cổ phiếu thưởng tăng vốn góp.</t>
         </is>
       </c>
-      <c r="G187" s="3" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr"/>
-      <c r="I187" s="3" t="inlineStr">
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>Capital surplus, also called share premium, is an account which may appear on a corporation's balance sheet, as a component of shareholders' equity, which represents the amount the corporation raises on the issue of shares in excess of their par value (nominal value) of the shares (common stock). This is called Additional paid in capital in US GAAP terminology but, additional paid in capital is not limited to share premium. It is a very broad concept and includes tax related and conversion related adjustments.</t>
+        </is>
+      </c>
+      <c r="H187" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Capital_surplus</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J187" s="3" t="inlineStr">
         <is>
           <t>Vốn góp của chủ sở hữu, Vốn chủ sở hữu, Cổ phiếu quỹ</t>
         </is>
@@ -7519,7 +8567,8 @@
       </c>
       <c r="G188" s="3" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr"/>
-      <c r="I188" s="3" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="3" t="inlineStr">
         <is>
           <t>Chuẩn mực kế toán Việt Nam, Tài khoản kế toán, Báo cáo tài chính, Sổ kế toán</t>
         </is>
@@ -7552,7 +8601,8 @@
       </c>
       <c r="G189" s="3" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr"/>
-      <c r="I189" s="3" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="3" t="inlineStr">
         <is>
           <t>Chi phí khác, Lợi nhuận trước thuế</t>
         </is>
@@ -7589,7 +8639,8 @@
       </c>
       <c r="G190" s="3" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr"/>
-      <c r="I190" s="3" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính, Giao dịch với các bên liên quan, Sự kiện phát sinh sau ngày kết thúc kỳ kế toán</t>
         </is>
@@ -7620,9 +8671,22 @@
           <t>Gồm tiền mặt, tiền gửi ngân hàng không kỳ hạn, tiền đang chuyển và các khoản đầu tư ngắn hạn có thời hạn thu hồi không quá 3 tháng, dễ chuyển thành tiền và ít rủi ro (như tiền gửi kỳ hạn dưới 3 tháng). Trên Bảng cân đối kế toán là chỉ tiêu mã 110. Đây cũng là số dư cuối kỳ được đối chiếu trên Báo cáo lưu chuyển tiền tệ.</t>
         </is>
       </c>
-      <c r="G191" s="3" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr"/>
-      <c r="I191" s="3" t="inlineStr">
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents (CCE) are the most liquid current assets found on a business's balance sheet. Cash equivalents are short-term commitments "with temporarily idle cash and easily convertible into a known cash amount". An investment normally counts as a cash equivalent when it has a short maturity period of 90 days or less, and can be included in the cash and cash equivalents balance from the date of acquisition when it carries an insignificant risk of changes in the asset value. If it has a maturity of more than 90 days, it is not considered a cash equivalent.</t>
+        </is>
+      </c>
+      <c r="H191" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Cash_and_cash_equivalents</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J191" s="3" t="inlineStr">
         <is>
           <t>Tài sản ngắn hạn, Đầu tư tài chính ngắn hạn, Báo cáo lưu chuyển tiền tệ</t>
         </is>
@@ -7655,7 +8719,8 @@
       </c>
       <c r="G192" s="3" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr"/>
-      <c r="I192" s="3" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="3" t="inlineStr">
         <is>
           <t>Kiểm toán độc lập, Ý kiến ngoại trừ, Ý kiến trái ngược, Thuyết minh báo cáo tài chính</t>
         </is>
@@ -7688,7 +8753,8 @@
       </c>
       <c r="G193" s="3" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr"/>
-      <c r="I193" s="3" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="3" t="inlineStr">
         <is>
           <t>Ý kiến trái ngược, Ý kiến ngoại trừ, Kiểm toán độc lập, Hoạt động liên tục</t>
         </is>
@@ -7719,9 +8785,22 @@
           <t>Đoạn trong báo cáo kiểm toán dùng để lưu ý người đọc về một vấn đề đã được trình bày trong BCTC mà kiểm toán viên cho là quan trọng, như sự không chắc chắn về khả năng hoạt động liên tục hay một vụ kiện lớn (VSA 706). Đoạn này không làm thay đổi ý kiến kiểm toán nhưng là thông tin cảnh báo đáng chú ý.</t>
         </is>
       </c>
-      <c r="G194" s="3" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr"/>
-      <c r="I194" s="3" t="inlineStr">
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>Emphasis of matter is a type of paragraph in an auditors' report on financial statements. Such a paragraph is added to indicate a matter which is disclosed appropriately in the notes forming part of the financial statements that the auditor considers is fundamental to the users' understanding of the financial statements. An emphasis of matter paragraph indicates that the auditor's opinion is not modified with respect to the matter emphasized.</t>
+        </is>
+      </c>
+      <c r="H194" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Emphasis_of_matter</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J194" s="3" t="inlineStr">
         <is>
           <t>Ý kiến chấp nhận toàn phần, Hoạt động liên tục, Kiểm toán viên</t>
         </is>
@@ -7754,7 +8833,8 @@
       </c>
       <c r="G195" s="3" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr"/>
-      <c r="I195" s="3" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="3" t="inlineStr">
         <is>
           <t>Chi phí lãi vay, Nợ ngắn hạn, Nợ dài hạn, Tài sản cố định thuê tài chính, Lưu chuyển tiền thuần từ hoạt động tài chính</t>
         </is>
@@ -7799,7 +8879,12 @@
           <t>https://vi.wikipedia.org/wiki/V%E1%BB%91n_ch%E1%BB%A7_s%E1%BB%9F_h%E1%BB%AFu</t>
         </is>
       </c>
-      <c r="I196" s="3" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J196" s="3" t="inlineStr">
         <is>
           <t>Vốn góp của chủ sở hữu, Thặng dư vốn cổ phần, Lợi nhuận sau thuế chưa phân phối, Lợi ích cổ đông không kiểm soát, Nợ phải trả</t>
         </is>
@@ -7830,9 +8915,22 @@
           <t>Số vốn các chủ sở hữu thực góp vào doanh nghiệp; với công ty cổ phần, khoản này bằng số cổ phiếu đã phát hành nhân với mệnh giá 10.000 đồng. Theo dõi trên TK 4111; trên Bảng cân đối kế toán là chỉ tiêu mã 411. Khoản này tăng khi công ty phát hành thêm cổ phiếu, kể cả trả cổ tức bằng cổ phiếu.</t>
         </is>
       </c>
-      <c r="G197" s="3" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr"/>
-      <c r="I197" s="3" t="inlineStr">
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>A corporation's share capital, commonly referred to as capital stock in the United States, is the portion of a corporation's equity that has been derived by the issue of shares in the corporation to a shareholder, usually for cash.</t>
+        </is>
+      </c>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Share_capital</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J197" s="3" t="inlineStr">
         <is>
           <t>Vốn chủ sở hữu, Thặng dư vốn cổ phần, Cổ phiếu quỹ</t>
         </is>
@@ -7867,9 +8965,22 @@
           <t>Chi phí đầu tư xây dựng, mua sắm, nâng cấp tài sản cố định đang thực hiện nhưng chưa hoàn thành, chưa đưa vào sử dụng. Theo dõi trên TK 241; trên Bảng cân đối kế toán là chỉ tiêu mã 242, thuộc Tài sản dở dang dài hạn. Khi dự án hoàn thành, khoản này được chuyển sang tài sản cố định và bắt đầu trích khấu hao.</t>
         </is>
       </c>
-      <c r="G198" s="3" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr"/>
-      <c r="I198" s="3" t="inlineStr">
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>An accountancy term, construction in progress (CIP) asset or capital work in progress entry records the cost of construction work, which is not yet completed (typically, applied to capital budget items). A CIP item is not depreciated until the asset is placed in service. Normally, upon completion, a CIP item is reclassified, and the reclassified asset is capitalized and depreciated. While costs are added to the construction in progress, related CIP account is debited with corresponding credits to accounts payable, accrued expenses, inventory, cash, and others.</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Construction_in_progress</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J198" s="3" t="inlineStr">
         <is>
           <t>Tài sản cố định, Tài sản dài hạn, Lưu chuyển tiền thuần từ hoạt động đầu tư</t>
         </is>
@@ -7902,7 +9013,8 @@
       </c>
       <c r="G199" s="3" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr"/>
-      <c r="I199" s="3" t="inlineStr">
+      <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" s="3" t="inlineStr">
         <is>
           <t>Kiểm toán độc lập, Ý kiến ngoại trừ, Vấn đề cần nhấn mạnh</t>
         </is>
@@ -7935,7 +9047,8 @@
       </c>
       <c r="G200" s="3" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr"/>
-      <c r="I200" s="3" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" s="3" t="inlineStr">
         <is>
           <t>Ý kiến chấp nhận toàn phần, Ý kiến trái ngược, Từ chối đưa ra ý kiến, Trọng yếu</t>
         </is>
@@ -7968,7 +9081,8 @@
       </c>
       <c r="G201" s="3" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr"/>
-      <c r="I201" s="3" t="inlineStr">
+      <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="3" t="inlineStr">
         <is>
           <t>Ý kiến ngoại trừ, Từ chối đưa ra ý kiến, Trọng yếu, Kiểm toán độc lập</t>
         </is>
@@ -8003,9 +9117,22 @@
           <t>Mô hình chấm điểm do Edward Altman xây dựng năm 1968 để dự báo nguy cơ phá sản của doanh nghiệp trong khoảng hai năm. Công thức gốc cho doanh nghiệp sản xuất niêm yết: Z = 1,2X1 + 1,4X2 + 3,3X3 + 0,6X4 + 1,0X5, với X1 = Vốn lưu động ròng / Tổng tài sản, X2 = Lợi nhuận giữ lại / Tổng tài sản, X3 = EBIT / Tổng tài sản, X4 = Giá trị thị trường vốn chủ / Tổng nợ, X5 = Doanh thu / Tổng tài sản. Z &gt; 2,99 là vùng an toàn, 1,81–2,99 là vùng xám, dưới 1,81 là vùng nguy hiểm; với doanh nghiệp phi sản xuất hoặc thị trường mới nổi như Việt Nam nên dùng phiên bản Z'' (bỏ X5) với ngưỡng riêng.</t>
         </is>
       </c>
-      <c r="G202" s="3" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr"/>
-      <c r="I202" s="3" t="inlineStr">
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>The Z-score formula for predicting bankruptcy was published in 1968 by Edward I. Altman, who was, at the time, an Assistant Professor of Finance at New York University. The formula may be used to determine the probability that a firm will go into bankruptcy within two years. Z-scores are used to predict corporate defaults and an easy-to-calculate control measure for the financial distress status of companies in academic studies. The Z-score uses multiple corporate income and balance sheet values to measure the financial health of a company.</t>
+        </is>
+      </c>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Altman_Z-score</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J202" s="3" t="inlineStr">
         <is>
           <t>Vốn lưu động ròng, Lợi nhuận trước lãi vay và thuế, Tỷ lệ nợ trên tổng tài sản, Piotroski F-score, Beneish M-score</t>
         </is>
@@ -8040,9 +9167,22 @@
           <t>Mô hình xác suất do Messod Beneish xây dựng để phát hiện khả năng doanh nghiệp thao túng lợi nhuận, dựa trên 8 chỉ số: DSRI (phải thu so với doanh thu), GMI (biên gộp), AQI (chất lượng tài sản), SGI (tăng trưởng doanh thu), DEPI (khấu hao), SGAI (chi phí bán hàng và quản lý), LVGI (đòn bẩy) và TATA (dồn tích trên tổng tài sản). Công thức: M = −4,84 + 0,92·DSRI + 0,528·GMI + 0,404·AQI + 0,892·SGI + 0,115·DEPI − 0,172·SGAI + 4,679·TATA − 0,327·LVGI. M lớn hơn −1,78 là dấu hiệu nghi vấn cần soát xét kỹ BCTC, nhưng đây chỉ là công cụ sàng lọc chứ không phải bằng chứng gian lận.</t>
         </is>
       </c>
-      <c r="G203" s="3" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr"/>
-      <c r="I203" s="3" t="inlineStr">
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>The Beneish model is a statistical model that uses financial ratios calculated with accounting data of a specific company in order to check if it is likely (high probability) that the reported earnings of the company have been manipulated.</t>
+        </is>
+      </c>
+      <c r="H203" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Beneish_M-score</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J203" s="3" t="inlineStr">
         <is>
           <t>Chất lượng lợi nhuận, Tỷ lệ dồn tích, Kỳ thu tiền bình quân, Altman Z-score</t>
         </is>
@@ -8079,7 +9219,8 @@
       </c>
       <c r="G204" s="3" t="inlineStr"/>
       <c r="H204" s="2" t="inlineStr"/>
-      <c r="I204" s="3" t="inlineStr">
+      <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" s="3" t="inlineStr">
         <is>
           <t>Giá trị nội tại, Phân tích độ nhạy, Giá trị hợp lý</t>
         </is>
@@ -8110,9 +9251,22 @@
           <t>Tỷ lệ EBITDA trên doanh thu, đo khả năng tạo tiền từ hoạt động cốt lõi trên mỗi đồng doanh thu. Công thức: Biên EBITDA = EBITDA / Doanh thu thuần × 100%. Chỉ số thường dùng để so sánh trong các ngành có khấu hao lớn như điện, viễn thông, cảng biển, thép, nơi biên lợi nhuận ròng bị chi phối mạnh bởi khấu hao và lãi vay.</t>
         </is>
       </c>
-      <c r="G205" s="3" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr"/>
-      <c r="I205" s="3" t="inlineStr">
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước lãi vay, thuế, khấu hao và khấu trừ dần của một công ty (thường được viết tắt là EBITDA, phát âm là ) là một thước đo lợi nhuận của hoạt động kinh doanh cốt lõi, tức là trước khi tính đến tác động của các khoản nợ, nghĩa vụ thuế và chi phí duy trì tài sản.</t>
+        </is>
+      </c>
+      <c r="H205" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/L%E1%BB%A3i_nhu%E1%BA%ADn_tr%C6%B0%E1%BB%9Bc_l%C3%A3i_vay,_thu%E1%BA%BF,_kh%E1%BA%A5u_hao_v%C3%A0_kh%E1%BA%A5u_tr%E1%BB%AB_d%E1%BA%A7n</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J205" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận trước lãi vay, thuế và khấu hao, Biên lợi nhuận hoạt động, Hệ số EV/EBITDA</t>
         </is>
@@ -8153,7 +9307,12 @@
           <t>https://vi.wikipedia.org/wiki/Bi%C3%AAn_l%E1%BB%A3i_nhu%E1%BA%ADn_g%E1%BB%99p</t>
         </is>
       </c>
-      <c r="I206" s="3" t="inlineStr">
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J206" s="3" t="inlineStr">
         <is>
           <t>Biên lợi nhuận hoạt động, Biên lợi nhuận ròng, Phân tích theo chiều dọc, Piotroski F-score</t>
         </is>
@@ -8194,7 +9353,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_su%E1%BA%A5t_l%E1%BB%A3i_nhu%E1%BA%ADn_tr%C3%AAn_doanh_thu</t>
         </is>
       </c>
-      <c r="I207" s="3" t="inlineStr">
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J207" s="3" t="inlineStr">
         <is>
           <t>Biên lợi nhuận gộp, Lợi nhuận trước lãi vay và thuế, Độ lớn đòn bẩy hoạt động, Lợi nhuận cốt lõi</t>
         </is>
@@ -8225,9 +9389,22 @@
           <t>Cho biết mỗi đồng doanh thu thuần mang lại bao nhiêu đồng lợi nhuận sau thuế. Công thức: Biên lợi nhuận ròng = LNST / Doanh thu thuần × 100%. Đây là thành phần đầu tiên của phân tích Dupont; biên ròng tăng nhờ khoản bất thường (như lãi thoái vốn) cần được loại trừ trước khi kết luận hiệu quả kinh doanh cải thiện.</t>
         </is>
       </c>
-      <c r="G208" s="3" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr"/>
-      <c r="I208" s="3" t="inlineStr">
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>Profit margin is a financial ratio that measures the percentage of profit earned by a company in relation to its revenue. Expressed as a percentage, it indicates how much profit the company makes for every dollar of revenue generated. Profit margin is important because this percentage provides a comprehensive picture of the operating efficiency of a business or an industry. All margin changes provide useful indicators for assessing growth potential, investment viability and the financial stability of a company relative to its competitors.</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Profit_margin</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J208" s="3" t="inlineStr">
         <is>
           <t>Biên lợi nhuận gộp, Phân tích Dupont, Lợi nhuận cốt lõi, Tỷ suất lợi nhuận trên vốn chủ sở hữu</t>
         </is>
@@ -8260,7 +9437,8 @@
       </c>
       <c r="G209" s="3" t="inlineStr"/>
       <c r="H209" s="2" t="inlineStr"/>
-      <c r="I209" s="3" t="inlineStr">
+      <c r="I209" s="2" t="inlineStr"/>
+      <c r="J209" s="3" t="inlineStr">
         <is>
           <t>Biên lợi nhuận hoạt động, Biên lợi nhuận ròng, Khoản mục bất thường</t>
         </is>
@@ -8291,9 +9469,22 @@
           <t>Mức độ lợi nhuận kế toán phản ánh đúng hiệu quả kinh doanh thực, được hậu thuẫn bởi dòng tiền và có tính bền vững, lặp lại. Dấu hiệu lợi nhuận chất lượng thấp gồm: dòng tiền kinh doanh thấp hơn lợi nhuận trong nhiều kỳ, phải thu và hàng tồn kho tăng nhanh hơn doanh thu, lợi nhuận phụ thuộc vào khoản bất thường hoặc giao dịch với bên liên quan, thay đổi chính sách khấu hao, trích lập dự phòng. Các công cụ đo lường thường dùng là tỷ lệ CFO/LNST, tỷ lệ dồn tích và Beneish M-score.</t>
         </is>
       </c>
-      <c r="G210" s="3" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr"/>
-      <c r="I210" s="3" t="inlineStr">
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>In accounting, earnings quality, also known as quality of earnings (QoE), refers to the ability of a firm's reported earnings (net profit/income) to predict its future cash flows. It is an assessment criterion for how "repeatable, controllable and bankable" a firm's earnings are, amongst other factors, and has variously been defined as the degree to which earnings reflect underlying economic effects, are better estimates of cash flows, are conservative, or are predictable.</t>
+        </is>
+      </c>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Earnings_quality</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J210" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ dòng tiền hoạt động trên lợi nhuận ròng, Tỷ lệ dồn tích, Khoản mục bất thường, Beneish M-score, Lợi nhuận cốt lõi</t>
         </is>
@@ -8330,7 +9521,8 @@
       </c>
       <c r="G211" s="3" t="inlineStr"/>
       <c r="H211" s="2" t="inlineStr"/>
-      <c r="I211" s="3" t="inlineStr">
+      <c r="I211" s="2" t="inlineStr"/>
+      <c r="J211" s="3" t="inlineStr">
         <is>
           <t>Chi phí vốn bình quân gia quyền, Hệ số khả năng thanh toán lãi vay, Chi phí vốn chủ sở hữu</t>
         </is>
@@ -8375,7 +9567,12 @@
           <t>https://vi.wikipedia.org/wiki/Chi_ph%C3%AD_v%E1%BB%91n_b%C3%ACnh_qu%C3%A2n_gia_quy%E1%BB%81n</t>
         </is>
       </c>
-      <c r="I212" s="3" t="inlineStr">
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J212" s="3" t="inlineStr">
         <is>
           <t>Chi phí vốn chủ sở hữu, Chi phí nợ, Mô hình chiết khấu dòng tiền, Tỷ suất lợi nhuận trên vốn đầu tư</t>
         </is>
@@ -8410,9 +9607,22 @@
           <t>Mức lợi suất tối thiểu cổ đông đòi hỏi để bù đắp rủi ro khi đầu tư vào cổ phiếu của doanh nghiệp. Thường được ước tính bằng CAPM: Ke = Lãi suất phi rủi ro + Beta × Phần bù rủi ro thị trường (có thể cộng thêm phần bù rủi ro quốc gia hoặc quy mô). Ke luôn cao hơn chi phí nợ và là tỷ lệ chiết khấu dùng cho FCFE, mô hình chiết khấu cổ tức và mô hình thu nhập thặng dư.</t>
         </is>
       </c>
-      <c r="G213" s="3" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr"/>
-      <c r="I213" s="3" t="inlineStr">
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>In finance, the cost of equity is the return (often expressed as a rate of return) a firm theoretically pays to its equity investors, i.e., shareholders, to compensate for the risk they undertake by investing their capital. Firms need to acquire capital from others to operate and grow. Individuals and organizations who are willing to provide their funds to others naturally desire to be rewarded. Just as landlords seek rents on their property, capital providers seek returns on their funds, which must be commensurate with the risk undertaken.</t>
+        </is>
+      </c>
+      <c r="H213" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Cost_of_equity</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J213" s="3" t="inlineStr">
         <is>
           <t>Mô hình định giá tài sản vốn, Hệ số beta, Lãi suất phi rủi ro, Phần bù rủi ro thị trường, Chi phí vốn bình quân gia quyền</t>
         </is>
@@ -8447,9 +9657,22 @@
           <t>Khoản tiền doanh nghiệp chi để mua sắm, xây dựng, nâng cấp tài sản cố định và tài sản dài hạn khác. Trên BCTC Việt Nam, capex được lấy từ chỉ tiêu Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác (mã 21) trong Báo cáo lưu chuyển tiền tệ. Nên phân biệt capex bảo trì (xấp xỉ mức khấu hao) và capex mở rộng; capex lớn kéo dài làm giảm dòng tiền tự do hiện tại nhưng có thể tạo tăng trưởng trong tương lai.</t>
         </is>
       </c>
-      <c r="G214" s="3" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr"/>
-      <c r="I214" s="3" t="inlineStr">
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>Chi phí vốn, chi tiêu vốn hay chi phí tài sản cố định (tiếng Anh: Capital Expenditures và thường được viết tắt là Capex) là số tiền mà công ty dành để mua, duy trì, hoặc cải thiện tài sản cố định, như nhà cửa, xe cộ, thiết bị hoặc đất. Nó được coi là chi phí đầu tư khi tài sản được mua mới hoặc khi tiền được sử dụng để kéo dài tuổi thọ hữu ích của một tài sản hiện có, chẳng hạn như sửa mái nhà.</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Chi_ph%C3%AD_t%C3%A0i_s%E1%BA%A3n_c%E1%BB%91_%C4%91%E1%BB%8Bnh</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J214" s="3" t="inlineStr">
         <is>
           <t>Dòng tiền tự do, Vòng quay tài sản cố định, Dòng tiền tự do cho doanh nghiệp</t>
         </is>
@@ -8494,7 +9717,12 @@
           <t>https://vi.wikipedia.org/wiki/Chu_k%E1%BB%B3_chuy%E1%BB%83n_%C4%91%E1%BB%95i_ti%E1%BB%81n_m%E1%BA%B7t</t>
         </is>
       </c>
-      <c r="I215" s="3" t="inlineStr">
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J215" s="3" t="inlineStr">
         <is>
           <t>Số ngày tồn kho bình quân, Kỳ thu tiền bình quân, Kỳ trả tiền bình quân, Nhu cầu vốn lưu động</t>
         </is>
@@ -8539,7 +9767,12 @@
           <t>https://vi.wikipedia.org/wiki/%C4%90i%E1%BB%83m_h%C3%B2a_v%E1%BB%91n</t>
         </is>
       </c>
-      <c r="I216" s="3" t="inlineStr">
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J216" s="3" t="inlineStr">
         <is>
           <t>Độ lớn đòn bẩy hoạt động, Phân tích độ nhạy, Biên lợi nhuận gộp</t>
         </is>
@@ -8570,9 +9803,22 @@
           <t>Phương pháp ước tính giá trị doanh nghiệp dựa trên bội số định giá (P/E, P/B, EV/EBITDA...) của các doanh nghiệp tương đồng về ngành, quy mô và thị trường. Công thức: Giá trị cổ phiếu = Bội số tham chiếu (thường là trung vị nhóm so sánh) × Chỉ tiêu tương ứng của doanh nghiệp (EPS, BVPS...). Do Việt Nam ít doanh nghiệp cùng ngành niêm yết, nhà phân tích hay dùng thêm nhóm so sánh trong khu vực ASEAN và điều chỉnh theo khác biệt về tăng trưởng, rủi ro.</t>
         </is>
       </c>
-      <c r="G217" s="3" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr"/>
-      <c r="I217" s="3" t="inlineStr">
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>Relative valuation also called valuation using multiples is the notion of comparing the price of an asset to the market value of similar assets. In the field of securities investment, the idea has led to important practical tools, which could presumably spot pricing anomalies. These tools have subsequently become instrumental in enabling analysts and investors to make vital decisions on asset allocation.</t>
+        </is>
+      </c>
+      <c r="H217" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Relative_valuation</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J217" s="3" t="inlineStr">
         <is>
           <t>Hệ số giá trên thu nhập, Hệ số giá trên giá trị sổ sách, Hệ số EV/EBITDA, Mô hình chiết khấu dòng tiền</t>
         </is>
@@ -8609,7 +9855,8 @@
       </c>
       <c r="G218" s="3" t="inlineStr"/>
       <c r="H218" s="2" t="inlineStr"/>
-      <c r="I218" s="3" t="inlineStr">
+      <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" s="3" t="inlineStr">
         <is>
           <t>Định giá so sánh, Mô hình chiết khấu dòng tiền, Nợ vay ròng, Giá trị doanh nghiệp</t>
         </is>
@@ -8646,7 +9893,8 @@
       </c>
       <c r="G219" s="3" t="inlineStr"/>
       <c r="H219" s="2" t="inlineStr"/>
-      <c r="I219" s="3" t="inlineStr">
+      <c r="I219" s="2" t="inlineStr"/>
+      <c r="J219" s="3" t="inlineStr">
         <is>
           <t>Độ lớn đòn bẩy tài chính, Độ lớn đòn bẩy tổng, Điểm hòa vốn, Biên lợi nhuận hoạt động</t>
         </is>
@@ -8683,7 +9931,8 @@
       </c>
       <c r="G220" s="3" t="inlineStr"/>
       <c r="H220" s="2" t="inlineStr"/>
-      <c r="I220" s="3" t="inlineStr">
+      <c r="I220" s="2" t="inlineStr"/>
+      <c r="J220" s="3" t="inlineStr">
         <is>
           <t>Độ lớn đòn bẩy hoạt động, Độ lớn đòn bẩy tổng, Hệ số khả năng thanh toán lãi vay, Hệ số đòn bẩy tài chính</t>
         </is>
@@ -8720,7 +9969,8 @@
       </c>
       <c r="G221" s="3" t="inlineStr"/>
       <c r="H221" s="2" t="inlineStr"/>
-      <c r="I221" s="3" t="inlineStr">
+      <c r="I221" s="2" t="inlineStr"/>
+      <c r="J221" s="3" t="inlineStr">
         <is>
           <t>Độ lớn đòn bẩy hoạt động, Độ lớn đòn bẩy tài chính, Phân tích độ nhạy</t>
         </is>
@@ -8755,9 +10005,22 @@
           <t>Lượng tiền doanh nghiệp tạo ra sau khi đã chi cho đầu tư duy trì và mở rộng tài sản cố định, có thể dùng để trả nợ, chia cổ tức hoặc mua lại cổ phiếu. Công thức đơn giản: FCF = Lưu chuyển tiền thuần từ hoạt động kinh doanh (mã 20) − Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác (mã 21) trên Báo cáo lưu chuyển tiền tệ. FCF dương và ổn định là dấu hiệu sức khỏe tài chính tốt; FCF âm kéo dài trong khi lợi nhuận cao là tín hiệu cần soi lại chất lượng lợi nhuận.</t>
         </is>
       </c>
-      <c r="G222" s="3" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr"/>
-      <c r="I222" s="3" t="inlineStr">
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>In financial accounting, free cash flow (FCF) or free cash flow to firm (FCFF) is the amount by which a business's operating cash flow exceeds its working capital needs and expenditures on fixed assets (known as capital expenditures). It is that portion of cash flow that can be extracted from a company and distributed to creditors and securities holders without causing issues in its operations.</t>
+        </is>
+      </c>
+      <c r="H222" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Free_cash_flow</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J222" s="3" t="inlineStr">
         <is>
           <t>Dòng tiền tự do cho doanh nghiệp, Dòng tiền tự do cho chủ sở hữu, Chi tiêu vốn, Chất lượng lợi nhuận</t>
         </is>
@@ -8792,9 +10055,22 @@
           <t>Dòng tiền còn lại thuộc về cổ đông sau khi doanh nghiệp đã trả mọi chi phí, nghĩa vụ nợ (lãi và gốc) và thực hiện các khoản đầu tư cần thiết. Công thức: FCFE = FCFF − Chi phí lãi vay × (1 − t) + Vay nợ ròng (vay mới − trả nợ gốc), hay FCFE = LNST + Khấu hao − Capex − Thay đổi vốn lưu động + Vay nợ ròng. Chiết khấu FCFE bằng chi phí vốn chủ sở hữu cho ra trực tiếp giá trị vốn chủ sở hữu, phù hợp với doanh nghiệp có cấu trúc nợ ổn định.</t>
         </is>
       </c>
-      <c r="G223" s="3" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr"/>
-      <c r="I223" s="3" t="inlineStr">
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>In corporate finance, free cash flow to equity (FCFE) is a metric of how much cash can be distributed to the equity shareholders of the company as dividends or stock buybacks—after all expenses, reinvestments, and debt repayments are taken care of. It is also referred to as the levered free cash flow or the flow to equity (FTE). Whereas dividends are the cash flows actually paid to shareholders, the FCFE is the cash flow simply available to shareholders. The FCFE is usually calculated as a part of DCF or LBO modelling and valuation.</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Free_cash_flow_to_equity</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J223" s="3" t="inlineStr">
         <is>
           <t>Dòng tiền tự do cho doanh nghiệp, Chi phí vốn chủ sở hữu, Mô hình chiết khấu dòng tiền, Dòng tiền tự do</t>
         </is>
@@ -8831,7 +10107,8 @@
       </c>
       <c r="G224" s="3" t="inlineStr"/>
       <c r="H224" s="2" t="inlineStr"/>
-      <c r="I224" s="3" t="inlineStr">
+      <c r="I224" s="2" t="inlineStr"/>
+      <c r="J224" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận hoạt động thuần sau thuế, Chi phí vốn bình quân gia quyền, Giá trị doanh nghiệp, Nhu cầu vốn lưu động, Dòng tiền tự do cho chủ sở hữu</t>
         </is>
@@ -8864,7 +10141,8 @@
       </c>
       <c r="G225" s="3" t="inlineStr"/>
       <c r="H225" s="2" t="inlineStr"/>
-      <c r="I225" s="3" t="inlineStr">
+      <c r="I225" s="2" t="inlineStr"/>
+      <c r="J225" s="3" t="inlineStr">
         <is>
           <t>Giá trị hợp lý, Hệ số P/E dự phóng, Phân tích kịch bản</t>
         </is>
@@ -8901,7 +10179,8 @@
       </c>
       <c r="G226" s="3" t="inlineStr"/>
       <c r="H226" s="2" t="inlineStr"/>
-      <c r="I226" s="3" t="inlineStr">
+      <c r="I226" s="2" t="inlineStr"/>
+      <c r="J226" s="3" t="inlineStr">
         <is>
           <t>Mô hình chiết khấu dòng tiền, Tốc độ tăng trưởng dài hạn, Chi phí vốn bình quân gia quyền, Mô hình Gordon</t>
         </is>
@@ -8936,9 +10215,22 @@
           <t>Tổng giá trị của doanh nghiệp đối với mọi nhà cung cấp vốn, xấp xỉ chi phí để mua lại toàn bộ doanh nghiệp. Công thức: EV = Vốn hóa thị trường + Nợ vay ngắn và dài hạn (gồm trái phiếu) + Lợi ích cổ đông không kiểm soát + Cổ phiếu ưu đãi − Tiền, tương đương tiền và tiền gửi có kỳ hạn. Khác với vốn hóa, EV không bị ảnh hưởng bởi cơ cấu vốn nên phù hợp để so sánh các doanh nghiệp có mức nợ khác nhau.</t>
         </is>
       </c>
-      <c r="G227" s="3" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr"/>
-      <c r="I227" s="3" t="inlineStr">
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>Enterprise value (EV), total enterprise value (TEV), or firm value (FV) is an economic measure reflecting the market value of a business (i.e. as distinct from market price). It is a sum of claims by all claimants: creditors (secured and unsecured) and shareholders (preferred and common). Enterprise value is one of the fundamental metrics used in business valuation, financial analysis, accounting, portfolio analysis, and risk analysis. Enterprise value is more comprehensive than market capitalization, which only reflects common equity.</t>
+        </is>
+      </c>
+      <c r="H227" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Enterprise_value</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J227" s="3" t="inlineStr">
         <is>
           <t>Hệ số EV/EBITDA, Hệ số EV/Doanh thu, Nợ vay ròng, Dòng tiền tự do cho doanh nghiệp</t>
         </is>
@@ -8969,9 +10261,22 @@
           <t>Trong kế toán (IFRS 13), giá trị hợp lý là mức giá sẽ nhận được khi bán một tài sản hoặc phải trả để chuyển giao một khoản nợ trong giao dịch thông thường giữa các bên tham gia thị trường tại ngày đo lường. Trong phân tích đầu tư, giá trị hợp lý của cổ phiếu là kết quả định giá tổng hợp, thường là bình quân có trọng số của nhiều phương pháp (DCF, P/E, P/B, EV/EBITDA). Việt Nam đang theo lộ trình áp dụng IFRS nên nhiều khoản mục theo VAS hiện vẫn được ghi nhận theo giá gốc thay vì giá trị hợp lý.</t>
         </is>
       </c>
-      <c r="G228" s="3" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr"/>
-      <c r="I228" s="3" t="inlineStr">
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>In economics and accounting, fair value is a rational and unbiased estimate of the potential market price of a good, service, or asset. The derivation takes into account such objective factors as the costs associated with production or replacement, market conditions and matters of supply and demand. Subjective factors may also be considered such as the risk characteristics, the cost of and return on capital, and individually perceived utility.</t>
+        </is>
+      </c>
+      <c r="H228" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fair_value</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J228" s="3" t="inlineStr">
         <is>
           <t>Giá trị nội tại, Giá mục tiêu, Định giá so sánh, Mô hình chiết khấu dòng tiền</t>
         </is>
@@ -9006,9 +10311,22 @@
           <t>Phần lợi nhuận kinh tế doanh nghiệp tạo ra sau khi đã trừ chi phí của toàn bộ vốn sử dụng, kể cả chi phí cơ hội của vốn chủ sở hữu. Công thức: EVA = NOPAT − WACC × Vốn đầu tư = (ROIC − WACC) × Vốn đầu tư. EVA dương nghĩa là doanh nghiệp tạo ra giá trị; EVA âm kéo dài dù vẫn có lãi kế toán nghĩa là doanh nghiệp đang phá hủy giá trị của cổ đông.</t>
         </is>
       </c>
-      <c r="G229" s="3" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr"/>
-      <c r="I229" s="3" t="inlineStr">
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>In accounting, as part of financial statements analysis, economic value added (EVA) is an estimate of a firm's economic profit, or the value created in excess of the required return of the company's shareholders. EVA is the net profit less the capital charge ($) for raising the firm's capital. The idea is that value is created when the return on the firm's economic capital employed exceeds the cost of that capital, and equally if the return is less than the cost of capital, the firm is operating at a loss. The value of EVA can be determined by making adjustments to GAAP accounting.</t>
+        </is>
+      </c>
+      <c r="H229" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Economic_value_added</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J229" s="3" t="inlineStr">
         <is>
           <t>Tỷ suất lợi nhuận trên vốn đầu tư, Chi phí vốn bình quân gia quyền, Lợi nhuận hoạt động thuần sau thuế, Mô hình thu nhập thặng dư</t>
         </is>
@@ -9041,7 +10359,8 @@
       </c>
       <c r="G230" s="3" t="inlineStr"/>
       <c r="H230" s="2" t="inlineStr"/>
-      <c r="I230" s="3" t="inlineStr">
+      <c r="I230" s="2" t="inlineStr"/>
+      <c r="J230" s="3" t="inlineStr">
         <is>
           <t>Mô hình chiết khấu dòng tiền, Biên an toàn, Giá trị hợp lý, Mô hình chiết khấu cổ tức</t>
         </is>
@@ -9078,7 +10397,8 @@
       </c>
       <c r="G231" s="3" t="inlineStr"/>
       <c r="H231" s="2" t="inlineStr"/>
-      <c r="I231" s="3" t="inlineStr">
+      <c r="I231" s="2" t="inlineStr"/>
+      <c r="J231" s="3" t="inlineStr">
         <is>
           <t>Hệ số giá trên giá trị sổ sách, Mô hình thu nhập thặng dư, Thu nhập trên mỗi cổ phiếu</t>
         </is>
@@ -9113,9 +10433,22 @@
           <t>Đo mức độ biến động của lợi suất cổ phiếu so với lợi suất toàn thị trường, đại diện cho rủi ro hệ thống không thể đa dạng hóa. Công thức: β = Cov(Ri, Rm) / Var(Rm); tại Việt Nam thường tính so với VN-Index bằng dữ liệu tuần hoặc tháng trong 2–5 năm. Beta lớn hơn 1 nghĩa là cổ phiếu biến động mạnh hơn thị trường (như chứng khoán, bất động sản), beta nhỏ hơn 1 thường gặp ở nhóm phòng thủ như điện, nước, tiêu dùng thiết yếu.</t>
         </is>
       </c>
-      <c r="G232" s="3" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr"/>
-      <c r="I232" s="3" t="inlineStr">
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>In finance, the beta (β or market beta or beta coefficient) is a statistic that measures the expected increase or decrease of an individual stock price in proportion to movements of the stock market as a whole. Beta can be used to indicate the contribution of an individual asset to the market risk of a portfolio when it is added in small quantity. It refers to an asset's non-diversifiable risk, systematic risk, or market risk. Beta is not a measure of idiosyncratic risk. Beta is the hedge ratio of an investment with respect to the stock market.</t>
+        </is>
+      </c>
+      <c r="H232" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Beta_(finance)</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J232" s="3" t="inlineStr">
         <is>
           <t>Mô hình định giá tài sản vốn, Chi phí vốn chủ sở hữu, Độ lớn đòn bẩy tài chính</t>
         </is>
@@ -9146,9 +10479,22 @@
           <t>Cho biết tổng tài sản lớn gấp bao nhiêu lần vốn chủ sở hữu, phản ánh mức độ doanh nghiệp dùng nợ (kể cả nợ không chịu lãi) để tài trợ tài sản. Công thức: Hệ số đòn bẩy tài chính = Tổng tài sản bình quân / Vốn chủ sở hữu bình quân. Đây là thành phần thứ ba trong phân tích Dupont: đòn bẩy cao khuếch đại ROE khi kinh doanh tốt nhưng cũng khuếch đại thua lỗ khi gặp khó khăn.</t>
         </is>
       </c>
-      <c r="G233" s="3" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr"/>
-      <c r="I233" s="3" t="inlineStr">
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>Trong tài chính, đòn bẩy hay đòn bẩy nợ (tiếng anh là leverage trong Anh-Mỹ hay gearing trong Anh-Anh và Anh-Úc) là bất kỳ kỹ thuật nào liên quan đến việc sử dụng nợ (tiền đi vay) thay vì vốn chủ sở hữu để mua tài sản, với kỳ vọng rằng lợi nhuận sau thuế cho chủ sở hữu vốn từ giao dịch sẽ vượt quá chi phí đi vay, thường là một số bội số ⁠— do đó nguồn gốc của từ này từ tác dụng của một đòn bẩy trong vật lý, một cỗ máy đơn giản khuếch đại việc áp dụng một lực đầu vào tương đối nhỏ thành một lực đầu ra tương ứng lớn hơn.</t>
+        </is>
+      </c>
+      <c r="H233" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/%C4%90%C3%B2n_b%E1%BA%A9y_(t%C3%A0i_ch%C3%ADnh)</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J233" s="3" t="inlineStr">
         <is>
           <t>Phân tích Dupont, Tỷ lệ nợ trên vốn chủ sở hữu, Tỷ suất lợi nhuận trên vốn chủ sở hữu, Độ lớn đòn bẩy tài chính</t>
         </is>
@@ -9185,7 +10531,8 @@
       </c>
       <c r="G234" s="3" t="inlineStr"/>
       <c r="H234" s="2" t="inlineStr"/>
-      <c r="I234" s="3" t="inlineStr">
+      <c r="I234" s="2" t="inlineStr"/>
+      <c r="J234" s="3" t="inlineStr">
         <is>
           <t>Hệ số giá trên doanh thu, Giá trị doanh nghiệp, Hệ số EV/EBITDA</t>
         </is>
@@ -9222,7 +10569,8 @@
       </c>
       <c r="G235" s="3" t="inlineStr"/>
       <c r="H235" s="2" t="inlineStr"/>
-      <c r="I235" s="3" t="inlineStr">
+      <c r="I235" s="2" t="inlineStr"/>
+      <c r="J235" s="3" t="inlineStr">
         <is>
           <t>Giá trị doanh nghiệp, Lợi nhuận trước lãi vay, thuế và khấu hao, Định giá so sánh, Hệ số EV/Doanh thu</t>
         </is>
@@ -9259,7 +10607,8 @@
       </c>
       <c r="G236" s="3" t="inlineStr"/>
       <c r="H236" s="2" t="inlineStr"/>
-      <c r="I236" s="3" t="inlineStr">
+      <c r="I236" s="2" t="inlineStr"/>
+      <c r="J236" s="3" t="inlineStr">
         <is>
           <t>Hệ số EV/Doanh thu, Biên lợi nhuận ròng, Định giá so sánh</t>
         </is>
@@ -9294,9 +10643,22 @@
           <t>So sánh giá thị trường với giá trị sổ sách của mỗi cổ phiếu. Công thức: P/B = Giá thị trường / BVPS. P/B được dùng phổ biến khi định giá ngân hàng, chứng khoán, bất động sản; P/B dưới 1 có thể là cơ hội nhưng cũng có thể phản ánh lo ngại về chất lượng tài sản hoặc ROE thấp kéo dài, vì về lý thuyết P/B hợp lý tăng theo ROE.</t>
         </is>
       </c>
-      <c r="G237" s="3" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr"/>
-      <c r="I237" s="3" t="inlineStr">
+      <c r="G237" s="3" t="inlineStr">
+        <is>
+          <t>The price-to-book ratio, or P/B ratio, (also PBR) is a financial ratio used to compare a company's current market value to its book value (where book value is the value of all assets minus liabilities owned by a company). The calculation can be performed in two ways, but the result should be the same. In the first way, the company's market capitalization can be divided by the company's total book value from its balance sheet.</t>
+        </is>
+      </c>
+      <c r="H237" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/P/B_ratio</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J237" s="3" t="inlineStr">
         <is>
           <t>Giá trị sổ sách trên mỗi cổ phiếu, Tỷ suất lợi nhuận trên vốn chủ sở hữu, Mô hình thu nhập thặng dư, Định giá so sánh</t>
         </is>
@@ -9341,7 +10703,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_s%E1%BB%91_P/E</t>
         </is>
       </c>
-      <c r="I238" s="3" t="inlineStr">
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J238" s="3" t="inlineStr">
         <is>
           <t>Thu nhập trên mỗi cổ phiếu, Hệ số P/E dự phóng, Hệ số PEG, Định giá so sánh, Số liệu bốn quý gần nhất</t>
         </is>
@@ -9376,9 +10743,22 @@
           <t>Đo mức độ lợi nhuận hoạt động đủ để trả lãi vay. Công thức: ICR = EBIT / Chi phí lãi vay (có thể dùng EBITDA thay EBIT để có góc nhìn dòng tiền). ICR dưới 1,5 lần là vùng rủi ro, dưới 1 nghĩa là lợi nhuận hoạt động không đủ trả lãi; nhiều doanh nghiệp bất động sản, thép Việt Nam từng có ICR giảm mạnh trong giai đoạn lãi suất tăng 2022–2023.</t>
         </is>
       </c>
-      <c r="G239" s="3" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr"/>
-      <c r="I239" s="3" t="inlineStr">
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>Tỷ số khả năng trả lãi (hay Tỷ số trang trải lãi vay) là một tỷ số tài chính đo lường khả năng sử dụng lợi nhuận thu được từ quá trình kinh doanh để trả lãi các khoản mà công ty đã vay.</t>
+        </is>
+      </c>
+      <c r="H239" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_s%E1%BB%91_kh%E1%BA%A3_n%C4%83ng_tr%E1%BA%A3_l%C3%A3i</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J239" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận trước lãi vay và thuế, Chi phí nợ, Nợ vay ròng trên EBITDA, Độ lớn đòn bẩy tài chính</t>
         </is>
@@ -9415,7 +10795,8 @@
       </c>
       <c r="G240" s="3" t="inlineStr"/>
       <c r="H240" s="2" t="inlineStr"/>
-      <c r="I240" s="3" t="inlineStr">
+      <c r="I240" s="2" t="inlineStr"/>
+      <c r="J240" s="3" t="inlineStr">
         <is>
           <t>Hệ số giá trên thu nhập, Hệ số PEG, Tỷ lệ hoàn thành kế hoạch</t>
         </is>
@@ -9452,7 +10833,8 @@
       </c>
       <c r="G241" s="3" t="inlineStr"/>
       <c r="H241" s="2" t="inlineStr"/>
-      <c r="I241" s="3" t="inlineStr">
+      <c r="I241" s="2" t="inlineStr"/>
+      <c r="J241" s="3" t="inlineStr">
         <is>
           <t>Hệ số giá trên thu nhập, Hệ số P/E dự phóng, Tốc độ tăng trưởng kép hàng năm</t>
         </is>
@@ -9493,7 +10875,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_s%E1%BB%91_thanh_kho%E1%BA%A3n_hi%E1%BB%87n_th%E1%BB%9Di</t>
         </is>
       </c>
-      <c r="I242" s="3" t="inlineStr">
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J242" s="3" t="inlineStr">
         <is>
           <t>Hệ số thanh toán nhanh, Hệ số thanh toán tiền mặt, Vốn lưu động ròng, Piotroski F-score</t>
         </is>
@@ -9524,9 +10911,22 @@
           <t>Đo khả năng thanh toán nợ ngắn hạn bằng các tài sản có tính thanh khoản cao, loại trừ hàng tồn kho. Công thức: Hệ số thanh toán nhanh = (Tài sản ngắn hạn − Hàng tồn kho) / Nợ ngắn hạn. Hệ số dưới 0,5 là đáng lưu ý, đặc biệt với doanh nghiệp có hàng tồn kho lớn và chậm luân chuyển như bất động sản.</t>
         </is>
       </c>
-      <c r="G243" s="3" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr"/>
-      <c r="I243" s="3" t="inlineStr">
+      <c r="G243" s="3" t="inlineStr">
+        <is>
+          <t>Tỷ số thanh khoản nhanh (hay Hệ số khả năng thanh toán nhanh, Hệ số khả năng thanh toán tức thời, Hệ số thanh toán tức thời, Hệ số thử axit) là một tỷ số tài chính dùng nhằm đo khả năng huy động tài sản lưu động của một doanh nghiệp để thanh toán ngay các khoản nợ ngắn hạn của doanh nghiệp này.</t>
+        </is>
+      </c>
+      <c r="H243" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_s%E1%BB%91_thanh_kho%E1%BA%A3n_nhanh</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J243" s="3" t="inlineStr">
         <is>
           <t>Hệ số thanh toán hiện hành, Hệ số thanh toán tiền mặt, Vòng quay hàng tồn kho</t>
         </is>
@@ -9559,7 +10959,8 @@
       </c>
       <c r="G244" s="3" t="inlineStr"/>
       <c r="H244" s="2" t="inlineStr"/>
-      <c r="I244" s="3" t="inlineStr">
+      <c r="I244" s="2" t="inlineStr"/>
+      <c r="J244" s="3" t="inlineStr">
         <is>
           <t>Hệ số thanh toán nhanh, Hệ số thanh toán hiện hành, Nợ vay ròng</t>
         </is>
@@ -9592,7 +10993,8 @@
       </c>
       <c r="G245" s="3" t="inlineStr"/>
       <c r="H245" s="2" t="inlineStr"/>
-      <c r="I245" s="3" t="inlineStr">
+      <c r="I245" s="2" t="inlineStr"/>
+      <c r="J245" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận cốt lõi, Chất lượng lợi nhuận, Biên lợi nhuận trước thuế</t>
         </is>
@@ -9637,7 +11039,12 @@
           <t>https://vi.wikipedia.org/wiki/K%E1%BB%B3_thu_ti%E1%BB%81n_b%C3%ACnh_qu%C3%A2n</t>
         </is>
       </c>
-      <c r="I246" s="3" t="inlineStr">
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J246" s="3" t="inlineStr">
         <is>
           <t>Vòng quay khoản phải thu, Chu kỳ chuyển đổi tiền mặt, Kỳ trả tiền bình quân</t>
         </is>
@@ -9672,9 +11079,22 @@
           <t>Số ngày bình quân doanh nghiệp được nhà cung cấp cho nợ trước khi phải thanh toán. Công thức: DPO = Phải trả người bán bình quân / Giá vốn hàng bán × 365 = 365 / Vòng quay khoản phải trả. DPO dài giúp rút ngắn chu kỳ chuyển đổi tiền mặt; các nhà bán lẻ lớn thường có DPO cao nhờ sức mạnh đàm phán với nhà cung cấp.</t>
         </is>
       </c>
-      <c r="G247" s="3" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr"/>
-      <c r="I247" s="3" t="inlineStr">
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>Days payable outstanding (DPO) is an efficiency ratio that measures the average number of days a company takes to pay its suppliers. The formula is DPO = (ending AP)/(purchase per day), where ending AP is the accounts payable balance at the end of the accounting period being considered and purchase per day is calculated by dividing the total cost of goods sold per year by 365 days. DPO provides one measure of how long a business holds onto its cash. DPO can also be used to compare one company's payment policies to another.</t>
+        </is>
+      </c>
+      <c r="H247" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Days_payable_outstanding</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J247" s="3" t="inlineStr">
         <is>
           <t>Vòng quay khoản phải trả, Chu kỳ chuyển đổi tiền mặt, Kỳ thu tiền bình quân</t>
         </is>
@@ -9709,9 +11129,22 @@
           <t>Lợi suất của khoản đầu tư được coi như không có rủi ro vỡ nợ, là điểm xuất phát của mọi tỷ lệ chiết khấu. Tại Việt Nam, nhà phân tích thường dùng lợi suất trái phiếu Chính phủ kỳ hạn 10 năm (hoặc kỳ hạn khớp với thời gian dự phóng) do Kho bạc Nhà nước phát hành. Lãi suất phi rủi ro tăng làm tăng chi phí vốn và kéo giảm giá trị định giá của cổ phiếu, nhất là nhóm tăng trưởng.</t>
         </is>
       </c>
-      <c r="G248" s="3" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr"/>
-      <c r="I248" s="3" t="inlineStr">
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>The risk-free rate of return, usually shortened to the risk-free rate, is the rate of return of a hypothetical investment with scheduled payments over a fixed period of time that is assumed to meet all payment obligations. Since the risk-free rate can be obtained with no risk, any other investment having some risk will have to have a higher rate of return in order to induce any investors to hold it.</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Risk-free_rate</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J248" s="3" t="inlineStr">
         <is>
           <t>Mô hình định giá tài sản vốn, Phần bù rủi ro thị trường, Chi phí vốn chủ sở hữu</t>
         </is>
@@ -9744,7 +11177,8 @@
       </c>
       <c r="G249" s="3" t="inlineStr"/>
       <c r="H249" s="2" t="inlineStr"/>
-      <c r="I249" s="3" t="inlineStr">
+      <c r="I249" s="2" t="inlineStr"/>
+      <c r="J249" s="3" t="inlineStr">
         <is>
           <t>Khoản mục bất thường, Chất lượng lợi nhuận, Biên lợi nhuận ròng, Thu nhập trên mỗi cổ phiếu</t>
         </is>
@@ -9779,9 +11213,22 @@
           <t>Lợi nhuận từ hoạt động kinh doanh sau thuế nhưng chưa trừ chi phí lãi vay, tức lợi nhuận doanh nghiệp tạo ra nếu hoàn toàn không vay nợ. Công thức: NOPAT = EBIT × (1 − Thuế suất thuế TNDN), với thuế suất phổ thông tại Việt Nam là 20%. NOPAT là tử số của ROIC, EVA và là điểm xuất phát để tính FCFF.</t>
         </is>
       </c>
-      <c r="G250" s="3" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr"/>
-      <c r="I250" s="3" t="inlineStr">
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>In corporate finance, net operating profit after tax (NOPAT) is a company's after-tax operating profit for all investors, including shareholders and debt holders. NOPAT is used by analysts and investors as a precise and accurate measurement of profitability to compare a company's financial results across its history and against competitors. When calculating NOPAT, one removes Interest Expense and the effects of other non-operating activities (non-recurring gains and losses) from Net Income to arrive at a value that approximates the value of a firm's annual earnings.</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Net_operating_profit_after_taxes</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J250" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận trước lãi vay và thuế, Tỷ suất lợi nhuận trên vốn đầu tư, Giá trị kinh tế gia tăng, Dòng tiền tự do cho doanh nghiệp</t>
         </is>
@@ -9816,9 +11263,22 @@
           <t>Thước đo gần đúng dòng tiền tạo ra từ hoạt động kinh doanh trước khi tính đến cấu trúc vốn, thuế và chính sách khấu hao. Công thức: EBITDA = EBIT + Khấu hao và phân bổ (lấy từ chỉ tiêu Khấu hao TSCĐ và BĐSĐT trên Báo cáo lưu chuyển tiền tệ). Hữu ích khi so sánh doanh nghiệp thâm dụng vốn, nhưng không phản ánh nhu cầu capex và vốn lưu động nên không thay thế được dòng tiền tự do.</t>
         </is>
       </c>
-      <c r="G251" s="3" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr"/>
-      <c r="I251" s="3" t="inlineStr">
+      <c r="G251" s="3" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước lãi vay, thuế, khấu hao và khấu trừ dần của một công ty (thường được viết tắt là EBITDA, phát âm là ) là một thước đo lợi nhuận của hoạt động kinh doanh cốt lõi, tức là trước khi tính đến tác động của các khoản nợ, nghĩa vụ thuế và chi phí duy trì tài sản.</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/L%E1%BB%A3i_nhu%E1%BA%ADn_tr%C6%B0%E1%BB%9Bc_l%C3%A3i_vay,_thu%E1%BA%BF,_kh%E1%BA%A5u_hao_v%C3%A0_kh%E1%BA%A5u_tr%E1%BB%AB_d%E1%BA%A7n</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J251" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận trước lãi vay và thuế, Biên EBITDA, Hệ số EV/EBITDA, Nợ vay ròng trên EBITDA</t>
         </is>
@@ -9863,7 +11323,12 @@
           <t>https://vi.wikipedia.org/wiki/L%E1%BB%A3i_nhu%E1%BA%ADn_tr%C6%B0%E1%BB%9Bc_thu%E1%BA%BF_v%C3%A0_l%C3%A3i</t>
         </is>
       </c>
-      <c r="I252" s="3" t="inlineStr">
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J252" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận trước lãi vay, thuế và khấu hao, Lợi nhuận hoạt động thuần sau thuế, Hệ số khả năng thanh toán lãi vay, Tỷ suất lợi nhuận trên vốn sử dụng</t>
         </is>
@@ -9898,9 +11363,22 @@
           <t>Phương pháp định giá cổ phiếu bằng giá trị hiện tại của toàn bộ cổ tức kỳ vọng trong tương lai. Công thức: P0 = Σ D_t / (1 + Ke)^t. Mô hình phù hợp với doanh nghiệp chi trả cổ tức tiền mặt đều đặn như điện, nước, cảng, nhưng kém phù hợp với nhiều doanh nghiệp Việt Nam hay chia cổ tức bằng cổ phiếu hoặc giữ lại phần lớn lợi nhuận.</t>
         </is>
       </c>
-      <c r="G253" s="3" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr"/>
-      <c r="I253" s="3" t="inlineStr">
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>In financial economics, the dividend discount model (DDM) is a method of valuing the price of a company's capital stock or business value based on the assertion that intrinsic value is determined by the sum of future cash flows from dividend payments to shareholders, discounted back to their present value. The constant-growth form of the DDM is sometimes referred to as the Gordon growth model (GGM), after Myron J.</t>
+        </is>
+      </c>
+      <c r="H253" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Dividend_discount_model</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J253" s="3" t="inlineStr">
         <is>
           <t>Mô hình Gordon, Chi phí vốn chủ sở hữu, Tỷ suất cổ tức, Tỷ lệ chi trả cổ tức</t>
         </is>
@@ -9937,7 +11415,8 @@
       </c>
       <c r="G254" s="3" t="inlineStr"/>
       <c r="H254" s="2" t="inlineStr"/>
-      <c r="I254" s="3" t="inlineStr">
+      <c r="I254" s="2" t="inlineStr"/>
+      <c r="J254" s="3" t="inlineStr">
         <is>
           <t>Dòng tiền tự do cho doanh nghiệp, Chi phí vốn bình quân gia quyền, Giá trị cuối kỳ, Phân tích độ nhạy, Giá trị nội tại</t>
         </is>
@@ -9982,7 +11461,12 @@
           <t>https://vi.wikipedia.org/wiki/M%C3%B4_h%C3%ACnh_%C4%91%E1%BB%8Bnh_gi%C3%A1_t%C3%A0i_s%E1%BA%A3n_v%E1%BB%91n</t>
         </is>
       </c>
-      <c r="I255" s="3" t="inlineStr">
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J255" s="3" t="inlineStr">
         <is>
           <t>Chi phí vốn chủ sở hữu, Hệ số beta, Phần bù rủi ro thị trường, Lãi suất phi rủi ro</t>
         </is>
@@ -10013,9 +11497,22 @@
           <t>Dạng đơn giản của mô hình chiết khấu cổ tức, giả định cổ tức tăng trưởng đều mãi mãi với tốc độ g không đổi. Công thức: P0 = D1 / (Ke − g), trong đó D1 là cổ tức dự kiến năm tới và điều kiện bắt buộc là Ke &gt; g. Công thức cùng dạng cũng được dùng để tính giá trị cuối kỳ trong DCF và để suy ra P/E, P/B hợp lý.</t>
         </is>
       </c>
-      <c r="G256" s="3" t="inlineStr"/>
-      <c r="H256" s="2" t="inlineStr"/>
-      <c r="I256" s="3" t="inlineStr">
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>In financial economics, the dividend discount model (DDM) is a method of valuing the price of a company's capital stock or business value based on the assertion that intrinsic value is determined by the sum of future cash flows from dividend payments to shareholders, discounted back to their present value. The constant-growth form of the DDM is sometimes referred to as the Gordon growth model (GGM), after Myron J.</t>
+        </is>
+      </c>
+      <c r="H256" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Dividend_discount_model</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J256" s="3" t="inlineStr">
         <is>
           <t>Mô hình chiết khấu cổ tức, Tốc độ tăng trưởng dài hạn, Giá trị cuối kỳ, Chi phí vốn chủ sở hữu</t>
         </is>
@@ -10052,7 +11549,8 @@
       </c>
       <c r="G257" s="3" t="inlineStr"/>
       <c r="H257" s="2" t="inlineStr"/>
-      <c r="I257" s="3" t="inlineStr">
+      <c r="I257" s="2" t="inlineStr"/>
+      <c r="J257" s="3" t="inlineStr">
         <is>
           <t>Giá trị sổ sách trên mỗi cổ phiếu, Chi phí vốn chủ sở hữu, Giá trị kinh tế gia tăng, Hệ số giá trên giá trị sổ sách</t>
         </is>
@@ -10085,7 +11583,8 @@
       </c>
       <c r="G258" s="3" t="inlineStr"/>
       <c r="H258" s="2" t="inlineStr"/>
-      <c r="I258" s="3" t="inlineStr">
+      <c r="I258" s="2" t="inlineStr"/>
+      <c r="J258" s="3" t="inlineStr">
         <is>
           <t>Vốn lưu động ròng, Chu kỳ chuyển đổi tiền mặt, Dòng tiền tự do cho doanh nghiệp</t>
         </is>
@@ -10118,7 +11617,8 @@
       </c>
       <c r="G259" s="3" t="inlineStr"/>
       <c r="H259" s="2" t="inlineStr"/>
-      <c r="I259" s="3" t="inlineStr">
+      <c r="I259" s="2" t="inlineStr"/>
+      <c r="J259" s="3" t="inlineStr">
         <is>
           <t>Nợ vay ròng trên EBITDA, Giá trị doanh nghiệp, Tỷ lệ nợ vay trên vốn chủ sở hữu, Hệ số thanh toán tiền mặt</t>
         </is>
@@ -10155,7 +11655,8 @@
       </c>
       <c r="G260" s="3" t="inlineStr"/>
       <c r="H260" s="2" t="inlineStr"/>
-      <c r="I260" s="3" t="inlineStr">
+      <c r="I260" s="2" t="inlineStr"/>
+      <c r="J260" s="3" t="inlineStr">
         <is>
           <t>Nợ vay ròng, Lợi nhuận trước lãi vay, thuế và khấu hao, Hệ số khả năng thanh toán lãi vay</t>
         </is>
@@ -10192,7 +11693,8 @@
       </c>
       <c r="G261" s="3" t="inlineStr"/>
       <c r="H261" s="2" t="inlineStr"/>
-      <c r="I261" s="3" t="inlineStr">
+      <c r="I261" s="2" t="inlineStr"/>
+      <c r="J261" s="3" t="inlineStr">
         <is>
           <t>Phần bù rủi ro thị trường, Lãi suất phi rủi ro, Chi phí vốn chủ sở hữu</t>
         </is>
@@ -10229,7 +11731,8 @@
       </c>
       <c r="G262" s="3" t="inlineStr"/>
       <c r="H262" s="2" t="inlineStr"/>
-      <c r="I262" s="3" t="inlineStr">
+      <c r="I262" s="2" t="inlineStr"/>
+      <c r="J262" s="3" t="inlineStr">
         <is>
           <t>Mô hình định giá tài sản vốn, Phần bù rủi ro quốc gia, Lãi suất phi rủi ro, Chi phí vốn chủ sở hữu</t>
         </is>
@@ -10270,7 +11773,12 @@
           <t>https://vi.wikipedia.org/wiki/Ph%C3%A2n_t%C3%ADch_%C4%91%E1%BB%99_nh%E1%BA%A1y</t>
         </is>
       </c>
-      <c r="I263" s="3" t="inlineStr">
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J263" s="3" t="inlineStr">
         <is>
           <t>Phân tích kịch bản, Mô hình chiết khấu dòng tiền, Tốc độ tăng trưởng dài hạn, Biên an toàn</t>
         </is>
@@ -10301,9 +11809,22 @@
           <t>Phương pháp tách ROE thành ba nhân tố để biết ROE đến từ đâu. Công thức: ROE = Biên lợi nhuận ròng × Vòng quay tổng tài sản × Hệ số đòn bẩy tài chính = (LNST / Doanh thu) × (Doanh thu / Tổng tài sản) × (Tổng tài sản / Vốn chủ sở hữu). Nhờ đó nhà phân tích phân biệt được ROE cao là nhờ sinh lời tốt, nhờ dùng tài sản hiệu quả hay chỉ nhờ vay nợ nhiều.</t>
         </is>
       </c>
-      <c r="G264" s="3" t="inlineStr"/>
-      <c r="H264" s="2" t="inlineStr"/>
-      <c r="I264" s="3" t="inlineStr">
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>Dupont analysis is a tool used in financial analysis, where return on equity (ROE) is separated into its component parts. Useful in several contexts, this "decomposition" of ROE allows financial managers to focus on the key metrics of financial performance individually, and thereby to identify strengths and weaknesses within the company that should be addressed. Similarly, it allows investors to compare the operational efficiency of two comparable firms.</t>
+        </is>
+      </c>
+      <c r="H264" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/DuPont_analysis</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J264" s="3" t="inlineStr">
         <is>
           <t>Tỷ suất lợi nhuận trên vốn chủ sở hữu, Biên lợi nhuận ròng, Vòng quay tổng tài sản, Hệ số đòn bẩy tài chính, Phân tích Dupont 5 thành phần</t>
         </is>
@@ -10336,7 +11857,8 @@
       </c>
       <c r="G265" s="3" t="inlineStr"/>
       <c r="H265" s="2" t="inlineStr"/>
-      <c r="I265" s="3" t="inlineStr">
+      <c r="I265" s="2" t="inlineStr"/>
+      <c r="J265" s="3" t="inlineStr">
         <is>
           <t>Phân tích Dupont, Lợi nhuận trước lãi vay và thuế, Tỷ suất lợi nhuận trên vốn chủ sở hữu, Hệ số đòn bẩy tài chính</t>
         </is>
@@ -10367,9 +11889,22 @@
           <t>Kỹ thuật xây dựng nhiều kịch bản (thường là cơ sở, lạc quan và bi quan) trong đó nhiều giả định như sản lượng, giá bán, chi phí, lãi suất thay đổi đồng thời và nhất quán với nhau. Mỗi kịch bản cho ra một giá trị định giá; có thể gán xác suất để tính Giá trị kỳ vọng = Σ (Xác suất × Giá trị kịch bản). Khác với phân tích độ nhạy, phân tích kịch bản phản ánh tốt hơn các tình huống thực tế như suy thoái ngành hay thay đổi chính sách.</t>
         </is>
       </c>
-      <c r="G266" s="3" t="inlineStr"/>
-      <c r="H266" s="2" t="inlineStr"/>
-      <c r="I266" s="3" t="inlineStr">
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>Scenario planning, scenario thinking, scenario analysis, scenario prediction and the scenario method all describe a strategic planning method that some organizations use to make flexible long-term plans. It is in large part an adaptation and generalization of classic methods used by military intelligence. In the most common application of the method, analysts generate simulation games for policy makers.</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Scenario_planning</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J266" s="3" t="inlineStr">
         <is>
           <t>Phân tích độ nhạy, Giá mục tiêu, Giá trị hợp lý</t>
         </is>
@@ -10402,7 +11937,8 @@
       </c>
       <c r="G267" s="3" t="inlineStr"/>
       <c r="H267" s="2" t="inlineStr"/>
-      <c r="I267" s="3" t="inlineStr">
+      <c r="I267" s="2" t="inlineStr"/>
+      <c r="J267" s="3" t="inlineStr">
         <is>
           <t>Phân tích theo chiều ngang, Biên lợi nhuận gộp, Phân tích tỷ số tài chính</t>
         </is>
@@ -10435,7 +11971,8 @@
       </c>
       <c r="G268" s="3" t="inlineStr"/>
       <c r="H268" s="2" t="inlineStr"/>
-      <c r="I268" s="3" t="inlineStr">
+      <c r="I268" s="2" t="inlineStr"/>
+      <c r="J268" s="3" t="inlineStr">
         <is>
           <t>Phân tích theo chiều dọc, Phân tích xu hướng, Tăng trưởng so với cùng kỳ năm trước</t>
         </is>
@@ -10476,7 +12013,12 @@
           <t>https://vi.wikipedia.org/wiki/Ph%C3%A2n_t%C3%ADch_t%C3%A0i_ch%C3%ADnh</t>
         </is>
       </c>
-      <c r="I269" s="3" t="inlineStr">
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J269" s="3" t="inlineStr">
         <is>
           <t>Phân tích Dupont, Phân tích theo chiều dọc, Định giá so sánh, Piotroski F-score</t>
         </is>
@@ -10507,9 +12049,22 @@
           <t>Phương pháp theo dõi diễn biến của một chỉ tiêu qua nhiều kỳ (thường 3–5 năm hoặc 8–12 quý) để nhận diện hướng đi dài hạn. Cách làm phổ biến là chọn một kỳ gốc bằng 100 và tính chỉ số xu hướng: Chỉ số kỳ t = Giá trị kỳ t / Giá trị kỳ gốc × 100. Phân tích xu hướng giúp tách biến động mang tính chu kỳ, mùa vụ khỏi những thay đổi mang tính cấu trúc.</t>
         </is>
       </c>
-      <c r="G270" s="3" t="inlineStr"/>
-      <c r="H270" s="2" t="inlineStr"/>
-      <c r="I270" s="3" t="inlineStr">
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>Trend analysis is the practice of collecting information and attempting to spot a pattern. In some fields of study, the term has more formally defined meanings. Although trend analysis is often used to predict future events, it could be used to estimate uncertain events in the past, such as how many ancient kings probably ruled between two dates, based on data such as the average years which other known kings reigned.</t>
+        </is>
+      </c>
+      <c r="H270" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Trend_analysis</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J270" s="3" t="inlineStr">
         <is>
           <t>Phân tích theo chiều ngang, Tốc độ tăng trưởng kép hàng năm, Tăng trưởng so với cùng kỳ năm trước</t>
         </is>
@@ -10544,9 +12099,22 @@
           <t>Bộ chấm điểm sức khỏe tài chính từ 0 đến 9 do Joseph Piotroski đề xuất năm 2000, gồm 9 tiêu chí nhị phân (đạt được 1 điểm, không đạt 0 điểm). Ba nhóm tiêu chí gồm: sinh lời (ROA dương, CFO dương, ROA tăng, CFO lớn hơn LNST); đòn bẩy, thanh khoản và nguồn vốn (tỷ lệ nợ dài hạn giảm, hệ số thanh toán hiện hành tăng, không phát hành thêm cổ phiếu); hiệu quả hoạt động (biên lợi nhuận gộp tăng, vòng quay tổng tài sản tăng). Điểm 8–9 cho thấy nền tảng tài chính mạnh, 0–2 là yếu; riêng tiêu chí không phát hành thêm cổ phiếu khá khắt khe với doanh nghiệp Việt Nam vốn thường xuyên tăng vốn.</t>
         </is>
       </c>
-      <c r="G271" s="3" t="inlineStr"/>
-      <c r="H271" s="2" t="inlineStr"/>
-      <c r="I271" s="3" t="inlineStr">
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>Piotroski F-score is a number between 0 and 9 which is used to assess strength of company's financial position. The score is used by financial investors in order to find the best value stocks (nine being the best). The score is named after Stanford accounting professor Joseph Piotroski.</t>
+        </is>
+      </c>
+      <c r="H271" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Piotroski_F-score</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J271" s="3" t="inlineStr">
         <is>
           <t>Altman Z-score, Beneish M-score, Tỷ suất lợi nhuận trên tổng tài sản, Tỷ lệ dòng tiền hoạt động trên lợi nhuận ròng</t>
         </is>
@@ -10581,9 +12149,22 @@
           <t>Tổng giá trị của một chỉ tiêu trong bốn quý tài chính gần nhất, giúp có số liệu cả năm luôn cập nhật mà không phải chờ BCTC năm. Công thức: Chỉ tiêu TTM = Tổng 4 quý gần nhất, hoặc = Số cả năm trước + Lũy kế năm nay − Lũy kế cùng kỳ năm trước. EPS TTM được dùng để tính P/E trượt; với chỉ tiêu thời điểm trên bảng cân đối kế toán, cần dùng số bình quân thay vì cộng dồn.</t>
         </is>
       </c>
-      <c r="G272" s="3" t="inlineStr"/>
-      <c r="H272" s="2" t="inlineStr"/>
-      <c r="I272" s="3" t="inlineStr">
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>Trailing twelve months (TTM) is a measurement of a company's financial performance (income and expenses) used in finance. It is measured by using the income statements from a company's reports (such as interim, quarterly or annual reports), to calculate the income for the twelve-month period immediately prior to the date of the report.</t>
+        </is>
+      </c>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Trailing_twelve_months</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J272" s="3" t="inlineStr">
         <is>
           <t>Hệ số giá trên thu nhập, Số liệu lũy kế, Thu nhập trên mỗi cổ phiếu</t>
         </is>
@@ -10618,9 +12199,22 @@
           <t>Giá trị cộng dồn của một chỉ tiêu từ đầu năm tài chính đến hết kỳ báo cáo. BCKQKD giữa niên độ theo VAS trình bày cả số liệu riêng của quý và cột lũy kế từ đầu năm, trong khi Báo cáo lưu chuyển tiền tệ quý thường chỉ có số lũy kế; muốn có dòng tiền riêng của một quý phải lấy lũy kế quý này trừ lũy kế quý trước. Số lũy kế thường được so với kế hoạch năm để đánh giá tiến độ thực hiện.</t>
         </is>
       </c>
-      <c r="G273" s="3" t="inlineStr"/>
-      <c r="H273" s="2" t="inlineStr"/>
-      <c r="I273" s="3" t="inlineStr">
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>Year-to-date (YTD) is the period starting from the beginning of the current year (either the calendar year or fiscal year) and continuing up to the present day.</t>
+        </is>
+      </c>
+      <c r="H273" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Year-to-date</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J273" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ hoàn thành kế hoạch, Số liệu bốn quý gần nhất, Tăng trưởng so với cùng kỳ năm trước</t>
         </is>
@@ -10657,7 +12251,8 @@
       </c>
       <c r="G274" s="3" t="inlineStr"/>
       <c r="H274" s="2" t="inlineStr"/>
-      <c r="I274" s="3" t="inlineStr">
+      <c r="I274" s="2" t="inlineStr"/>
+      <c r="J274" s="3" t="inlineStr">
         <is>
           <t>Vòng quay hàng tồn kho, Chu kỳ chuyển đổi tiền mặt, Kỳ thu tiền bình quân</t>
         </is>
@@ -10694,7 +12289,8 @@
       </c>
       <c r="G275" s="3" t="inlineStr"/>
       <c r="H275" s="2" t="inlineStr"/>
-      <c r="I275" s="3" t="inlineStr">
+      <c r="I275" s="2" t="inlineStr"/>
+      <c r="J275" s="3" t="inlineStr">
         <is>
           <t>Tăng trưởng so với quý trước, Số liệu lũy kế, Tốc độ tăng trưởng kép hàng năm</t>
         </is>
@@ -10731,7 +12327,8 @@
       </c>
       <c r="G276" s="3" t="inlineStr"/>
       <c r="H276" s="2" t="inlineStr"/>
-      <c r="I276" s="3" t="inlineStr">
+      <c r="I276" s="2" t="inlineStr"/>
+      <c r="J276" s="3" t="inlineStr">
         <is>
           <t>Tăng trưởng so với cùng kỳ năm trước, Số liệu lũy kế, Phân tích xu hướng</t>
         </is>
@@ -10766,9 +12363,22 @@
           <t>Phần lợi nhuận sau thuế phân bổ cho mỗi cổ phiếu phổ thông đang lưu hành. Công thức: EPS = (LNST thuộc cổ đông công ty mẹ − Trích quỹ khen thưởng, phúc lợi) / Số cổ phiếu phổ thông lưu hành bình quân gia quyền trong kỳ; việc trừ quỹ khen thưởng, phúc lợi là đặc thù theo hướng dẫn kế toán Việt Nam. EPS là mẫu số của P/E, và khi doanh nghiệp chia cổ tức bằng cổ phiếu, EPS các kỳ trước phải được điều chỉnh hồi tố để so sánh được.</t>
         </is>
       </c>
-      <c r="G277" s="3" t="inlineStr"/>
-      <c r="H277" s="2" t="inlineStr"/>
-      <c r="I277" s="3" t="inlineStr">
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>Tỉ suất thu nhập trên cổ phần hay gọi tắt là EPS (tiếng Anh: Earnings per Share) là chỉ số nói lên phần lợi nhuận thu được trên mỗi cổ phần. Đây cũng có thể coi như phần lợi nhuận thu được trên mỗi khoản đầu tư ban đầu, nên nó được coi như là chỉ số xác định khả năng lợi nhuận của một công ty (hay một dự án đầu tư).</t>
+        </is>
+      </c>
+      <c r="H277" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/T%E1%BB%89_su%E1%BA%A5t_l%E1%BB%A3i_nhu%E1%BA%ADn_tr%C3%AAn_c%E1%BB%95_ph%E1%BA%A7n</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J277" s="3" t="inlineStr">
         <is>
           <t>Thu nhập trên mỗi cổ phiếu pha loãng, Hệ số giá trên thu nhập, Tỷ lệ chi trả cổ tức, Giá trị sổ sách trên mỗi cổ phiếu</t>
         </is>
@@ -10803,9 +12413,22 @@
           <t>EPS được tính lại với giả định mọi công cụ có thể chuyển thành cổ phiếu phổ thông (trái phiếu chuyển đổi, quyền chọn ESOP, quyền mua cổ phiếu) đều đã được chuyển đổi. Công thức: EPS pha loãng = (LNST phân bổ cho cổ đông phổ thông + Chi phí lãi trái phiếu chuyển đổi sau thuế) / (Số cổ phiếu bình quân + Số cổ phiếu tiềm năng có tác động suy giảm). EPS pha loãng luôn nhỏ hơn hoặc bằng EPS cơ bản; chênh lệch lớn cho thấy rủi ro pha loãng quyền lợi cổ đông hiện hữu.</t>
         </is>
       </c>
-      <c r="G278" s="3" t="inlineStr"/>
-      <c r="H278" s="2" t="inlineStr"/>
-      <c r="I278" s="3" t="inlineStr">
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>Tỉ suất thu nhập trên cổ phần hay gọi tắt là EPS (tiếng Anh: Earnings per Share) là chỉ số nói lên phần lợi nhuận thu được trên mỗi cổ phần. Đây cũng có thể coi như phần lợi nhuận thu được trên mỗi khoản đầu tư ban đầu, nên nó được coi như là chỉ số xác định khả năng lợi nhuận của một công ty (hay một dự án đầu tư).</t>
+        </is>
+      </c>
+      <c r="H278" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/T%E1%BB%89_su%E1%BA%A5t_l%E1%BB%A3i_nhu%E1%BA%ADn_tr%C3%AAn_c%E1%BB%95_ph%E1%BA%A7n</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J278" s="3" t="inlineStr">
         <is>
           <t>Thu nhập trên mỗi cổ phiếu, Hệ số giá trên thu nhập</t>
         </is>
@@ -10840,9 +12463,22 @@
           <t>Tốc độ tăng trưởng tối đa doanh nghiệp có thể đạt được chỉ bằng lợi nhuận giữ lại, không phát hành thêm cổ phiếu và giữ nguyên cơ cấu vốn. Công thức: SGR = ROE × Tỷ lệ lợi nhuận giữ lại = ROE × (1 − Tỷ lệ chi trả cổ tức). Nếu kế hoạch tăng trưởng vượt xa SGR, doanh nghiệp sẽ phải vay thêm hoặc tăng vốn, điều rất thường thấy ở doanh nghiệp Việt Nam.</t>
         </is>
       </c>
-      <c r="G279" s="3" t="inlineStr"/>
-      <c r="H279" s="2" t="inlineStr"/>
-      <c r="I279" s="3" t="inlineStr">
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>Tỷ số tăng trưởng bền vững, hay còn được viết tắt là SGR (tiếng Anh: Sustainable Growth Rate) là một tỷ số tài chính để đánh giá khả năng tăng trưởng của vốn chủ sở hữu thông qua tích lũy lợi nhuận.</t>
+        </is>
+      </c>
+      <c r="H279" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_s%E1%BB%91_t%C4%83ng_tr%C6%B0%E1%BB%9Fng_b%E1%BB%81n_v%E1%BB%AFng</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J279" s="3" t="inlineStr">
         <is>
           <t>Tỷ suất lợi nhuận trên vốn chủ sở hữu, Tỷ lệ lợi nhuận giữ lại, Tỷ lệ chi trả cổ tức, Tốc độ tăng trưởng dài hạn</t>
         </is>
@@ -10879,7 +12515,8 @@
       </c>
       <c r="G280" s="3" t="inlineStr"/>
       <c r="H280" s="2" t="inlineStr"/>
-      <c r="I280" s="3" t="inlineStr">
+      <c r="I280" s="2" t="inlineStr"/>
+      <c r="J280" s="3" t="inlineStr">
         <is>
           <t>Giá trị cuối kỳ, Mô hình Gordon, Tốc độ tăng trưởng bền vững, Phân tích độ nhạy</t>
         </is>
@@ -10914,9 +12551,22 @@
           <t>Tốc độ tăng trưởng bình quân mỗi năm với giả định tăng trưởng đều theo lãi kép trong suốt một giai đoạn. Công thức: CAGR = (Giá trị cuối kỳ / Giá trị đầu kỳ)^(1/n) − 1, với n là số năm. CAGR làm mượt biến động từng năm nên tiện để so sánh, nhưng không tính được khi giá trị đầu kỳ âm và có thể che giấu những năm tăng trưởng âm.</t>
         </is>
       </c>
-      <c r="G281" s="3" t="inlineStr"/>
-      <c r="H281" s="2" t="inlineStr"/>
-      <c r="I281" s="3" t="inlineStr">
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>Tốc độ tăng trưởng hằng năm kép (thuật ngữ tiếng Anh: Compounded Annual Growth rate, viết tắt CAGR) là một thuật ngữ kinh doanh và đầu tư cụ thể cho thu nhập đầu tư thường niên hóa trơn tru trong một thời kỳ nhất định. CAGR không phải là một thuật ngữ kế toán, nhưng vẫn được sử dụng rộng rãi, đặc biệt trong các ngành công nghiệp tăng trưởng hoặc để so sánh tốc độ tăng trưởng của hai khoản đầu tư bởi vì CAGR là làm suy giảm ảnh hưởng của biến động của các hoàn vốn định kỳ có thể làm cho các ý nghĩa số học là không thích hợp.</t>
+        </is>
+      </c>
+      <c r="H281" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_l%E1%BB%87_t%C4%83ng_tr%C6%B0%E1%BB%9Fng_h%C3%A0ng_n%C4%83m_k%C3%A9p</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J281" s="3" t="inlineStr">
         <is>
           <t>Phân tích xu hướng, Tăng trưởng so với cùng kỳ năm trước, Hệ số PEG</t>
         </is>
@@ -10947,9 +12597,22 @@
           <t>Tỷ lệ lợi nhuận sau thuế được chia cho cổ đông dưới dạng cổ tức tiền mặt. Công thức: Tỷ lệ chi trả cổ tức = Cổ tức tiền mặt / LNST thuộc cổ đông công ty mẹ = DPS / EPS. Ở Việt Nam cổ tức thường được công bố theo % mệnh giá 10.000 đồng (ví dụ 20% tương ứng 2.000 đồng/cổ phiếu), còn cổ tức bằng cổ phiếu không làm giảm tiền nên thường không tính vào tỷ lệ này.</t>
         </is>
       </c>
-      <c r="G282" s="3" t="inlineStr"/>
-      <c r="H282" s="2" t="inlineStr"/>
-      <c r="I282" s="3" t="inlineStr">
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>The dividend payout ratio is the fraction of net income a firm pays to its stockholders in dividends: Dividend payout ratio = Dividends Net Income for the same period {\textstyle {\mbox{Dividend payout ratio}}={\frac {\mbox{Dividends}}{\mbox{Net Income for the same period}}}} The part of earnings not paid to investors is left for investment to provide for future earnings growth. Investors seeking high current income and limited capital growth prefer companies with a high dividend payout ratio.</t>
+        </is>
+      </c>
+      <c r="H282" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Dividend_payout_ratio</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J282" s="3" t="inlineStr">
         <is>
           <t>Tỷ suất cổ tức, Tỷ lệ lợi nhuận giữ lại, Mô hình chiết khấu cổ tức, Thu nhập trên mỗi cổ phiếu</t>
         </is>
@@ -10982,7 +12645,8 @@
       </c>
       <c r="G283" s="3" t="inlineStr"/>
       <c r="H283" s="2" t="inlineStr"/>
-      <c r="I283" s="3" t="inlineStr">
+      <c r="I283" s="2" t="inlineStr"/>
+      <c r="J283" s="3" t="inlineStr">
         <is>
           <t>Chất lượng lợi nhuận, Tỷ lệ dòng tiền hoạt động trên lợi nhuận ròng, Beneish M-score</t>
         </is>
@@ -11019,7 +12683,8 @@
       </c>
       <c r="G284" s="3" t="inlineStr"/>
       <c r="H284" s="2" t="inlineStr"/>
-      <c r="I284" s="3" t="inlineStr">
+      <c r="I284" s="2" t="inlineStr"/>
+      <c r="J284" s="3" t="inlineStr">
         <is>
           <t>Chất lượng lợi nhuận, Tỷ lệ dồn tích, Dòng tiền tự do, Piotroski F-score</t>
         </is>
@@ -11052,7 +12717,8 @@
       </c>
       <c r="G285" s="3" t="inlineStr"/>
       <c r="H285" s="2" t="inlineStr"/>
-      <c r="I285" s="3" t="inlineStr">
+      <c r="I285" s="2" t="inlineStr"/>
+      <c r="J285" s="3" t="inlineStr">
         <is>
           <t>Số liệu lũy kế, Hệ số P/E dự phóng, Tăng trưởng so với cùng kỳ năm trước</t>
         </is>
@@ -11083,9 +12749,22 @@
           <t>Phần lợi nhuận sau thuế được giữ lại để tái đầu tư thay vì chi trả cổ tức tiền mặt. Công thức: Tỷ lệ lợi nhuận giữ lại = (LNST − Cổ tức tiền mặt) / LNST = 1 − Tỷ lệ chi trả cổ tức. Tỷ lệ giữ lại cao chỉ có lợi cho cổ đông khi doanh nghiệp tái đầu tư được với ROE cao hơn chi phí vốn chủ sở hữu.</t>
         </is>
       </c>
-      <c r="G286" s="3" t="inlineStr"/>
-      <c r="H286" s="2" t="inlineStr"/>
-      <c r="I286" s="3" t="inlineStr">
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>In corporate finance, the retention ratio indicates the percentage of a company's earnings that are not paid out in dividends to shareholders but credited to retained earnings. It is the opposite of the dividend payout ratio, and is a key indicator of how much profit a company is keeping to fund its operations, growth, and development.</t>
+        </is>
+      </c>
+      <c r="H286" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Retention_ratio</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J286" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ chi trả cổ tức, Tốc độ tăng trưởng bền vững, Chi phí vốn chủ sở hữu</t>
         </is>
@@ -11116,9 +12795,22 @@
           <t>Tỷ trọng tài sản được tài trợ bằng nợ phải trả. Công thức: Tỷ lệ nợ trên tổng tài sản = Nợ phải trả / Tổng tài sản. Hệ số cao cho thấy rủi ro tài chính lớn, nhưng mức hợp lý khác nhau giữa các ngành: ngân hàng thường trên 90%, bất động sản cao do khoản người mua trả tiền trước, còn doanh nghiệp tiêu dùng thường thấp.</t>
         </is>
       </c>
-      <c r="G287" s="3" t="inlineStr"/>
-      <c r="H287" s="2" t="inlineStr"/>
-      <c r="I287" s="3" t="inlineStr">
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>Tỷ số nợ trên tài sản (hay Tỷ lệ nợ trên tài sản, Tỷ số nợ trên tổng tài sản, Tỷ số nợ D/A) là một tỷ số tài chính đo lường năng lực sử dụng và quản lý nợ của doanh nghiệp.</t>
+        </is>
+      </c>
+      <c r="H287" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_s%E1%BB%91_n%E1%BB%A3_tr%C3%AAn_t%C3%A0i_s%E1%BA%A3n</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J287" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ nợ trên vốn chủ sở hữu, Hệ số đòn bẩy tài chính, Altman Z-score</t>
         </is>
@@ -11163,7 +12855,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_s%E1%BB%91_n%E1%BB%A3_tr%C3%AAn_v%E1%BB%91n_ch%E1%BB%A7_s%E1%BB%9F_h%E1%BB%AFu</t>
         </is>
       </c>
-      <c r="I288" s="3" t="inlineStr">
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J288" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ nợ vay trên vốn chủ sở hữu, Tỷ lệ nợ trên tổng tài sản, Hệ số đòn bẩy tài chính</t>
         </is>
@@ -11196,7 +12893,8 @@
       </c>
       <c r="G289" s="3" t="inlineStr"/>
       <c r="H289" s="2" t="inlineStr"/>
-      <c r="I289" s="3" t="inlineStr">
+      <c r="I289" s="2" t="inlineStr"/>
+      <c r="J289" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ nợ trên vốn chủ sở hữu, Nợ vay ròng, Hệ số khả năng thanh toán lãi vay</t>
         </is>
@@ -11227,9 +12925,22 @@
           <t>Mức lợi suất tiền mặt nhà đầu tư nhận được từ cổ tức so với giá cổ phiếu đang giao dịch. Công thức: Tỷ suất cổ tức = Cổ tức tiền mặt mỗi cổ phiếu (DPS) / Giá thị trường × 100%. Cần phân biệt với tỷ lệ cổ tức theo mệnh giá mà doanh nghiệp Việt Nam hay công bố: cổ tức 20% mệnh giá (2.000 đồng) trên cổ phiếu giá 40.000 đồng chỉ tương ứng tỷ suất cổ tức 5%.</t>
         </is>
       </c>
-      <c r="G290" s="3" t="inlineStr"/>
-      <c r="H290" s="2" t="inlineStr"/>
-      <c r="I290" s="3" t="inlineStr">
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>The dividend yield of a share is the ratio of annualised cash dividends to the share's current market price. It is usually expressed as a percentage and is commonly calculated by dividing the annual dividend per share by the current share price. Closely related measures compare dividends to price and are often referred to as the dividend–price ratio. At the company level, the same idea can be expressed as total annual dividends divided by the company’s market capitalisation, assuming the number of shares remains unchanged.</t>
+        </is>
+      </c>
+      <c r="H290" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Dividend_yield</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J290" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ chi trả cổ tức, Mô hình Gordon, Mô hình chiết khấu cổ tức</t>
         </is>
@@ -11274,7 +12985,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_s%E1%BB%91_l%E1%BB%A3i_nhu%E1%BA%ADn_tr%C3%AAn_t%C3%A0i_s%E1%BA%A3n</t>
         </is>
       </c>
-      <c r="I291" s="3" t="inlineStr">
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J291" s="3" t="inlineStr">
         <is>
           <t>Tỷ suất lợi nhuận trên vốn chủ sở hữu, Vòng quay tổng tài sản, Biên lợi nhuận ròng, Phân tích Dupont</t>
         </is>
@@ -11319,7 +13035,12 @@
           <t>https://vi.wikipedia.org/wiki/L%E1%BB%A3i_nhu%E1%BA%ADn_tr%C3%AAn_v%E1%BB%91n</t>
         </is>
       </c>
-      <c r="I292" s="3" t="inlineStr">
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J292" s="3" t="inlineStr">
         <is>
           <t>Tỷ suất lợi nhuận trên tổng tài sản, Phân tích Dupont, Hệ số đòn bẩy tài chính, Tốc độ tăng trưởng bền vững</t>
         </is>
@@ -11354,9 +13075,22 @@
           <t>Đo hiệu quả sinh lời trên toàn bộ vốn đầu tư vào hoạt động kinh doanh cốt lõi, gồm cả vốn chủ và nợ vay. Công thức: ROIC = NOPAT / Vốn đầu tư bình quân, trong đó Vốn đầu tư = Vốn chủ sở hữu + Nợ vay − Tiền và đầu tư tài chính ngắn hạn. Doanh nghiệp chỉ thực sự tạo ra giá trị cho cổ đông khi ROIC lớn hơn WACC một cách bền vững.</t>
         </is>
       </c>
-      <c r="G293" s="3" t="inlineStr"/>
-      <c r="H293" s="2" t="inlineStr"/>
-      <c r="I293" s="3" t="inlineStr">
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>Return on capital (ROC), or return on invested capital (ROIC), is a ratio used in finance, valuation and accounting, as a measure of the profitability and value-creating potential of companies relative to the amount of capital invested by shareholders and other debtholders. It indicates how effective a company is at turning capital into profits. The ratio is calculated by dividing the after tax operating income (NOPAT) by the average book-value of the invested capital (IC).</t>
+        </is>
+      </c>
+      <c r="H293" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Return_on_capital</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J293" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận hoạt động thuần sau thuế, Chi phí vốn bình quân gia quyền, Giá trị kinh tế gia tăng, Tỷ suất lợi nhuận trên vốn sử dụng</t>
         </is>
@@ -11391,9 +13125,22 @@
           <t>Đo lợi nhuận trước lãi vay và thuế tạo ra trên mỗi đồng vốn dài hạn được sử dụng. Công thức: ROCE = EBIT / Vốn sử dụng, với Vốn sử dụng = Tổng tài sản − Nợ ngắn hạn (hoặc Vốn chủ sở hữu + Nợ dài hạn). Chỉ số hữu ích để so sánh các doanh nghiệp thâm dụng vốn như thép, điện, xi măng có cấu trúc vốn khác nhau.</t>
         </is>
       </c>
-      <c r="G294" s="3" t="inlineStr"/>
-      <c r="H294" s="2" t="inlineStr"/>
-      <c r="I294" s="3" t="inlineStr">
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>Return on capital employed is an accounting ratio used in finance, valuation, and accounting. It is a useful measure for comparing the relative profitability of companies after taking into account the amount of capital used.</t>
+        </is>
+      </c>
+      <c r="H294" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Return_on_capital_employed</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J294" s="3" t="inlineStr">
         <is>
           <t>Tỷ suất lợi nhuận trên vốn đầu tư, Lợi nhuận trước lãi vay và thuế, Tỷ suất lợi nhuận trên vốn chủ sở hữu</t>
         </is>
@@ -11434,7 +13181,12 @@
           <t>https://vi.wikipedia.org/wiki/V%E1%BB%91n_l%C6%B0u_%C4%91%E1%BB%99ng</t>
         </is>
       </c>
-      <c r="I295" s="3" t="inlineStr">
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J295" s="3" t="inlineStr">
         <is>
           <t>Vốn lưu động ròng, Nhu cầu vốn lưu động, Chu kỳ chuyển đổi tiền mặt</t>
         </is>
@@ -11469,9 +13221,22 @@
           <t>Phần chênh lệch giữa tài sản ngắn hạn và nợ ngắn hạn, cũng chính là phần nguồn vốn dài hạn dùng để tài trợ cho tài sản ngắn hạn. Công thức: Vốn lưu động ròng = Tài sản ngắn hạn − Nợ ngắn hạn = (Vốn chủ sở hữu + Nợ dài hạn) − Tài sản dài hạn. Vốn lưu động ròng âm cho thấy doanh nghiệp đang dùng nợ ngắn hạn để tài trợ tài sản dài hạn, một dấu hiệu mất cân đối kỳ hạn cần lưu ý.</t>
         </is>
       </c>
-      <c r="G296" s="3" t="inlineStr"/>
-      <c r="H296" s="2" t="inlineStr"/>
-      <c r="I296" s="3" t="inlineStr">
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>Vốn lưu động (thuật ngữ tiếng Anh: Working capital, viết tắt WC) là một thước đo tài chính đại diện cho thanh khoản vận hành có sẵn cho một doanh nghiệp, tổ chức hoặc thực thể khác, bao gồm cả cơ quan chính phủ. Cùng với các tài sản cố định như nhà máy và thiết bị, vốn lưu động được coi là một phần của vốn hoạt động. Vốn lưu động được tính như tài sản hiện tại trừ nợ ngắn hạn. Nó là một nguồn gốc của vốn lưu động, thường được sử dụng trong các kỹ thuật định giá như DCFS (các dòng tiền chiết khấu).</t>
+        </is>
+      </c>
+      <c r="H296" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/V%E1%BB%91n_l%C6%B0u_%C4%91%E1%BB%99ng</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J296" s="3" t="inlineStr">
         <is>
           <t>Vốn lưu động, Hệ số thanh toán hiện hành, Nhu cầu vốn lưu động, Altman Z-score</t>
         </is>
@@ -11502,9 +13267,22 @@
           <t>Cho biết hàng tồn kho quay vòng bao nhiêu lần trong kỳ. Công thức: Vòng quay hàng tồn kho = Giá vốn hàng bán / Hàng tồn kho bình quân. Vòng quay cao thể hiện hàng bán nhanh, ít ứ đọng vốn; vòng quay giảm liên tục có thể báo hiệu sức mua yếu hoặc rủi ro phải trích lập dự phòng giảm giá hàng tồn kho.</t>
         </is>
       </c>
-      <c r="G297" s="3" t="inlineStr"/>
-      <c r="H297" s="2" t="inlineStr"/>
-      <c r="I297" s="3" t="inlineStr">
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>Số vòng quay hàng tồn kho (hay Hệ số quay vòng của hàng tồn kho) là một trong những tỷ số tài chính để đánh giá hiệu quả hoạt động của doanh nghiệp. Tỷ số này được tính ra bằng cách lấy doanh thu (hoặc giá vốn hàng bán) trong một kỳ nhất định chia cho bình quân giá trị hàng tồn kho trong cùng kỳ. Ở đây, bình quân giá trị hàng tồn kho bằng trung bình cộng của giá trị đầu kỳ và giá trị cuối kỳ. Tỷ số cho biết hàng tồn kho quay bao nhiêu vòng trong kỳ để tạo ra số doanh thu được ghi nhận trong kỳ đó. Tỷ số càng cao có thể là dấu hiệu doanh nghiệp hoạt động có hiệu quả.</t>
+        </is>
+      </c>
+      <c r="H297" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/S%E1%BB%91_v%C3%B2ng_quay_h%C3%A0ng_t%E1%BB%93n_kho</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J297" s="3" t="inlineStr">
         <is>
           <t>Số ngày tồn kho bình quân, Chu kỳ chuyển đổi tiền mặt, Hệ số thanh toán nhanh</t>
         </is>
@@ -11537,7 +13315,8 @@
       </c>
       <c r="G298" s="3" t="inlineStr"/>
       <c r="H298" s="2" t="inlineStr"/>
-      <c r="I298" s="3" t="inlineStr">
+      <c r="I298" s="2" t="inlineStr"/>
+      <c r="J298" s="3" t="inlineStr">
         <is>
           <t>Kỳ thu tiền bình quân, Chất lượng lợi nhuận, Beneish M-score</t>
         </is>
@@ -11570,7 +13349,8 @@
       </c>
       <c r="G299" s="3" t="inlineStr"/>
       <c r="H299" s="2" t="inlineStr"/>
-      <c r="I299" s="3" t="inlineStr">
+      <c r="I299" s="2" t="inlineStr"/>
+      <c r="J299" s="3" t="inlineStr">
         <is>
           <t>Kỳ trả tiền bình quân, Chu kỳ chuyển đổi tiền mặt, Nhu cầu vốn lưu động</t>
         </is>
@@ -11601,9 +13381,22 @@
           <t>Đo hiệu quả sử dụng tài sản cố định trong việc tạo ra doanh thu. Công thức: Vòng quay TSCĐ = Doanh thu thuần / Giá trị còn lại TSCĐ bình quân. Chỉ số tăng cho thấy nhà máy, thiết bị được khai thác tốt hơn; chỉ số giảm mạnh thường xảy ra ngay sau khi doanh nghiệp đưa dự án lớn vào hoạt động nhưng chưa chạy hết công suất.</t>
         </is>
       </c>
-      <c r="G300" s="3" t="inlineStr"/>
-      <c r="H300" s="2" t="inlineStr"/>
-      <c r="I300" s="3" t="inlineStr">
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>Số vòng quay tài sản cố định (Hệ số quay vòng tài sản cố định) là một trong những tỷ số tài chính đánh giá khái quát hiệu quả sử dụng tài sản, ở đây là tài sản cố định, của doanh nghiệp. Thước đo này được tính bằng cách lấy doanh thu của doanh nghiệp đạt được trong một kỳ nào đó chia cho giá trị bình quân tài sản cố định thuần (ròng) của doanh nghiệp trong kỳ đó. Giá trị bình quân này được tính bằng cách lấy giá trị trung bình cộng của giá trị đầu kỳ và giá trị cuối kỳ.</t>
+        </is>
+      </c>
+      <c r="H300" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/S%E1%BB%91_v%C3%B2ng_quay_t%C3%A0i_s%E1%BA%A3n_c%E1%BB%91_%C4%91%E1%BB%8Bnh</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J300" s="3" t="inlineStr">
         <is>
           <t>Vòng quay tổng tài sản, Chi tiêu vốn, Độ lớn đòn bẩy hoạt động</t>
         </is>
@@ -11634,9 +13427,22 @@
           <t>Cho biết mỗi đồng tài sản tạo ra bao nhiêu đồng doanh thu, phản ánh hiệu quả khai thác tài sản. Công thức: Vòng quay tổng tài sản = Doanh thu thuần / Tổng tài sản bình quân. Bán lẻ, phân phối thường có vòng quay cao (trên 2 lần), trong khi điện, bất động sản, hạ tầng thường dưới 0,5 lần; đây là thành phần thứ hai của phân tích Dupont.</t>
         </is>
       </c>
-      <c r="G301" s="3" t="inlineStr"/>
-      <c r="H301" s="2" t="inlineStr"/>
-      <c r="I301" s="3" t="inlineStr">
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>Số vòng quay tổng tài sản (hay gọi tắt là Số vòng quay tài sản) là một tỷ số tài chính, là thước đo khái quát nhất hiệu quả sử dụng tài sản của doanh nghiệp. Tỷ số này được tính ra bằng cách lấy doanh thu thuần (ròng) đạt được trong một thời kỳ nhất định chia cho giá trị bình quân tổng tài sản (bao gồm cả tài sản lưu động lẫn tài sản cố định) của doanh nghiệp trong cũng kỳ đó. Giá trị bình quân tính bằng trung bình cộng của giá trị đầu kỳ và giá trị cuối kỳ. Tỷ số này cho biết mỗi đồng tài sản tạo ra cho doanh nghiệp bao nhiêu đồng doanh thu.</t>
+        </is>
+      </c>
+      <c r="H301" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/S%E1%BB%91_v%C3%B2ng_quay_t%E1%BB%95ng_t%C3%A0i_s%E1%BA%A3n</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J301" s="3" t="inlineStr">
         <is>
           <t>Phân tích Dupont, Vòng quay tài sản cố định, Tỷ suất lợi nhuận trên tổng tài sản</t>
         </is>
@@ -11677,7 +13483,12 @@
           <t>https://vi.wikipedia.org/wiki/Bancassurance</t>
         </is>
       </c>
-      <c r="I302" s="3" t="inlineStr">
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J302" s="3" t="inlineStr">
         <is>
           <t>Thu nhập ngoài lãi, Lãi thuần từ hoạt động dịch vụ</t>
         </is>
@@ -11708,9 +13519,22 @@
           <t>Cơ chế bảo vệ người gửi tiền khi tổ chức tín dụng mất khả năng chi trả, do Bảo hiểm tiền gửi Việt Nam (DIV) thực hiện. Theo Quyết định 32/2021/QĐ-TTg, hạn mức chi trả tối đa là 125 triệu đồng cho mỗi người tại một tổ chức tham gia bảo hiểm tiền gửi.</t>
         </is>
       </c>
-      <c r="G303" s="3" t="inlineStr"/>
-      <c r="H303" s="2" t="inlineStr"/>
-      <c r="I303" s="3" t="inlineStr">
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>Deposit insurance, deposit protection or deposit guarantee is a measure implemented in many countries to protect bank depositors, in full or in part, from losses caused by a bank's inability to pay its debts when due. Deposit insurance or deposit guarantee systems are one component of a financial system safety net that promotes financial stability, and are typically integrated with bank regulation and supervision.</t>
+        </is>
+      </c>
+      <c r="H303" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Deposit_insurance</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J303" s="3" t="inlineStr">
         <is>
           <t>Tổ chức tín dụng, Tiền gửi có kỳ hạn</t>
         </is>
@@ -11741,9 +13565,22 @@
           <t>Cam kết của ngân hàng thực hiện nghĩa vụ tài chính thay khách hàng nếu khách hàng không thực hiện đúng cam kết với bên nhận bảo lãnh (như bảo lãnh dự thầu, thực hiện hợp đồng, thanh toán). Ngân hàng thu phí bảo lãnh và theo dõi khoản này ngoại bảng.</t>
         </is>
       </c>
-      <c r="G304" s="3" t="inlineStr"/>
-      <c r="H304" s="2" t="inlineStr"/>
-      <c r="I304" s="3" t="inlineStr">
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>A bank guarantee is a kind of guarantee from a lending organization. The bank guarantee also signifies that the lending institution ensures that the liabilities of a debtor are going to be met. In other words, if the debtor fails to perform the obligation, the bank will cover it. A bank guarantee allows the customer, or debtor, to acquire goods, purchase equipment or draw down a loan. A bank guarantee is a promise from a bank or other lending institution that if a particular borrower defaults, the bank will cover the loss. A bank guarantee is similar to, but not the same as a letter of credit.</t>
+        </is>
+      </c>
+      <c r="H304" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bank_guarantee</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J304" s="3" t="inlineStr">
         <is>
           <t>Cấp tín dụng, Lãi thuần từ hoạt động dịch vụ, Thư tín dụng</t>
         </is>
@@ -11784,7 +13621,12 @@
           <t>https://vi.wikipedia.org/wiki/Basel_II</t>
         </is>
       </c>
-      <c r="I305" s="3" t="inlineStr">
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J305" s="3" t="inlineStr">
         <is>
           <t>Hiệp ước Basel, Basel III, Hệ số an toàn vốn</t>
         </is>
@@ -11815,9 +13657,22 @@
           <t>Bộ chuẩn mực ra đời sau khủng hoảng tài chính 2008, nâng chất lượng và số lượng vốn (đặc biệt vốn cấp 1), bổ sung bộ đệm vốn, tỷ lệ đòn bẩy và hai chuẩn thanh khoản LCR, NSFR. Một số ngân hàng Việt Nam như VCB, TCB, VIB, ACB đã chủ động áp dụng sớm.</t>
         </is>
       </c>
-      <c r="G306" s="3" t="inlineStr"/>
-      <c r="H306" s="2" t="inlineStr"/>
-      <c r="I306" s="3" t="inlineStr">
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>Basel III is a framework published by the Basel Committee on Banking Supervision (BCBS) in response to the deficiencies in financial regulation revealed by the 2008 financial crisis. It sets international standards and recommendations for bank capital requirements, stress tests, liquidity regulations, and leverage, with the goal of mitigating the risk of bank runs and bank failures. Basel III builds upon the standards of Basel II, introduced in 2004, and Basel I, introduced in 1988.</t>
+        </is>
+      </c>
+      <c r="H306" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Basel_III</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J306" s="3" t="inlineStr">
         <is>
           <t>Basel II, Tỷ lệ khả năng chi trả, Tỷ lệ nguồn vốn ổn định ròng</t>
         </is>
@@ -11852,9 +13707,22 @@
           <t>Chỉ số đo khả năng sinh lãi từ hoạt động tín dụng: NIM = Thu nhập lãi thuần / Tài sản sinh lãi bình quân. NIM của các ngân hàng Việt Nam thường khoảng 2,5–4,5%; NIM cao cho thấy ngân hàng có nguồn vốn rẻ (CASA cao) hoặc cho vay với lãi suất cao.</t>
         </is>
       </c>
-      <c r="G307" s="3" t="inlineStr"/>
-      <c r="H307" s="2" t="inlineStr"/>
-      <c r="I307" s="3" t="inlineStr">
+      <c r="G307" s="3" t="inlineStr">
+        <is>
+          <t>Net interest margin (NIM) is a measure of the difference between the interest income generated by banks or other financial institutions and the amount of interest paid out to their lenders (for example, deposits), relative to the amount of their (interest-earning) assets. It is similar to the gross margin (or gross profit margin) of non-financial companies.</t>
+        </is>
+      </c>
+      <c r="H307" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Net_interest_margin</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J307" s="3" t="inlineStr">
         <is>
           <t>Thu nhập lãi thuần, Tài sản sinh lãi, Chi phí vốn huy động, Tỷ lệ tiền gửi không kỳ hạn</t>
         </is>
@@ -11887,7 +13755,8 @@
       </c>
       <c r="G308" s="3" t="inlineStr"/>
       <c r="H308" s="2" t="inlineStr"/>
-      <c r="I308" s="3" t="inlineStr">
+      <c r="I308" s="2" t="inlineStr"/>
+      <c r="J308" s="3" t="inlineStr">
         <is>
           <t>Cho vay khách hàng, Bảo lãnh ngân hàng, Giới hạn cấp tín dụng</t>
         </is>
@@ -11918,9 +13787,22 @@
           <t>Phương pháp đánh giá khả năng trả nợ của khách hàng bằng điểm số dựa trên thu nhập, lịch sử vay trả, tài sản và các dữ liệu khác. Ngân hàng dùng điểm tín dụng (kết hợp dữ liệu từ CIC) để quyết định cho vay, hạn mức và lãi suất.</t>
         </is>
       </c>
-      <c r="G309" s="3" t="inlineStr"/>
-      <c r="H309" s="2" t="inlineStr"/>
-      <c r="I309" s="3" t="inlineStr">
+      <c r="G309" s="3" t="inlineStr">
+        <is>
+          <t>A credit score is a numerical expression based on a level analysis of a person's credit files, to represent the creditworthiness of an individual. A credit score is primarily based on a credit report, information typically sourced from credit bureaus. Lenders, such as banks and credit card companies, use credit scores to evaluate the potential risk posed by lending money to consumers and to mitigate losses due to bad debt. Lenders use credit scores to determine who qualifies for a loan, at what interest rate, and what credit limits.</t>
+        </is>
+      </c>
+      <c r="H309" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Credit_score</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J309" s="3" t="inlineStr">
         <is>
           <t>Trung tâm Thông tin tín dụng Quốc gia, Cho vay tín chấp, Rủi ro tín dụng</t>
         </is>
@@ -11953,7 +13835,8 @@
       </c>
       <c r="G310" s="3" t="inlineStr"/>
       <c r="H310" s="2" t="inlineStr"/>
-      <c r="I310" s="3" t="inlineStr">
+      <c r="I310" s="2" t="inlineStr"/>
+      <c r="J310" s="3" t="inlineStr">
         <is>
           <t>Lãi suất cho vay, Lãi suất huy động, Biên lãi ròng</t>
         </is>
@@ -11986,7 +13869,8 @@
       </c>
       <c r="G311" s="3" t="inlineStr"/>
       <c r="H311" s="2" t="inlineStr"/>
-      <c r="I311" s="3" t="inlineStr">
+      <c r="I311" s="2" t="inlineStr"/>
+      <c r="J311" s="3" t="inlineStr">
         <is>
           <t>Dự phòng cụ thể, Dự phòng chung, Chi phí tín dụng, Nợ xấu</t>
         </is>
@@ -12023,7 +13907,8 @@
       </c>
       <c r="G312" s="3" t="inlineStr"/>
       <c r="H312" s="2" t="inlineStr"/>
-      <c r="I312" s="3" t="inlineStr">
+      <c r="I312" s="2" t="inlineStr"/>
+      <c r="J312" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ chi phí trên thu nhập, Lợi nhuận trước dự phòng</t>
         </is>
@@ -12056,7 +13941,8 @@
       </c>
       <c r="G313" s="3" t="inlineStr"/>
       <c r="H313" s="2" t="inlineStr"/>
-      <c r="I313" s="3" t="inlineStr">
+      <c r="I313" s="2" t="inlineStr"/>
+      <c r="J313" s="3" t="inlineStr">
         <is>
           <t>Chi phí dự phòng rủi ro tín dụng, Dư nợ tín dụng, Nợ xấu</t>
         </is>
@@ -12093,7 +13979,8 @@
       </c>
       <c r="G314" s="3" t="inlineStr"/>
       <c r="H314" s="2" t="inlineStr"/>
-      <c r="I314" s="3" t="inlineStr">
+      <c r="I314" s="2" t="inlineStr"/>
+      <c r="J314" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ tiền gửi không kỳ hạn, Lãi suất huy động, Biên lãi ròng</t>
         </is>
@@ -12126,7 +14013,8 @@
       </c>
       <c r="G315" s="3" t="inlineStr"/>
       <c r="H315" s="2" t="inlineStr"/>
-      <c r="I315" s="3" t="inlineStr">
+      <c r="I315" s="2" t="inlineStr"/>
+      <c r="J315" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng bán lẻ, Cho vay tiêu dùng, Cho vay doanh nghiệp</t>
         </is>
@@ -12159,7 +14047,8 @@
       </c>
       <c r="G316" s="3" t="inlineStr"/>
       <c r="H316" s="2" t="inlineStr"/>
-      <c r="I316" s="3" t="inlineStr">
+      <c r="I316" s="2" t="inlineStr"/>
+      <c r="J316" s="3" t="inlineStr">
         <is>
           <t>Rủi ro tập trung tín dụng, Tài sản có rủi ro, Nợ xấu</t>
         </is>
@@ -12192,7 +14081,8 @@
       </c>
       <c r="G317" s="3" t="inlineStr"/>
       <c r="H317" s="2" t="inlineStr"/>
-      <c r="I317" s="3" t="inlineStr">
+      <c r="I317" s="2" t="inlineStr"/>
+      <c r="J317" s="3" t="inlineStr">
         <is>
           <t>Tài sản bảo đảm, Phát mại tài sản bảo đảm, Cho vay tín chấp</t>
         </is>
@@ -12225,7 +14115,8 @@
       </c>
       <c r="G318" s="3" t="inlineStr"/>
       <c r="H318" s="2" t="inlineStr"/>
-      <c r="I318" s="3" t="inlineStr">
+      <c r="I318" s="2" t="inlineStr"/>
+      <c r="J318" s="3" t="inlineStr">
         <is>
           <t>Cho vay bán lẻ, Rủi ro tập trung tín dụng, Hạn mức tín dụng</t>
         </is>
@@ -12258,7 +14149,8 @@
       </c>
       <c r="G319" s="3" t="inlineStr"/>
       <c r="H319" s="2" t="inlineStr"/>
-      <c r="I319" s="3" t="inlineStr">
+      <c r="I319" s="2" t="inlineStr"/>
+      <c r="J319" s="3" t="inlineStr">
         <is>
           <t>Dư nợ tín dụng, Tăng trưởng tín dụng, Nợ xấu</t>
         </is>
@@ -12289,9 +14181,22 @@
           <t>Cho vay cá nhân để mua sắm hàng hóa, dịch vụ phục vụ đời sống (điện thoại, xe máy, du lịch, học phí), thường không cần tài sản bảo đảm. Lãi suất cao bù cho rủi ro nợ xấu cao; mảng này chủ yếu do các công ty tài chính thực hiện.</t>
         </is>
       </c>
-      <c r="G320" s="3" t="inlineStr"/>
-      <c r="H320" s="2" t="inlineStr"/>
-      <c r="I320" s="3" t="inlineStr">
+      <c r="G320" s="3" t="inlineStr">
+        <is>
+          <t>Tín dụng là khái niệm thể hiện mối quan hệ giữa người cho vay và người vay. Tín dụng ra đời, tồn tại qua nhiều hình thái kinh tế - xã hội. Quan hệ tín dụng được phát sinh ngay từ thời kỳ chế độ công xã nguyên thủy bắt đầu tan rã. Khi chế độ tư hữu về tư liệu sản xuất xuất hiện, cũng là đồng thời xuất hiện quan hệ trao đổi hàng hóa. Thời kỳ này, tín dụng được thực hiện dưới hình thức vay mượn bằng hiện vật - hàng hóa.</t>
+        </is>
+      </c>
+      <c r="H320" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/T%C3%ADn_d%E1%BB%A5ng</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J320" s="3" t="inlineStr">
         <is>
           <t>Công ty tài chính, Cho vay tín chấp, Cho vay bán lẻ</t>
         </is>
@@ -12324,7 +14229,8 @@
       </c>
       <c r="G321" s="3" t="inlineStr"/>
       <c r="H321" s="2" t="inlineStr"/>
-      <c r="I321" s="3" t="inlineStr">
+      <c r="I321" s="2" t="inlineStr"/>
+      <c r="J321" s="3" t="inlineStr">
         <is>
           <t>Cho vay tiêu dùng, Chấm điểm tín dụng, Cho vay có tài sản bảo đảm</t>
         </is>
@@ -12369,7 +14275,12 @@
           <t>https://vi.wikipedia.org/wiki/Ch%E1%BB%A9ng_ch%E1%BB%89_ti%E1%BB%81n_g%E1%BB%ADi</t>
         </is>
       </c>
-      <c r="I322" s="3" t="inlineStr">
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J322" s="3" t="inlineStr">
         <is>
           <t>Phát hành giấy tờ có giá, Vốn huy động</t>
         </is>
@@ -12400,9 +14311,22 @@
           <t>Việc ngân hàng điều chỉnh kỳ hạn trả nợ hoặc gia hạn nợ cho khách hàng gặp khó khăn tạm thời. Theo các chính sách hỗ trợ như Thông tư 02/2023/TT-NHNN, ngân hàng được cơ cấu lại và giữ nguyên nhóm nợ trong một thời gian, giúp giảm áp lực nợ xấu và dự phòng.</t>
         </is>
       </c>
-      <c r="G323" s="3" t="inlineStr"/>
-      <c r="H323" s="2" t="inlineStr"/>
-      <c r="I323" s="3" t="inlineStr">
+      <c r="G323" s="3" t="inlineStr">
+        <is>
+          <t>Debt rescheduling is the lengthening of the time of debt repayment by restructuring the terms of an existing loan.</t>
+        </is>
+      </c>
+      <c r="H323" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Debt_rescheduling</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J323" s="3" t="inlineStr">
         <is>
           <t>Nợ xấu tiềm ẩn, Nợ quá hạn, Phân loại nợ</t>
         </is>
@@ -12439,7 +14363,8 @@
       </c>
       <c r="G324" s="3" t="inlineStr"/>
       <c r="H324" s="2" t="inlineStr"/>
-      <c r="I324" s="3" t="inlineStr">
+      <c r="I324" s="2" t="inlineStr"/>
+      <c r="J324" s="3" t="inlineStr">
         <is>
           <t>Trái phiếu đặc biệt VAMC, Nợ xấu</t>
         </is>
@@ -12470,9 +14395,22 @@
           <t>Tổ chức tín dụng phi ngân hàng, không được nhận tiền gửi không kỳ hạn từ cá nhân, chủ yếu cho vay tiêu dùng tín chấp với lãi suất cao. Ví dụ FE Credit (thuộc VPBank), HD Saison (thuộc HDBank).</t>
         </is>
       </c>
-      <c r="G325" s="3" t="inlineStr"/>
-      <c r="H325" s="2" t="inlineStr"/>
-      <c r="I325" s="3" t="inlineStr">
+      <c r="G325" s="3" t="inlineStr">
+        <is>
+          <t>Trong kinh tế học tài chính, tổ chức tài chính hay định chế tài chính là tổ chức có chức năng cung cấp các dịch vụ tài chính cho các khách hàng hoặc các thành viên. Có lẽ dịch vụ tài chính quan trọng nhất mà các tổ chức tài chính cung cấp là hoạt động như các trung gian tài chính. Phần lớn các tổ chức tài chính được đặt dưới sự kiểm soát chặt chẽ của nhà nước.</t>
+        </is>
+      </c>
+      <c r="H325" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/T%E1%BB%95_ch%E1%BB%A9c_t%C3%A0i_ch%C3%ADnh</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J325" s="3" t="inlineStr">
         <is>
           <t>Tổ chức tín dụng, Cho vay tiêu dùng, Cho vay tín chấp</t>
         </is>
@@ -12507,9 +14445,22 @@
           <t>Cơ chế ngân hàng “mua” vốn từ bộ phận huy động và “bán” vốn cho bộ phận cho vay theo một giá nội bộ. FTP giúp đo lợi nhuận của từng chi nhánh, sản phẩm và tách rủi ro lãi suất, thanh khoản về hội sở quản lý tập trung.</t>
         </is>
       </c>
-      <c r="G326" s="3" t="inlineStr"/>
-      <c r="H326" s="2" t="inlineStr"/>
-      <c r="I326" s="3" t="inlineStr">
+      <c r="G326" s="3" t="inlineStr">
+        <is>
+          <t>The Fund Transfer Pricing (FTP) measures the contribution by each source of funding to the overall profitability in a financial institution. Funds that go toward lending products are charged to asset-generating businesses whereas funds generated by deposit and other funding products are credited to liability-generating businesses.</t>
+        </is>
+      </c>
+      <c r="H326" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Funds_transfer_pricing</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J326" s="3" t="inlineStr">
         <is>
           <t>Rủi ro lãi suất, Rủi ro thanh khoản, Chi phí vốn huy động</t>
         </is>
@@ -12542,7 +14493,8 @@
       </c>
       <c r="G327" s="3" t="inlineStr"/>
       <c r="H327" s="2" t="inlineStr"/>
-      <c r="I327" s="3" t="inlineStr">
+      <c r="I327" s="2" t="inlineStr"/>
+      <c r="J327" s="3" t="inlineStr">
         <is>
           <t>Cho vay khách hàng, Tăng trưởng tín dụng, Hạn mức tăng trưởng tín dụng</t>
         </is>
@@ -12575,7 +14527,8 @@
       </c>
       <c r="G328" s="3" t="inlineStr"/>
       <c r="H328" s="2" t="inlineStr"/>
-      <c r="I328" s="3" t="inlineStr">
+      <c r="I328" s="2" t="inlineStr"/>
+      <c r="J328" s="3" t="inlineStr">
         <is>
           <t>Dự phòng cụ thể, Tỷ lệ bao phủ nợ xấu, Chi phí dự phòng rủi ro tín dụng</t>
         </is>
@@ -12608,7 +14561,8 @@
       </c>
       <c r="G329" s="3" t="inlineStr"/>
       <c r="H329" s="2" t="inlineStr"/>
-      <c r="I329" s="3" t="inlineStr">
+      <c r="I329" s="2" t="inlineStr"/>
+      <c r="J329" s="3" t="inlineStr">
         <is>
           <t>Phân loại nợ, Dự phòng chung, Tài sản bảo đảm</t>
         </is>
@@ -12641,7 +14595,8 @@
       </c>
       <c r="G330" s="3" t="inlineStr"/>
       <c r="H330" s="2" t="inlineStr"/>
-      <c r="I330" s="3" t="inlineStr">
+      <c r="I330" s="2" t="inlineStr"/>
+      <c r="J330" s="3" t="inlineStr">
         <is>
           <t>Rủi ro tập trung tín dụng, Vốn tự có, Cấp tín dụng</t>
         </is>
@@ -12682,7 +14637,12 @@
           <t>https://vi.wikipedia.org/wiki/H%E1%BA%A1n_m%E1%BB%A9c_t%C3%ADn_d%E1%BB%A5ng</t>
         </is>
       </c>
-      <c r="I331" s="3" t="inlineStr">
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J331" s="3" t="inlineStr">
         <is>
           <t>Cho vay doanh nghiệp, Cấp tín dụng</t>
         </is>
@@ -12717,9 +14677,22 @@
           <t>CAR = Vốn tự có / Tổng tài sản có rủi ro (gồm rủi ro tín dụng, thị trường, hoạt động). Theo Thông tư 41/2016/TT-NHNN (chuẩn Basel II), ngân hàng thương mại phải duy trì CAR tối thiểu 8%; CAR càng cao thì bộ đệm vốn chống đỡ tổn thất càng dày.</t>
         </is>
       </c>
-      <c r="G332" s="3" t="inlineStr"/>
-      <c r="H332" s="2" t="inlineStr"/>
-      <c r="I332" s="3" t="inlineStr">
+      <c r="G332" s="3" t="inlineStr">
+        <is>
+          <t>Capital Adequacy Ratio (CAR) also known as Capital to Risk (Weighted) Assets Ratio (CRAR), is the ratio of a bank's capital to its risk-weighted assets (or credit exposure). National regulators track a bank's CAR and ensure it complies with statutory capital requirements to verify it can absorb a reasonable amount of loss (default of loans) without collapsing. The enforcement of regulated levels of this CAR is intended to protect depositors and promote stability and efficiency of financial systems around the world.</t>
+        </is>
+      </c>
+      <c r="H332" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Capital_adequacy_ratio</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J332" s="3" t="inlineStr">
         <is>
           <t>Vốn tự có, Tài sản có rủi ro, Basel II</t>
         </is>
@@ -12750,9 +14723,22 @@
           <t>Bộ chuẩn mực quốc tế về quản trị rủi ro và an toàn vốn ngân hàng do Ủy ban Basel về Giám sát Ngân hàng (BCBS, đặt tại BIS) ban hành, gồm Basel I (1988), Basel II (2004) và Basel III (2010). Việt Nam áp dụng dần qua các thông tư của NHNN.</t>
         </is>
       </c>
-      <c r="G333" s="3" t="inlineStr"/>
-      <c r="H333" s="2" t="inlineStr"/>
-      <c r="I333" s="3" t="inlineStr">
+      <c r="G333" s="3" t="inlineStr">
+        <is>
+          <t>Ủy ban Basel về Giám sát Ngân hàng (BCBS) là một ủy ban giám sát ngân hàng được thành lập bởi thống đốc ngân hàng trung ương của G-10 vào năm 1974.</t>
+        </is>
+      </c>
+      <c r="H333" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/%E1%BB%A6y_ban_Basel_v%E1%BB%81_Gi%C3%A1m_s%C3%A1t_Ng%C3%A2n_h%C3%A0ng</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J333" s="3" t="inlineStr">
         <is>
           <t>Basel II, Basel III, Hệ số an toàn vốn</t>
         </is>
@@ -12785,7 +14771,8 @@
       </c>
       <c r="G334" s="3" t="inlineStr"/>
       <c r="H334" s="2" t="inlineStr"/>
-      <c r="I334" s="3" t="inlineStr">
+      <c r="I334" s="2" t="inlineStr"/>
+      <c r="J334" s="3" t="inlineStr">
         <is>
           <t>Chi phí dự phòng rủi ro tín dụng, Dự phòng cụ thể</t>
         </is>
@@ -12818,7 +14805,8 @@
       </c>
       <c r="G335" s="3" t="inlineStr"/>
       <c r="H335" s="2" t="inlineStr"/>
-      <c r="I335" s="3" t="inlineStr">
+      <c r="I335" s="2" t="inlineStr"/>
+      <c r="J335" s="3" t="inlineStr">
         <is>
           <t>Rủi ro lãi suất, Tài sản sinh lãi</t>
         </is>
@@ -12851,7 +14839,8 @@
       </c>
       <c r="G336" s="3" t="inlineStr"/>
       <c r="H336" s="2" t="inlineStr"/>
-      <c r="I336" s="3" t="inlineStr">
+      <c r="I336" s="2" t="inlineStr"/>
+      <c r="J336" s="3" t="inlineStr">
         <is>
           <t>Lãi suất huy động, Biên lãi ròng, Lãi suất thả nổi</t>
         </is>
@@ -12884,7 +14873,8 @@
       </c>
       <c r="G337" s="3" t="inlineStr"/>
       <c r="H337" s="2" t="inlineStr"/>
-      <c r="I337" s="3" t="inlineStr">
+      <c r="I337" s="2" t="inlineStr"/>
+      <c r="J337" s="3" t="inlineStr">
         <is>
           <t>Lãi suất cho vay, Chi phí vốn huy động, Tiền gửi có kỳ hạn</t>
         </is>
@@ -12915,9 +14905,22 @@
           <t>Lãi suất các ngân hàng áp dụng khi vay mượn lẫn nhau trên thị trường liên ngân hàng; lãi suất bình quân liên ngân hàng VND được NHNN công bố hằng ngày. Lãi suất qua đêm tăng vọt thường là dấu hiệu hệ thống đang thiếu thanh khoản.</t>
         </is>
       </c>
-      <c r="G338" s="3" t="inlineStr"/>
-      <c r="H338" s="2" t="inlineStr"/>
-      <c r="I338" s="3" t="inlineStr">
+      <c r="G338" s="3" t="inlineStr">
+        <is>
+          <t>The interbank lending market is a market in which banks lend funds to one another for a specified term. Most interbank loans are for maturities of one week or less, the majority being overnight. Such loans are made at the interbank rate (also called the overnight rate if the term of the loan is overnight). A sharp decline in transaction volume in this market was a major contributing factor to the collapse of several financial institutions during the 2008 financial crisis.</t>
+        </is>
+      </c>
+      <c r="H338" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Interbank_lending_market</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J338" s="3" t="inlineStr">
         <is>
           <t>Thị trường liên ngân hàng, Lãi suất điều hành, Lãi suất huy động</t>
         </is>
@@ -12948,9 +14951,22 @@
           <t>Lãi suất cho vay được điều chỉnh định kỳ (thường 3 hoặc 6 tháng) theo lãi suất cơ sở cộng một biên độ cố định, lãi suất cơ sở thường là bình quân lãi suất tiết kiệm 12 hoặc 13 tháng của một nhóm ngân hàng. Các khoản vay mua nhà dài hạn thường có lãi suất ưu đãi cố định vài năm đầu rồi chuyển sang thả nổi.</t>
         </is>
       </c>
-      <c r="G339" s="3" t="inlineStr"/>
-      <c r="H339" s="2" t="inlineStr"/>
-      <c r="I339" s="3" t="inlineStr">
+      <c r="G339" s="3" t="inlineStr">
+        <is>
+          <t>A floating interest rate, also known as a variable or adjustable rate, refers to any type of debt instrument, such as a loan, bond, mortgage, or credit, that does not have a fixed rate of interest over the life of the instrument. Floating interest rates typically change based on a reference rate (a benchmark of any financial factor, such as the Consumer Price Index). One of the most common reference rates to use as the basis for applying floating interest rates is the Secure Overnight Financing Rate, or SOFR.</t>
+        </is>
+      </c>
+      <c r="H339" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Floating_interest_rate</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J339" s="3" t="inlineStr">
         <is>
           <t>Lãi suất cho vay, Lãi suất huy động, Rủi ro lãi suất</t>
         </is>
@@ -12983,7 +14999,8 @@
       </c>
       <c r="G340" s="3" t="inlineStr"/>
       <c r="H340" s="2" t="inlineStr"/>
-      <c r="I340" s="3" t="inlineStr">
+      <c r="I340" s="2" t="inlineStr"/>
+      <c r="J340" s="3" t="inlineStr">
         <is>
           <t>Thu nhập ngoài lãi, Rủi ro lãi suất</t>
         </is>
@@ -13016,7 +15033,8 @@
       </c>
       <c r="G341" s="3" t="inlineStr"/>
       <c r="H341" s="2" t="inlineStr"/>
-      <c r="I341" s="3" t="inlineStr">
+      <c r="I341" s="2" t="inlineStr"/>
+      <c r="J341" s="3" t="inlineStr">
         <is>
           <t>Thu nhập ngoài lãi, Bancassurance, Bảo lãnh ngân hàng</t>
         </is>
@@ -13049,7 +15067,8 @@
       </c>
       <c r="G342" s="3" t="inlineStr"/>
       <c r="H342" s="2" t="inlineStr"/>
-      <c r="I342" s="3" t="inlineStr">
+      <c r="I342" s="2" t="inlineStr"/>
+      <c r="J342" s="3" t="inlineStr">
         <is>
           <t>Thu nhập ngoài lãi, Rủi ro thị trường</t>
         </is>
@@ -13086,7 +15105,8 @@
       </c>
       <c r="G343" s="3" t="inlineStr"/>
       <c r="H343" s="2" t="inlineStr"/>
-      <c r="I343" s="3" t="inlineStr">
+      <c r="I343" s="2" t="inlineStr"/>
+      <c r="J343" s="3" t="inlineStr">
         <is>
           <t>Tổng thu nhập hoạt động, Chi phí dự phòng rủi ro tín dụng, Chi phí hoạt động ngân hàng</t>
         </is>
@@ -13123,7 +15143,8 @@
       </c>
       <c r="G344" s="3" t="inlineStr"/>
       <c r="H344" s="2" t="inlineStr"/>
-      <c r="I344" s="3" t="inlineStr">
+      <c r="I344" s="2" t="inlineStr"/>
+      <c r="J344" s="3" t="inlineStr">
         <is>
           <t>Tài sản sinh lãi, Chi phí vốn huy động, Biên lãi ròng</t>
         </is>
@@ -13164,7 +15185,12 @@
           <t>https://vi.wikipedia.org/wiki/Ng%C3%A2n_h%C3%A0ng_b%C3%A1n_l%E1%BA%BB</t>
         </is>
       </c>
-      <c r="I345" s="3" t="inlineStr">
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J345" s="3" t="inlineStr">
         <is>
           <t>Cho vay bán lẻ, Cho vay tiêu dùng, Ngân hàng số</t>
         </is>
@@ -13195,9 +15221,22 @@
           <t>Mô hình cung cấp dịch vụ ngân hàng chủ yếu qua kênh điện tử (ứng dụng di động, internet banking), từ mở tài khoản định danh điện tử (eKYC) đến vay vốn trực tuyến. Ngân hàng số giúp giảm chi phí vận hành, tăng tỷ lệ CASA và thu phí dịch vụ.</t>
         </is>
       </c>
-      <c r="G346" s="3" t="inlineStr"/>
-      <c r="H346" s="2" t="inlineStr"/>
-      <c r="I346" s="3" t="inlineStr">
+      <c r="G346" s="3" t="inlineStr">
+        <is>
+          <t>Digital banking is part of the broader context for the move to online banking, where banking services are delivered over the internet. The shift from traditional to digital banking has been gradual, remains ongoing, and is constituted by differing degrees of banking service digitization. Digital banking involves high levels of process automation and web-based services and may include APIs enabling cross-institutional service composition to deliver banking products and provide transactions. It provides the ability for users to access financial data through desktop, mobile and ATM services.</t>
+        </is>
+      </c>
+      <c r="H346" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Digital_banking</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J346" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ tiền gửi không kỳ hạn, Lãi thuần từ hoạt động dịch vụ, Tỷ lệ chi phí trên thu nhập</t>
         </is>
@@ -13242,7 +15281,12 @@
           <t>https://vi.wikipedia.org/wiki/Ng%C3%A2n_h%C3%A0ng_th%C6%B0%C6%A1ng_m%E1%BA%A1i</t>
         </is>
       </c>
-      <c r="I347" s="3" t="inlineStr">
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J347" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng thương mại nhà nước, Ngân hàng thương mại cổ phần, Tổ chức tín dụng</t>
         </is>
@@ -13287,7 +15331,12 @@
           <t>https://vi.wikipedia.org/wiki/Ng%C3%A2n_h%C3%A0ng_th%C6%B0%C6%A1ng_m%E1%BA%A1i_c%E1%BB%95_ph%E1%BA%A7n</t>
         </is>
       </c>
-      <c r="I348" s="3" t="inlineStr">
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J348" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng thương mại, Ngân hàng thương mại nhà nước</t>
         </is>
@@ -13320,7 +15369,8 @@
       </c>
       <c r="G349" s="3" t="inlineStr"/>
       <c r="H349" s="2" t="inlineStr"/>
-      <c r="I349" s="3" t="inlineStr">
+      <c r="I349" s="2" t="inlineStr"/>
+      <c r="J349" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng thương mại, Ngân hàng thương mại cổ phần</t>
         </is>
@@ -13353,7 +15403,8 @@
       </c>
       <c r="G350" s="3" t="inlineStr"/>
       <c r="H350" s="2" t="inlineStr"/>
-      <c r="I350" s="3" t="inlineStr">
+      <c r="I350" s="2" t="inlineStr"/>
+      <c r="J350" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ nợ nhóm 2, Nợ dưới tiêu chuẩn, Phân loại nợ</t>
         </is>
@@ -13386,7 +15437,8 @@
       </c>
       <c r="G351" s="3" t="inlineStr"/>
       <c r="H351" s="2" t="inlineStr"/>
-      <c r="I351" s="3" t="inlineStr">
+      <c r="I351" s="2" t="inlineStr"/>
+      <c r="J351" s="3" t="inlineStr">
         <is>
           <t>Nợ xấu, Xóa nợ ngoại bảng, Dự phòng cụ thể</t>
         </is>
@@ -13419,7 +15471,8 @@
       </c>
       <c r="G352" s="3" t="inlineStr"/>
       <c r="H352" s="2" t="inlineStr"/>
-      <c r="I352" s="3" t="inlineStr">
+      <c r="I352" s="2" t="inlineStr"/>
+      <c r="J352" s="3" t="inlineStr">
         <is>
           <t>Phân loại nợ, Nợ cần chú ý</t>
         </is>
@@ -13452,7 +15505,8 @@
       </c>
       <c r="G353" s="3" t="inlineStr"/>
       <c r="H353" s="2" t="inlineStr"/>
-      <c r="I353" s="3" t="inlineStr">
+      <c r="I353" s="2" t="inlineStr"/>
+      <c r="J353" s="3" t="inlineStr">
         <is>
           <t>Nợ xấu, Nợ nghi ngờ, Phân loại nợ</t>
         </is>
@@ -13485,7 +15539,8 @@
       </c>
       <c r="G354" s="3" t="inlineStr"/>
       <c r="H354" s="2" t="inlineStr"/>
-      <c r="I354" s="3" t="inlineStr">
+      <c r="I354" s="2" t="inlineStr"/>
+      <c r="J354" s="3" t="inlineStr">
         <is>
           <t>Nợ xấu, Nợ có khả năng mất vốn, Phân loại nợ</t>
         </is>
@@ -13518,7 +15573,8 @@
       </c>
       <c r="G355" s="3" t="inlineStr"/>
       <c r="H355" s="2" t="inlineStr"/>
-      <c r="I355" s="3" t="inlineStr">
+      <c r="I355" s="2" t="inlineStr"/>
+      <c r="J355" s="3" t="inlineStr">
         <is>
           <t>Phân loại nợ, Nợ xấu, Cơ cấu lại thời hạn trả nợ</t>
         </is>
@@ -13551,7 +15607,8 @@
       </c>
       <c r="G356" s="3" t="inlineStr"/>
       <c r="H356" s="2" t="inlineStr"/>
-      <c r="I356" s="3" t="inlineStr">
+      <c r="I356" s="2" t="inlineStr"/>
+      <c r="J356" s="3" t="inlineStr">
         <is>
           <t>Cơ cấu lại thời hạn trả nợ, Nợ xấu tiềm ẩn, Phân loại nợ</t>
         </is>
@@ -13596,7 +15653,12 @@
           <t>https://vi.wikipedia.org/wiki/N%E1%BB%A3_x%E1%BA%A5u</t>
         </is>
       </c>
-      <c r="I357" s="3" t="inlineStr">
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J357" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ nợ xấu, Phân loại nợ, Tỷ lệ bao phủ nợ xấu</t>
         </is>
@@ -13629,7 +15691,8 @@
       </c>
       <c r="G358" s="3" t="inlineStr"/>
       <c r="H358" s="2" t="inlineStr"/>
-      <c r="I358" s="3" t="inlineStr">
+      <c r="I358" s="2" t="inlineStr"/>
+      <c r="J358" s="3" t="inlineStr">
         <is>
           <t>Nợ cần chú ý, Cơ cấu lại thời hạn trả nợ, Trái phiếu đặc biệt VAMC</t>
         </is>
@@ -13662,7 +15725,8 @@
       </c>
       <c r="G359" s="3" t="inlineStr"/>
       <c r="H359" s="2" t="inlineStr"/>
-      <c r="I359" s="3" t="inlineStr">
+      <c r="I359" s="2" t="inlineStr"/>
+      <c r="J359" s="3" t="inlineStr">
         <is>
           <t>Nợ đủ tiêu chuẩn, Nợ cần chú ý, Nợ dưới tiêu chuẩn, Dự phòng cụ thể</t>
         </is>
@@ -13695,7 +15759,8 @@
       </c>
       <c r="G360" s="3" t="inlineStr"/>
       <c r="H360" s="2" t="inlineStr"/>
-      <c r="I360" s="3" t="inlineStr">
+      <c r="I360" s="2" t="inlineStr"/>
+      <c r="J360" s="3" t="inlineStr">
         <is>
           <t>Chứng chỉ tiền gửi, Vốn cấp 2, Vốn huy động</t>
         </is>
@@ -13728,7 +15793,8 @@
       </c>
       <c r="G361" s="3" t="inlineStr"/>
       <c r="H361" s="2" t="inlineStr"/>
-      <c r="I361" s="3" t="inlineStr">
+      <c r="I361" s="2" t="inlineStr"/>
+      <c r="J361" s="3" t="inlineStr">
         <is>
           <t>Tài sản bảo đảm, Nợ xấu, Thu hồi nợ đã xử lý</t>
         </is>
@@ -13759,9 +15825,22 @@
           <t>Rủi ro tổn thất do quy trình nội bộ không đầy đủ hoặc sai sót, do con người, hệ thống hoặc sự kiện bên ngoài (gian lận, lỗi công nghệ, thiên tai). Theo Basel II, ngân hàng phải giữ vốn cho cả rủi ro hoạt động.</t>
         </is>
       </c>
-      <c r="G362" s="3" t="inlineStr"/>
-      <c r="H362" s="2" t="inlineStr"/>
-      <c r="I362" s="3" t="inlineStr">
+      <c r="G362" s="3" t="inlineStr">
+        <is>
+          <t>Operational risk is the risk of losses caused by flawed or failed processes, policies, systems or events that disrupt business operations. Employee errors, criminal activity such as fraud, and physical events are among the factors that can trigger operational risk. The process to manage operational risk is known as operational risk management.</t>
+        </is>
+      </c>
+      <c r="H362" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Operational_risk</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J362" s="3" t="inlineStr">
         <is>
           <t>Tài sản có rủi ro, Basel II, Rủi ro thị trường</t>
         </is>
@@ -13792,9 +15871,22 @@
           <t>Rủi ro thu nhập hoặc giá trị tài sản của ngân hàng bị ảnh hưởng khi lãi suất thị trường thay đổi, do kỳ hạn định lại lãi suất của tài sản và nợ không khớp nhau. Ví dụ ngân hàng huy động ngắn hạn nhưng cho vay lãi suất cố định dài hạn sẽ thiệt khi lãi suất huy động tăng.</t>
         </is>
       </c>
-      <c r="G363" s="3" t="inlineStr"/>
-      <c r="H363" s="2" t="inlineStr"/>
-      <c r="I363" s="3" t="inlineStr">
+      <c r="G363" s="3" t="inlineStr">
+        <is>
+          <t>Interest rate risk refers to the potential for financial loss due to fluctuations in interest rates. It will, in turn, impact differently re market risk, i.e. impacting instruments such as Bonds, re banks and re insurers.</t>
+        </is>
+      </c>
+      <c r="H363" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Interest_rate_risk</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J363" s="3" t="inlineStr">
         <is>
           <t>Khe hở nhạy cảm lãi suất, Định giá điều chuyển vốn nội bộ, Rủi ro thị trường</t>
         </is>
@@ -13827,7 +15919,8 @@
       </c>
       <c r="G364" s="3" t="inlineStr"/>
       <c r="H364" s="2" t="inlineStr"/>
-      <c r="I364" s="3" t="inlineStr">
+      <c r="I364" s="2" t="inlineStr"/>
+      <c r="J364" s="3" t="inlineStr">
         <is>
           <t>Giới hạn cấp tín dụng, Rủi ro tín dụng, Cho vay bất động sản</t>
         </is>
@@ -13868,7 +15961,12 @@
           <t>https://vi.wikipedia.org/wiki/R%E1%BB%A7i_ro_thanh_kho%E1%BA%A3n</t>
         </is>
       </c>
-      <c r="I365" s="3" t="inlineStr">
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J365" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ khả năng chi trả, Tỷ lệ dự trữ thanh khoản, Tỷ lệ cho vay trên tiền gửi</t>
         </is>
@@ -13899,9 +15997,22 @@
           <t>Rủi ro tổn thất do biến động của lãi suất, tỷ giá, giá chứng khoán và giá hàng hóa ảnh hưởng đến giá trị các trạng thái ngân hàng nắm giữ, chủ yếu trên sổ kinh doanh.</t>
         </is>
       </c>
-      <c r="G366" s="3" t="inlineStr"/>
-      <c r="H366" s="2" t="inlineStr"/>
-      <c r="I366" s="3" t="inlineStr">
+      <c r="G366" s="3" t="inlineStr">
+        <is>
+          <t>Market risk is the risk of losses in positions arising from movements in market variables like prices and volatility. There is no unique classification as each classification may refer to different aspects of market risk. Nevertheless, the most commonly used types of market risk are: Equity risk, the risk that stock or stock indices (e.g. Euro Stoxx 50, etc.) prices or their implied volatility will change. Interest rate risk, the risk that interest rates (e.g. Libor, Euribor, etc.) or their implied volatility will change. Currency risk, the risk that foreign exchange rates (e.g.</t>
+        </is>
+      </c>
+      <c r="H366" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Market_risk</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J366" s="3" t="inlineStr">
         <is>
           <t>Rủi ro hoạt động, Tài sản có rủi ro, Lãi thuần từ kinh doanh ngoại hối</t>
         </is>
@@ -13942,7 +16053,12 @@
           <t>https://vi.wikipedia.org/wiki/R%E1%BB%A7i_ro_t%C3%ADn_d%E1%BB%A5ng</t>
         </is>
       </c>
-      <c r="I367" s="3" t="inlineStr">
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J367" s="3" t="inlineStr">
         <is>
           <t>Nợ xấu, Chấm điểm tín dụng, Tài sản có rủi ro</t>
         </is>
@@ -13983,7 +16099,12 @@
           <t>https://vi.wikipedia.org/wiki/T%C3%A0i_s%E1%BA%A3n_%C4%91%E1%BA%A3m_b%E1%BA%A3o</t>
         </is>
       </c>
-      <c r="I368" s="3" t="inlineStr">
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J368" s="3" t="inlineStr">
         <is>
           <t>Cho vay có tài sản bảo đảm, Phát mại tài sản bảo đảm, Dự phòng cụ thể</t>
         </is>
@@ -14018,9 +16139,22 @@
           <t>Tổng tài sản của ngân hàng sau khi nhân với hệ số rủi ro tương ứng (ví dụ tiền mặt 0%, cho vay mua nhà có thế chấp hệ số thấp hơn cho vay bất động sản kinh doanh), cộng thêm phần vốn yêu cầu cho rủi ro thị trường và rủi ro hoạt động quy đổi. RWA là mẫu số của hệ số CAR.</t>
         </is>
       </c>
-      <c r="G369" s="3" t="inlineStr"/>
-      <c r="H369" s="2" t="inlineStr"/>
-      <c r="I369" s="3" t="inlineStr">
+      <c r="G369" s="3" t="inlineStr">
+        <is>
+          <t>Risk-weighted asset (RWA) is a bank's assets which includes retained tranches or off-balance-sheet exposures, weighted according to risk. This sort of asset calculation is used in determining the capital requirement or Capital Adequacy Ratio (CAR) for a financial institution.</t>
+        </is>
+      </c>
+      <c r="H369" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Risk-weighted_asset</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J369" s="3" t="inlineStr">
         <is>
           <t>Hệ số an toàn vốn, Rủi ro tín dụng, Rủi ro hoạt động</t>
         </is>
@@ -14053,7 +16187,8 @@
       </c>
       <c r="G370" s="3" t="inlineStr"/>
       <c r="H370" s="2" t="inlineStr"/>
-      <c r="I370" s="3" t="inlineStr">
+      <c r="I370" s="2" t="inlineStr"/>
+      <c r="J370" s="3" t="inlineStr">
         <is>
           <t>Biên lãi ròng, Lợi suất tài sản sinh lãi, Cho vay khách hàng</t>
         </is>
@@ -14086,7 +16221,8 @@
       </c>
       <c r="G371" s="3" t="inlineStr"/>
       <c r="H371" s="2" t="inlineStr"/>
-      <c r="I371" s="3" t="inlineStr">
+      <c r="I371" s="2" t="inlineStr"/>
+      <c r="J371" s="3" t="inlineStr">
         <is>
           <t>Hạn mức tăng trưởng tín dụng, Dư nợ tín dụng, Tổ chức tín dụng</t>
         </is>
@@ -14119,7 +16255,8 @@
       </c>
       <c r="G372" s="3" t="inlineStr"/>
       <c r="H372" s="2" t="inlineStr"/>
-      <c r="I372" s="3" t="inlineStr">
+      <c r="I372" s="2" t="inlineStr"/>
+      <c r="J372" s="3" t="inlineStr">
         <is>
           <t>Lãi suất liên ngân hàng, Rủi ro thanh khoản, Nghiệp vụ thị trường mở</t>
         </is>
@@ -14152,7 +16289,8 @@
       </c>
       <c r="G373" s="3" t="inlineStr"/>
       <c r="H373" s="2" t="inlineStr"/>
-      <c r="I373" s="3" t="inlineStr">
+      <c r="I373" s="2" t="inlineStr"/>
+      <c r="J373" s="3" t="inlineStr">
         <is>
           <t>Xóa nợ ngoại bảng, Thu nhập ngoài lãi, Nợ xấu</t>
         </is>
@@ -14187,9 +16325,22 @@
           <t>Phần chênh lệch giữa thu nhập lãi (từ cho vay, đầu tư trái phiếu, tiền gửi tại TCTD khác) và chi phí lãi (trả cho tiền gửi, giấy tờ có giá, vay). Đây là nguồn thu chính của ngân hàng Việt Nam, thường chiếm khoảng 70–80% tổng thu nhập hoạt động.</t>
         </is>
       </c>
-      <c r="G374" s="3" t="inlineStr"/>
-      <c r="H374" s="2" t="inlineStr"/>
-      <c r="I374" s="3" t="inlineStr">
+      <c r="G374" s="3" t="inlineStr">
+        <is>
+          <t>Net interest income (NII) is the difference between revenues generated by interest-bearing assets and the cost of servicing (interest-burdened) liabilities. For banks, the assets typically include commercial and personal loans, mortgages, construction loans and investment securities. The liabilities consist primarily of customers' deposits. NII is the difference between (a) interest payments the bank receives on outstanding loans and (b) interest payments the bank makes to customers on their deposits.</t>
+        </is>
+      </c>
+      <c r="H374" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Net_interest_income</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J374" s="3" t="inlineStr">
         <is>
           <t>Biên lãi ròng, Tổng thu nhập hoạt động, Tài sản sinh lãi</t>
         </is>
@@ -14222,7 +16373,8 @@
       </c>
       <c r="G375" s="3" t="inlineStr"/>
       <c r="H375" s="2" t="inlineStr"/>
-      <c r="I375" s="3" t="inlineStr">
+      <c r="I375" s="2" t="inlineStr"/>
+      <c r="J375" s="3" t="inlineStr">
         <is>
           <t>Lãi thuần từ hoạt động dịch vụ, Bancassurance, Thu hồi nợ đã xử lý</t>
         </is>
@@ -14255,7 +16407,8 @@
       </c>
       <c r="G376" s="3" t="inlineStr"/>
       <c r="H376" s="2" t="inlineStr"/>
-      <c r="I376" s="3" t="inlineStr">
+      <c r="I376" s="2" t="inlineStr"/>
+      <c r="J376" s="3" t="inlineStr">
         <is>
           <t>Thu nhập ngoài lãi, Vốn tự có</t>
         </is>
@@ -14300,7 +16453,12 @@
           <t>https://vi.wikipedia.org/wiki/Th%C6%B0_t%C3%ADn_d%E1%BB%A5ng</t>
         </is>
       </c>
-      <c r="I377" s="3" t="inlineStr">
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J377" s="3" t="inlineStr">
         <is>
           <t>Bảo lãnh ngân hàng, Lãi thuần từ hoạt động dịch vụ</t>
         </is>
@@ -14331,9 +16489,22 @@
           <t>Tiền gửi có thỏa thuận thời hạn (1 tháng, 6 tháng, 12 tháng...), rút trước hạn thường chỉ được hưởng lãi không kỳ hạn. Lãi suất cao hơn tiền gửi không kỳ hạn nên chi phí vốn lớn hơn, nhưng nguồn vốn ổn định hơn.</t>
         </is>
       </c>
-      <c r="G378" s="3" t="inlineStr"/>
-      <c r="H378" s="2" t="inlineStr"/>
-      <c r="I378" s="3" t="inlineStr">
+      <c r="G378" s="3" t="inlineStr">
+        <is>
+          <t>A time deposit or term deposit (also known as a certificate of deposit in the United States, and as a guaranteed investment certificate in Canada) is a deposit in a financial institution with a specific maturity date or a period to maturity, commonly referred to as its "term". Time deposits differ from at call deposits, such as savings or checking accounts, which can be withdrawn at any time, without any notice or penalty. Deposits that require notice of withdrawal to be given are effectively time deposits, though they do not have a fixed maturity date.</t>
+        </is>
+      </c>
+      <c r="H378" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Time_deposit</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J378" s="3" t="inlineStr">
         <is>
           <t>Tiền gửi tiết kiệm, Lãi suất huy động, Tiền gửi khách hàng</t>
         </is>
@@ -14366,7 +16537,8 @@
       </c>
       <c r="G379" s="3" t="inlineStr"/>
       <c r="H379" s="2" t="inlineStr"/>
-      <c r="I379" s="3" t="inlineStr">
+      <c r="I379" s="2" t="inlineStr"/>
+      <c r="J379" s="3" t="inlineStr">
         <is>
           <t>Tiền gửi không kỳ hạn, Tiền gửi có kỳ hạn, Vốn huy động</t>
         </is>
@@ -14397,9 +16569,22 @@
           <t>Tiền gửi khách hàng có thể rút bất cứ lúc nào, chủ yếu là số dư tài khoản thanh toán. Ngân hàng chỉ trả lãi rất thấp (thường 0,1–0,5%/năm) cho loại tiền gửi này nên đây là nguồn vốn rẻ nhất.</t>
         </is>
       </c>
-      <c r="G380" s="3" t="inlineStr"/>
-      <c r="H380" s="2" t="inlineStr"/>
-      <c r="I380" s="3" t="inlineStr">
+      <c r="G380" s="3" t="inlineStr">
+        <is>
+          <t>Demand deposits or checkbook money are funds held in demand accounts in commercial banks. These account balances are usually considered money and form the greater part of the narrowly defined money supply of a country. Simply put, these are deposits in the bank that can be withdrawn on demand, without any prior notice.</t>
+        </is>
+      </c>
+      <c r="H380" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Demand_deposit</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J380" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ tiền gửi không kỳ hạn, Tiền gửi khách hàng, Chi phí vốn huy động</t>
         </is>
@@ -14430,9 +16615,22 @@
           <t>Khoản tiền cá nhân gửi vào ngân hàng để hưởng lãi, được ghi nhận trên thẻ tiết kiệm hoặc tài khoản tiết kiệm trực tuyến. Tiền gửi tiết kiệm của cá nhân được bảo hiểm tiền gửi trong hạn mức theo quy định.</t>
         </is>
       </c>
-      <c r="G381" s="3" t="inlineStr"/>
-      <c r="H381" s="2" t="inlineStr"/>
-      <c r="I381" s="3" t="inlineStr">
+      <c r="G381" s="3" t="inlineStr">
+        <is>
+          <t>Tài khoản tiết kiệm là một tài khoản ngân hàng tại một ngân hàng bán lẻ mà có các tính năng bao gồm các yêu cầu chỉ có thể rút tiền hạn chế, không có phương tiện kiểm tra và thường không có tiện ích thẻ ghi nợ, có cơ sở chuyển khoản hạn chế và không thể dùng để rút tiền. Theo truyền thống, các giao dịch trên tài khoản tiết kiệm được ghi lại rộng rãi trong sổ tiết kiệm và đôi khi được gọi là tài khoản sổ tiết kiệm và không cung cấp sao kê ; tuy nhiên, hiện tại các giao dịch như vậy thường được ghi lại bằng điện tử và có thể truy cập trực tuyến.</t>
+        </is>
+      </c>
+      <c r="H381" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/T%C3%A0i_kho%E1%BA%A3n_ti%E1%BA%BFt_ki%E1%BB%87m</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J381" s="3" t="inlineStr">
         <is>
           <t>Tiền gửi có kỳ hạn, Bảo hiểm tiền gửi, Lãi suất huy động</t>
         </is>
@@ -14477,7 +16675,12 @@
           <t>https://vi.wikipedia.org/wiki/T%E1%BB%95_ch%E1%BB%A9c_t%C3%ADn_d%E1%BB%A5ng</t>
         </is>
       </c>
-      <c r="I382" s="3" t="inlineStr">
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J382" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng thương mại, Công ty tài chính, Bảo hiểm tiền gửi</t>
         </is>
@@ -14514,7 +16717,8 @@
       </c>
       <c r="G383" s="3" t="inlineStr"/>
       <c r="H383" s="2" t="inlineStr"/>
-      <c r="I383" s="3" t="inlineStr">
+      <c r="I383" s="2" t="inlineStr"/>
+      <c r="J383" s="3" t="inlineStr">
         <is>
           <t>Thu nhập lãi thuần, Thu nhập ngoài lãi, Tỷ lệ chi phí trên thu nhập</t>
         </is>
@@ -14547,7 +16751,8 @@
       </c>
       <c r="G384" s="3" t="inlineStr"/>
       <c r="H384" s="2" t="inlineStr"/>
-      <c r="I384" s="3" t="inlineStr">
+      <c r="I384" s="2" t="inlineStr"/>
+      <c r="J384" s="3" t="inlineStr">
         <is>
           <t>Công ty Quản lý tài sản của các tổ chức tín dụng Việt Nam, Nợ xấu tiềm ẩn</t>
         </is>
@@ -14584,7 +16789,8 @@
       </c>
       <c r="G385" s="3" t="inlineStr"/>
       <c r="H385" s="2" t="inlineStr"/>
-      <c r="I385" s="3" t="inlineStr">
+      <c r="I385" s="2" t="inlineStr"/>
+      <c r="J385" s="3" t="inlineStr">
         <is>
           <t>Chấm điểm tín dụng, Nợ xấu</t>
         </is>
@@ -14621,7 +16827,8 @@
       </c>
       <c r="G386" s="3" t="inlineStr"/>
       <c r="H386" s="2" t="inlineStr"/>
-      <c r="I386" s="3" t="inlineStr">
+      <c r="I386" s="2" t="inlineStr"/>
+      <c r="J386" s="3" t="inlineStr">
         <is>
           <t>Nợ xấu, Dự phòng chung, Dự phòng cụ thể</t>
         </is>
@@ -14658,7 +16865,8 @@
       </c>
       <c r="G387" s="3" t="inlineStr"/>
       <c r="H387" s="2" t="inlineStr"/>
-      <c r="I387" s="3" t="inlineStr">
+      <c r="I387" s="2" t="inlineStr"/>
+      <c r="J387" s="3" t="inlineStr">
         <is>
           <t>Chi phí hoạt động ngân hàng, Tổng thu nhập hoạt động, Ngân hàng số</t>
         </is>
@@ -14693,9 +16901,22 @@
           <t>Tỷ lệ dư nợ cho vay so với tổng tiền gửi, phản ánh mức độ dùng vốn huy động để cho vay. Theo Thông tư 22/2019/TT-NHNN, ngân hàng thương mại phải giữ LDR (theo cách tính quy định) không quá 85%; LDR quá cao cho thấy áp lực thanh khoản.</t>
         </is>
       </c>
-      <c r="G388" s="3" t="inlineStr"/>
-      <c r="H388" s="2" t="inlineStr"/>
-      <c r="I388" s="3" t="inlineStr">
+      <c r="G388" s="3" t="inlineStr">
+        <is>
+          <t>Loan-to-deposit ratio (LTD ratio or LDR) is a ratio between the banks total loans and total deposits. The ratio is generally expressed in percentage terms If the ratio is lower than one, the bank relied on its own deposits to make loans to its customers, without any outside borrowing. If on the other hand the ratio is greater than one, the bank borrowed money which it reloaned at higher rates, rather than relying entirely on its own deposits. Banks may not be earning an optimal return if the ratio is too low.</t>
+        </is>
+      </c>
+      <c r="H388" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Loan-to-deposit_ratio</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J388" s="3" t="inlineStr">
         <is>
           <t>Rủi ro thanh khoản, Vốn huy động, Cho vay khách hàng</t>
         </is>
@@ -14728,7 +16949,8 @@
       </c>
       <c r="G389" s="3" t="inlineStr"/>
       <c r="H389" s="2" t="inlineStr"/>
-      <c r="I389" s="3" t="inlineStr">
+      <c r="I389" s="2" t="inlineStr"/>
+      <c r="J389" s="3" t="inlineStr">
         <is>
           <t>Rủi ro thanh khoản, Tỷ lệ khả năng chi trả</t>
         </is>
@@ -14761,7 +16983,8 @@
       </c>
       <c r="G390" s="3" t="inlineStr"/>
       <c r="H390" s="2" t="inlineStr"/>
-      <c r="I390" s="3" t="inlineStr">
+      <c r="I390" s="2" t="inlineStr"/>
+      <c r="J390" s="3" t="inlineStr">
         <is>
           <t>Tỷ lệ nợ xấu, Xóa nợ ngoại bảng, Chi phí tín dụng</t>
         </is>
@@ -14798,7 +17021,8 @@
       </c>
       <c r="G391" s="3" t="inlineStr"/>
       <c r="H391" s="2" t="inlineStr"/>
-      <c r="I391" s="3" t="inlineStr">
+      <c r="I391" s="2" t="inlineStr"/>
+      <c r="J391" s="3" t="inlineStr">
         <is>
           <t>Rủi ro thanh khoản, Basel III, Tỷ lệ nguồn vốn ổn định ròng</t>
         </is>
@@ -14835,7 +17059,8 @@
       </c>
       <c r="G392" s="3" t="inlineStr"/>
       <c r="H392" s="2" t="inlineStr"/>
-      <c r="I392" s="3" t="inlineStr">
+      <c r="I392" s="2" t="inlineStr"/>
+      <c r="J392" s="3" t="inlineStr">
         <is>
           <t>Basel III, Tỷ lệ khả năng chi trả, Tỷ lệ vốn ngắn hạn cho vay trung dài hạn</t>
         </is>
@@ -14868,7 +17093,8 @@
       </c>
       <c r="G393" s="3" t="inlineStr"/>
       <c r="H393" s="2" t="inlineStr"/>
-      <c r="I393" s="3" t="inlineStr">
+      <c r="I393" s="2" t="inlineStr"/>
+      <c r="J393" s="3" t="inlineStr">
         <is>
           <t>Nợ cần chú ý, Tỷ lệ nợ xấu, Nợ xấu tiềm ẩn</t>
         </is>
@@ -14905,7 +17131,8 @@
       </c>
       <c r="G394" s="3" t="inlineStr"/>
       <c r="H394" s="2" t="inlineStr"/>
-      <c r="I394" s="3" t="inlineStr">
+      <c r="I394" s="2" t="inlineStr"/>
+      <c r="J394" s="3" t="inlineStr">
         <is>
           <t>Nợ xấu, Tỷ lệ nợ nhóm 2, Tỷ lệ hình thành nợ xấu mới</t>
         </is>
@@ -14942,7 +17169,8 @@
       </c>
       <c r="G395" s="3" t="inlineStr"/>
       <c r="H395" s="2" t="inlineStr"/>
-      <c r="I395" s="3" t="inlineStr">
+      <c r="I395" s="2" t="inlineStr"/>
+      <c r="J395" s="3" t="inlineStr">
         <is>
           <t>Tiền gửi không kỳ hạn, Chi phí vốn huy động, Biên lãi ròng</t>
         </is>
@@ -14975,7 +17203,8 @@
       </c>
       <c r="G396" s="3" t="inlineStr"/>
       <c r="H396" s="2" t="inlineStr"/>
-      <c r="I396" s="3" t="inlineStr">
+      <c r="I396" s="2" t="inlineStr"/>
+      <c r="J396" s="3" t="inlineStr">
         <is>
           <t>Rủi ro thanh khoản, Tỷ lệ cho vay trên tiền gửi</t>
         </is>
@@ -15016,7 +17245,12 @@
           <t>https://vi.wikipedia.org/wiki/V%E1%BB%91n_c%E1%BA%A5p_1</t>
         </is>
       </c>
-      <c r="I397" s="3" t="inlineStr">
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J397" s="3" t="inlineStr">
         <is>
           <t>Vốn tự có, Vốn cấp 2, Basel III</t>
         </is>
@@ -15047,9 +17281,22 @@
           <t>Vốn bổ sung của ngân hàng, gồm trái phiếu chuyển đổi, nợ thứ cấp đủ điều kiện, một phần dự phòng chung và chênh lệch đánh giá lại tài sản. Vốn cấp 2 chỉ được tính tối đa bằng mức quy định so với vốn cấp 1.</t>
         </is>
       </c>
-      <c r="G398" s="3" t="inlineStr"/>
-      <c r="H398" s="2" t="inlineStr"/>
-      <c r="I398" s="3" t="inlineStr">
+      <c r="G398" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 capital, or supplementary capital, includes a number of important and legitimate constituents of a bank's capital requirement. These forms of banking capital were largely standardized in the Basel I accord, issued by the Basel Committee on Banking Supervision and left untouched by the Basel II accord. National regulators of most countries around the world have implemented these standards in local legislation. In the calculation of regulatory capital, Tier 2 is limited to 100% of Tier 1 capital.</t>
+        </is>
+      </c>
+      <c r="H398" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Tier_2_capital</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J398" s="3" t="inlineStr">
         <is>
           <t>Vốn tự có, Vốn cấp 1, Phát hành giấy tờ có giá</t>
         </is>
@@ -15082,7 +17329,8 @@
       </c>
       <c r="G399" s="3" t="inlineStr"/>
       <c r="H399" s="2" t="inlineStr"/>
-      <c r="I399" s="3" t="inlineStr">
+      <c r="I399" s="2" t="inlineStr"/>
+      <c r="J399" s="3" t="inlineStr">
         <is>
           <t>Tiền gửi khách hàng, Phát hành giấy tờ có giá, Tỷ lệ cho vay trên tiền gửi</t>
         </is>
@@ -15115,7 +17363,8 @@
       </c>
       <c r="G400" s="3" t="inlineStr"/>
       <c r="H400" s="2" t="inlineStr"/>
-      <c r="I400" s="3" t="inlineStr">
+      <c r="I400" s="2" t="inlineStr"/>
+      <c r="J400" s="3" t="inlineStr">
         <is>
           <t>Vốn cấp 1, Vốn cấp 2, Hệ số an toàn vốn</t>
         </is>
@@ -15146,9 +17395,22 @@
           <t>Việc ngân hàng dùng dự phòng đã trích để xử lý khoản nợ xấu, đưa khoản nợ ra khỏi bảng cân đối và theo dõi ngoại bảng để tiếp tục thu hồi. Xóa nợ làm tỷ lệ nợ xấu giảm nhưng khách hàng vẫn còn nghĩa vụ trả nợ.</t>
         </is>
       </c>
-      <c r="G401" s="3" t="inlineStr"/>
-      <c r="H401" s="2" t="inlineStr"/>
-      <c r="I401" s="3" t="inlineStr">
+      <c r="G401" s="3" t="inlineStr">
+        <is>
+          <t>A write-off is a reduction of the recognized value of something. In accounting, this is a recognition of the reduced or zero value of an asset. In income tax statements, this is a reduction of taxable income, as a recognition of certain expenses required to produce the income.</t>
+        </is>
+      </c>
+      <c r="H401" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Write-off</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J401" s="3" t="inlineStr">
         <is>
           <t>Thu hồi nợ đã xử lý, Nợ có khả năng mất vốn, Tỷ lệ bao phủ nợ xấu</t>
         </is>
@@ -15181,7 +17443,8 @@
       </c>
       <c r="G402" s="3" t="inlineStr"/>
       <c r="H402" s="2" t="inlineStr"/>
-      <c r="I402" s="3" t="inlineStr">
+      <c r="I402" s="2" t="inlineStr"/>
+      <c r="J402" s="3" t="inlineStr">
         <is>
           <t>Call margin, Giao dịch ký quỹ, Giá sàn, Thị trường giá xuống</t>
         </is>
@@ -15222,7 +17485,12 @@
           <t>https://vi.wikipedia.org/wiki/B%C3%A1n_kh%E1%BB%91ng</t>
         </is>
       </c>
-      <c r="I403" s="3" t="inlineStr">
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J403" s="3" t="inlineStr">
         <is>
           <t>Hợp đồng tương lai chỉ số, Hệ thống KRX, Chứng khoán phái sinh, Thị trường giá xuống</t>
         </is>
@@ -15253,9 +17521,22 @@
           <t>Giới hạn tỷ lệ tăng hoặc giảm tối đa của giá chứng khoán trong một phiên so với giá tham chiếu. Hiện nay biên độ cổ phiếu là ±7% trên HOSE, ±10% trên HNX và ±15% trên UPCoM; ngày giao dịch đầu tiên của cổ phiếu mới niêm yết, đăng ký giao dịch được nới rộng (±20% HOSE, ±30% HNX, ±40% UPCoM). Biên độ giúp hạn chế biến động quá mức nhưng có thể gây hiện tượng trắng bên mua hoặc trắng bên bán.</t>
         </is>
       </c>
-      <c r="G404" s="3" t="inlineStr"/>
-      <c r="H404" s="2" t="inlineStr"/>
-      <c r="I404" s="3" t="inlineStr">
+      <c r="G404" s="3" t="inlineStr">
+        <is>
+          <t>In finance, a trading band is a range of prices for a commodity or currency, including: Currency trading band, a range of prices within which currency exchange rates are controlled Keltner channel, a technical indicator, a range of prices above or below a commodity's average price that may signal a changing trend Bollinger bands, another technical indicator, a range of prices above and below a commodity's average price that may signal a changing trend</t>
+        </is>
+      </c>
+      <c r="H404" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Trading_band</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J404" s="3" t="inlineStr">
         <is>
           <t>Giá tham chiếu, Giá trần, Giá sàn, Sở Giao dịch Chứng khoán TP. Hồ Chí Minh</t>
         </is>
@@ -15286,9 +17567,22 @@
           <t>Mức chênh lệch tối thiểu giữa hai mức giá đặt lệnh liền kề. Trên HOSE, với cổ phiếu và chứng chỉ quỹ đóng: giá dưới 10.000 đồng có bước giá 10 đồng, từ 10.000 đến 49.950 đồng là 50 đồng, từ 50.000 đồng trở lên là 100 đồng; chứng chỉ quỹ ETF và chứng quyền có bước giá 10 đồng. Trên HNX và UPCoM, bước giá cổ phiếu là 100 đồng.</t>
         </is>
       </c>
-      <c r="G405" s="3" t="inlineStr"/>
-      <c r="H405" s="2" t="inlineStr"/>
-      <c r="I405" s="3" t="inlineStr">
+      <c r="G405" s="3" t="inlineStr">
+        <is>
+          <t>In financial markets, the tick size is the smallest price increment in which the prices are quoted. The meaning of the term varies depending on whether stocks, bonds, or futures are being quoted.</t>
+        </is>
+      </c>
+      <c r="H405" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Tick_size</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J405" s="3" t="inlineStr">
         <is>
           <t>Lệnh giới hạn, Giá trần, Giá sàn, Lô chẵn và lô lẻ</t>
         </is>
@@ -15319,9 +17613,22 @@
           <t>Yêu cầu công ty chứng khoán gửi đến nhà đầu tư khi tỷ lệ tài sản thực có trên tổng tài sản trong tài khoản ký quỹ giảm xuống dưới tỷ lệ ký quỹ duy trì (thường khoảng 30-40% tùy công ty). Nhà đầu tư phải nộp thêm tiền, bổ sung tài sản hoặc bán bớt chứng khoán trong thời hạn quy định; nếu không, công ty chứng khoán sẽ bán giải chấp. Call margin hàng loạt thường xảy ra trong các nhịp giảm mạnh của thị trường.</t>
         </is>
       </c>
-      <c r="G406" s="3" t="inlineStr"/>
-      <c r="H406" s="2" t="inlineStr"/>
-      <c r="I406" s="3" t="inlineStr">
+      <c r="G406" s="3" t="inlineStr">
+        <is>
+          <t>Giao dịch ký quỹ (Margin) hay cho vay ký quỹ là giao dịch mua chứng khoán có sử dụng tiền đi vay của công ty chứng khoán, trong đó chứng khoán có được từ giao dịch này và các chứng khoán khác được giao dịch ký quỹ của nhà đầu tư được sử dụng làm tài sản bảo đảm cho khoản vay trên. Giá trị giao di dịch ký quỹ là số tiền hoặc tài sản mà nhà đầu tư phải đặt cọc cho một công ty môi giới chứng khoán để thực hiện các giao dịch vượt quá số vốn hiện có của nhà đầu tư.</t>
+        </is>
+      </c>
+      <c r="H406" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Giao_d%E1%BB%8Bch_k%C3%BD_qu%E1%BB%B9</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J406" s="3" t="inlineStr">
         <is>
           <t>Giao dịch ký quỹ, Bán giải chấp, Thị trường giá xuống</t>
         </is>
@@ -15354,7 +17661,8 @@
       </c>
       <c r="G407" s="3" t="inlineStr"/>
       <c r="H407" s="2" t="inlineStr"/>
-      <c r="I407" s="3" t="inlineStr">
+      <c r="I407" s="2" t="inlineStr"/>
+      <c r="J407" s="3" t="inlineStr">
         <is>
           <t>Hủy niêm yết, Giao dịch ký quỹ, Công bố thông tin, Niêm yết</t>
         </is>
@@ -15387,7 +17695,8 @@
       </c>
       <c r="G408" s="3" t="inlineStr"/>
       <c r="H408" s="2" t="inlineStr"/>
-      <c r="I408" s="3" t="inlineStr">
+      <c r="I408" s="2" t="inlineStr"/>
+      <c r="J408" s="3" t="inlineStr">
         <is>
           <t>Sở Giao dịch Chứng khoán Hà Nội, Chỉ số VN-Index, Thị trường UPCoM</t>
         </is>
@@ -15432,7 +17741,12 @@
           <t>https://vi.wikipedia.org/wiki/Vn-Index</t>
         </is>
       </c>
-      <c r="I409" s="3" t="inlineStr">
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J409" s="3" t="inlineStr">
         <is>
           <t>Chỉ số VN30, Sở Giao dịch Chứng khoán TP. Hồ Chí Minh, Vốn hóa thị trường, Thị trường giá lên</t>
         </is>
@@ -15469,7 +17783,8 @@
       </c>
       <c r="G410" s="3" t="inlineStr"/>
       <c r="H410" s="2" t="inlineStr"/>
-      <c r="I410" s="3" t="inlineStr">
+      <c r="I410" s="2" t="inlineStr"/>
+      <c r="J410" s="3" t="inlineStr">
         <is>
           <t>Chỉ số VN30, Chỉ số VNDiamond, Cổ phiếu vốn hóa lớn, Tỷ lệ free-float</t>
         </is>
@@ -15506,7 +17821,8 @@
       </c>
       <c r="G411" s="3" t="inlineStr"/>
       <c r="H411" s="2" t="inlineStr"/>
-      <c r="I411" s="3" t="inlineStr">
+      <c r="I411" s="2" t="inlineStr"/>
+      <c r="J411" s="3" t="inlineStr">
         <is>
           <t>Chỉ số VN-Index, Hợp đồng tương lai chỉ số, Quỹ ETF, Cổ phiếu blue-chip, Review danh mục ETF</t>
         </is>
@@ -15539,7 +17855,8 @@
       </c>
       <c r="G412" s="3" t="inlineStr"/>
       <c r="H412" s="2" t="inlineStr"/>
-      <c r="I412" s="3" t="inlineStr">
+      <c r="I412" s="2" t="inlineStr"/>
+      <c r="J412" s="3" t="inlineStr">
         <is>
           <t>Room ngoại, Chỉ số VN100, Quỹ ETF, Review danh mục ETF</t>
         </is>
@@ -15572,7 +17889,8 @@
       </c>
       <c r="G413" s="3" t="inlineStr"/>
       <c r="H413" s="2" t="inlineStr"/>
-      <c r="I413" s="3" t="inlineStr">
+      <c r="I413" s="2" t="inlineStr"/>
+      <c r="J413" s="3" t="inlineStr">
         <is>
           <t>Chỉ số VN100, Quỹ ETF, Review danh mục ETF, Chỉ số VN30</t>
         </is>
@@ -15603,9 +17921,22 @@
           <t>Nghiệp vụ chia một cổ phiếu thành nhiều cổ phiếu có mệnh giá nhỏ hơn (ví dụ 1 thành 2), làm tăng số lượng cổ phiếu và giảm giá mỗi cổ phiếu tương ứng mà không làm thay đổi vốn hóa. Do mệnh giá cổ phiếu niêm yết ở Việt Nam cố định 10.000 đồng, doanh nghiệp không thể chia tách theo đúng nghĩa mà thường tạo hiệu ứng tương tự bằng cổ phiếu thưởng hoặc cổ tức bằng cổ phiếu tỷ lệ lớn. Mục đích là đưa thị giá về mức dễ giao dịch, tăng thanh khoản.</t>
         </is>
       </c>
-      <c r="G414" s="3" t="inlineStr"/>
-      <c r="H414" s="2" t="inlineStr"/>
-      <c r="I414" s="3" t="inlineStr">
+      <c r="G414" s="3" t="inlineStr">
+        <is>
+          <t>A stock split or stock divide increases the number of shares in a company. For example, after a 2-for-1 split, each investor will own double the number of shares, and each share will be worth half as much. A stock split causes a decrease of market price of individual shares, but does not change the total market capitalization of the company: stock dilution does not occur. A company may split its stock when the market price per share is so high that it becomes unwieldy when traded. One of the reasons is that a very high share price may deter small investors from buying the shares.</t>
+        </is>
+      </c>
+      <c r="H414" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Stock_split</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J414" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu thưởng, Cổ tức bằng cổ phiếu, Thanh khoản, Vốn hóa thị trường</t>
         </is>
@@ -15650,7 +17981,12 @@
           <t>https://vi.wikipedia.org/wiki/T%2B2</t>
         </is>
       </c>
-      <c r="I415" s="3" t="inlineStr">
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J415" s="3" t="inlineStr">
         <is>
           <t>Tổng công ty Lưu ký và Bù trừ Chứng khoán Việt Nam, Ngày giao dịch không hưởng quyền, Hệ thống KRX, Giao dịch ký quỹ</t>
         </is>
@@ -15695,7 +18031,12 @@
           <t>https://vi.wikipedia.org/wiki/Ch%E1%BB%A9ng_ch%E1%BB%89_qu%E1%BB%B9</t>
         </is>
       </c>
-      <c r="I416" s="3" t="inlineStr">
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J416" s="3" t="inlineStr">
         <is>
           <t>Quỹ mở, Quỹ ETF, Công ty quản lý quỹ</t>
         </is>
@@ -15736,7 +18077,12 @@
           <t>https://vi.wikipedia.org/wiki/Ph%C3%A1i_sinh_(t%C3%A0i_ch%C3%ADnh)</t>
         </is>
       </c>
-      <c r="I417" s="3" t="inlineStr">
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J417" s="3" t="inlineStr">
         <is>
           <t>Hợp đồng tương lai chỉ số, Chứng quyền có bảo đảm, Sở Giao dịch Chứng khoán Hà Nội, Bán khống</t>
         </is>
@@ -15781,7 +18127,12 @@
           <t>https://vi.wikipedia.org/wiki/Ch%E1%BB%A9ng_quy%E1%BB%81n_c%C3%B3_b%E1%BA%A3o_%C4%91%E1%BA%A3m</t>
         </is>
       </c>
-      <c r="I418" s="3" t="inlineStr">
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J418" s="3" t="inlineStr">
         <is>
           <t>Chứng khoán phái sinh, Chỉ số VN30, Công ty chứng khoán, Bước giá</t>
         </is>
@@ -15814,7 +18165,8 @@
       </c>
       <c r="G419" s="3" t="inlineStr"/>
       <c r="H419" s="2" t="inlineStr"/>
-      <c r="I419" s="3" t="inlineStr">
+      <c r="I419" s="2" t="inlineStr"/>
+      <c r="J419" s="3" t="inlineStr">
         <is>
           <t>Người nội bộ, Công bố thông tin, Mua bán và sáp nhập, Tỷ lệ free-float</t>
         </is>
@@ -15855,7 +18207,12 @@
           <t>https://vi.wikipedia.org/wiki/C%E1%BB%95_phi%E1%BA%BFu</t>
         </is>
       </c>
-      <c r="I420" s="3" t="inlineStr">
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J420" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu phổ thông, Cổ phiếu ưu đãi, Cổ tức bằng tiền mặt, Đại hội đồng cổ đông</t>
         </is>
@@ -15886,9 +18243,22 @@
           <t>Cổ phiếu của các doanh nghiệp đầu ngành, vốn hóa lớn, tài chính vững mạnh, kinh doanh ổn định và có uy tín lâu năm. Tại Việt Nam, nhóm blue-chip thường được hiểu là các cổ phiếu thuộc rổ VN30 như VCB, FPT, VNM, HPG, MWG. Blue-chip có thanh khoản cao, được khối ngoại và quỹ ETF nắm giữ nhiều và dẫn dắt biến động của VN-Index.</t>
         </is>
       </c>
-      <c r="G421" s="3" t="inlineStr"/>
-      <c r="H421" s="2" t="inlineStr"/>
-      <c r="I421" s="3" t="inlineStr">
+      <c r="G421" s="3" t="inlineStr">
+        <is>
+          <t>Blue chip là cổ phiếu của một công ty có độ uy tín cao, tình hình tài chính vững chắc và giá trị vốn hóa thị trường lớn. Đây là cổ phiếu của của một công ty cổ phần có danh tiếng toàn quốc về chất lượng, độ tin cậy và khả năng hoạt động có lãi trong cả thời điểm thuận lợi và khó khăn. Từ Blue-chip (thẻ nhựa xanh) bắt nguồn từ loại thẻ đổi tiền khi chơi bài poker tại các sòng bạc, trong đó Chip là loại thẻ nhựa đổi tiền khi đánh bạc, theo thông lệ, chip màu xanh (blue) có giá trị quy đổi cao nhất.</t>
+        </is>
+      </c>
+      <c r="H421" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Blue_chip</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J421" s="3" t="inlineStr">
         <is>
           <t>Chỉ số VN30, Cổ phiếu vốn hóa lớn, Cổ phiếu penny, Khối ngoại</t>
         </is>
@@ -15921,7 +18291,8 @@
       </c>
       <c r="G422" s="3" t="inlineStr"/>
       <c r="H422" s="2" t="inlineStr"/>
-      <c r="I422" s="3" t="inlineStr">
+      <c r="I422" s="2" t="inlineStr"/>
+      <c r="J422" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu phòng thủ, Thị trường giá lên, Thị trường giá xuống, Phân tích cơ bản</t>
         </is>
@@ -15966,7 +18337,12 @@
           <t>https://vi.wikipedia.org/wiki/Ch%C6%B0%C6%A1ng_tr%C3%ACnh_ph%C3%A1t_h%C3%A0nh_c%E1%BB%95_phi%E1%BA%BFu_cho_ng%C6%B0%E1%BB%9Di_lao_%C4%91%E1%BB%99ng</t>
         </is>
       </c>
-      <c r="I423" s="3" t="inlineStr">
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J423" s="3" t="inlineStr">
         <is>
           <t>Phát hành thêm cổ phiếu, Đại hội đồng cổ đông, Cổ phiếu quỹ, Người nội bộ</t>
         </is>
@@ -15997,9 +18373,22 @@
           <t>Cổ phiếu có thị giá thấp (ở Việt Nam thường dưới 10.000 đồng, tức dưới mệnh giá), vốn hóa nhỏ, nền tảng kinh doanh yếu hoặc chưa rõ ràng. Cổ phiếu penny có thể tăng giảm rất mạnh, dễ bị đầu cơ, làm giá và thường không được cho vay margin. Nhà đầu tư cần đặc biệt thận trọng vì rủi ro mất vốn cao.</t>
         </is>
       </c>
-      <c r="G424" s="3" t="inlineStr"/>
-      <c r="H424" s="2" t="inlineStr"/>
-      <c r="I424" s="3" t="inlineStr">
+      <c r="G424" s="3" t="inlineStr">
+        <is>
+          <t>In American economics, penny stocks are common shares of small public companies that trade for less than $5 per share. The U.S. Securities and Exchange Commission (SEC) uses the term "penny stock" to refer to a security, a financial instrument which represents a given financial value, issued by small public companies that trade at less than $5 per share. Prior to the SEC's classification, penny stocks referred to shares that traded for "pennies on the dollar".</t>
+        </is>
+      </c>
+      <c r="H424" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Penny_stock</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J424" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu blue-chip, Cổ phiếu vốn hóa lớn, Thanh khoản, Cảnh báo, kiểm soát, hạn chế giao dịch</t>
         </is>
@@ -16040,7 +18429,12 @@
           <t>https://vi.wikipedia.org/wiki/C%E1%BB%95_phi%E1%BA%BFu_ph%E1%BB%95_th%C3%B4ng</t>
         </is>
       </c>
-      <c r="I425" s="3" t="inlineStr">
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J425" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu, Cổ phiếu ưu đãi, Quyền mua cổ phiếu, Đại hội đồng cổ đông</t>
         </is>
@@ -16073,7 +18467,8 @@
       </c>
       <c r="G426" s="3" t="inlineStr"/>
       <c r="H426" s="2" t="inlineStr"/>
-      <c r="I426" s="3" t="inlineStr">
+      <c r="I426" s="2" t="inlineStr"/>
+      <c r="J426" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu chu kỳ, Thị trường giá xuống, Cổ tức bằng tiền mặt, Rủi ro hệ thống</t>
         </is>
@@ -16104,9 +18499,22 @@
           <t>Cổ phiếu phát hành miễn phí cho cổ đông hiện hữu theo tỷ lệ sở hữu, từ các nguồn thuộc vốn chủ sở hữu như thặng dư vốn cổ phần, quỹ đầu tư phát triển. Cổ phiếu thưởng khác cổ tức bằng cổ phiếu ở nguồn phát hành nhưng có tác động tương tự: số cổ phiếu và vốn điều lệ tăng, giá tham chiếu bị điều chỉnh giảm, tổng giá trị tài sản của cổ đông không đổi.</t>
         </is>
       </c>
-      <c r="G427" s="3" t="inlineStr"/>
-      <c r="H427" s="2" t="inlineStr"/>
-      <c r="I427" s="3" t="inlineStr">
+      <c r="G427" s="3" t="inlineStr">
+        <is>
+          <t>Bonus shares are shares distributed by a company to its current shareholders as fully paid shares free of charge. to capitalise a part of the company's retained earnings for conversion of its share premium account, or distribution of treasury shares. An issue of bonus shares is referred to as a bonus share issue.</t>
+        </is>
+      </c>
+      <c r="H427" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bonus_share</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J427" s="3" t="inlineStr">
         <is>
           <t>Cổ tức bằng cổ phiếu, Phát hành thêm cổ phiếu, Ngày giao dịch không hưởng quyền, Chia tách cổ phiếu</t>
         </is>
@@ -16147,7 +18555,12 @@
           <t>https://vi.wikipedia.org/wiki/C%E1%BB%95_phi%E1%BA%BFu_%C6%B0u_%C4%91%C3%A3i</t>
         </is>
       </c>
-      <c r="I428" s="3" t="inlineStr">
+      <c r="I428" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J428" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu phổ thông, Cổ phiếu, Cổ tức bằng tiền mặt</t>
         </is>
@@ -16180,7 +18593,8 @@
       </c>
       <c r="G429" s="3" t="inlineStr"/>
       <c r="H429" s="2" t="inlineStr"/>
-      <c r="I429" s="3" t="inlineStr">
+      <c r="I429" s="2" t="inlineStr"/>
+      <c r="J429" s="3" t="inlineStr">
         <is>
           <t>Vốn hóa thị trường, Cổ phiếu blue-chip, Chỉ số VN30, Cổ phiếu penny</t>
         </is>
@@ -16211,9 +18625,22 @@
           <t>Hình thức chia lợi nhuận sau thuế chưa phân phối bằng cách phát hành thêm cổ phiếu cho cổ đông hiện hữu theo tỷ lệ (ví dụ 100:15, sở hữu 100 cổ phiếu nhận thêm 15 cổ phiếu mới). Doanh nghiệp giữ lại tiền để tái đầu tư, vốn điều lệ tăng nhưng tổng giá trị tài sản của cổ đông về lý thuyết không đổi do giá tham chiếu được điều chỉnh giảm tương ứng. Phần cổ phiếu lẻ phát sinh thường được làm tròn xuống và xử lý theo phương án của công ty.</t>
         </is>
       </c>
-      <c r="G430" s="3" t="inlineStr"/>
-      <c r="H430" s="2" t="inlineStr"/>
-      <c r="I430" s="3" t="inlineStr">
+      <c r="G430" s="3" t="inlineStr">
+        <is>
+          <t>Cổ tức (dividend) là một phần lợi nhuận sau thuế được chia cho các cổ đông của một công ty cổ phần. Cổ tức có thể được trả bằng tiền, cổ phiếu.</t>
+        </is>
+      </c>
+      <c r="H430" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/C%E1%BB%95_t%E1%BB%A9c</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J430" s="3" t="inlineStr">
         <is>
           <t>Cổ tức bằng tiền mặt, Cổ phiếu thưởng, Ngày giao dịch không hưởng quyền, Chia tách cổ phiếu</t>
         </is>
@@ -16244,9 +18671,22 @@
           <t>Phần lợi nhuận sau thuế được công ty chia cho cổ đông bằng tiền, thường công bố theo tỷ lệ phần trăm trên mệnh giá 10.000 đồng (ví dụ cổ tức 15% tức 1.500 đồng/cổ phiếu). Cổ đông có tên trong danh sách tại ngày đăng ký cuối cùng được nhận sau khi khấu trừ thuế thu nhập cá nhân 5%; theo Luật Doanh nghiệp, cổ tức phải được thanh toán trong vòng 6 tháng kể từ ngày kết thúc họp Đại hội đồng cổ đông thường niên. Vào ngày giao dịch không hưởng quyền, giá tham chiếu bị trừ đi đúng phần cổ tức.</t>
         </is>
       </c>
-      <c r="G431" s="3" t="inlineStr"/>
-      <c r="H431" s="2" t="inlineStr"/>
-      <c r="I431" s="3" t="inlineStr">
+      <c r="G431" s="3" t="inlineStr">
+        <is>
+          <t>Cổ tức (dividend) là một phần lợi nhuận sau thuế được chia cho các cổ đông của một công ty cổ phần. Cổ tức có thể được trả bằng tiền, cổ phiếu.</t>
+        </is>
+      </c>
+      <c r="H431" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/C%E1%BB%95_t%E1%BB%A9c</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J431" s="3" t="inlineStr">
         <is>
           <t>Cổ tức bằng cổ phiếu, Ngày đăng ký cuối cùng, Ngày giao dịch không hưởng quyền, Đại hội đồng cổ đông</t>
         </is>
@@ -16291,7 +18731,12 @@
           <t>https://vi.wikipedia.org/wiki/C%C3%B4ng_ty_ch%E1%BB%A9ng_kho%C3%A1n</t>
         </is>
       </c>
-      <c r="I432" s="3" t="inlineStr">
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J432" s="3" t="inlineStr">
         <is>
           <t>Tài khoản chứng khoán, Giao dịch ký quỹ, Phí giao dịch chứng khoán, Ủy ban Chứng khoán Nhà nước</t>
         </is>
@@ -16324,7 +18769,8 @@
       </c>
       <c r="G433" s="3" t="inlineStr"/>
       <c r="H433" s="2" t="inlineStr"/>
-      <c r="I433" s="3" t="inlineStr">
+      <c r="I433" s="2" t="inlineStr"/>
+      <c r="J433" s="3" t="inlineStr">
         <is>
           <t>Quỹ mở, Quỹ ETF, Chứng chỉ quỹ, Nhà đầu tư tổ chức</t>
         </is>
@@ -16355,9 +18801,22 @@
           <t>Chiến lược phân bổ vốn vào nhiều tài sản, cổ phiếu, ngành khác nhau trong danh mục đầu tư (tập hợp các tài sản nhà đầu tư nắm giữ) để giảm thiểu thiệt hại khi một tài sản riêng lẻ biến động bất lợi. Đa dạng hóa giúp loại bỏ phần lớn rủi ro phi hệ thống nhưng không loại bỏ được rủi ro hệ thống; nguyên tắc quen thuộc là không bỏ tất cả trứng vào một giỏ.</t>
         </is>
       </c>
-      <c r="G434" s="3" t="inlineStr"/>
-      <c r="H434" s="2" t="inlineStr"/>
-      <c r="I434" s="3" t="inlineStr">
+      <c r="G434" s="3" t="inlineStr">
+        <is>
+          <t>Đa dạng hoá (là cách viết tắt của Đa dạng hoá trong đầu tư) là ý tưởng mà nhà đầu tư phân bổ tiền vào nhiều loại đầu tư khác nhau. Khi một lĩnh vực đầu tư bị sụt giảm và lĩnh vực khác tăng trưởng thì việc lựa chọn đa dạng hoá trong đầu tư giúp nhà đầu tư giảm thiểu rủi ro của mình. Đa dạng hóa cùng phòng ngừa rủi ro là hai kỹ thuật chung để giảm thiểu rủi ro trong đầu tư tài chính. Mức độ cơ bản nhất trong đa dạng hoá danh mục đầu tư là mua nhiều loại cổ phiếu thay vì mua chỉ một loại cổ phiếu.</t>
+        </is>
+      </c>
+      <c r="H434" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/%C4%90a_d%E1%BA%A1ng_h%C3%B3a_(%C4%91%E1%BA%A7u_t%C6%B0)</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J434" s="3" t="inlineStr">
         <is>
           <t>Rủi ro phi hệ thống, Rủi ro hệ thống, Đầu tư thụ động, Quỹ mở</t>
         </is>
@@ -16402,7 +18861,12 @@
           <t>https://vi.wikipedia.org/wiki/%C4%90%E1%BA%A1i_h%E1%BB%99i_c%E1%BB%95_%C4%91%C3%B4ng</t>
         </is>
       </c>
-      <c r="I435" s="3" t="inlineStr">
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J435" s="3" t="inlineStr">
         <is>
           <t>Cổ đông lớn, Cổ tức bằng tiền mặt, Ngày đăng ký cuối cùng, Phát hành thêm cổ phiếu</t>
         </is>
@@ -16443,7 +18907,12 @@
           <t>https://vi.wikipedia.org/wiki/%C4%90%E1%BA%A7u_t%C6%B0_gi%C3%A1_tr%E1%BB%8B</t>
         </is>
       </c>
-      <c r="I436" s="3" t="inlineStr">
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J436" s="3" t="inlineStr">
         <is>
           <t>Phân tích cơ bản, Đầu tư tăng trưởng, Cổ phiếu blue-chip</t>
         </is>
@@ -16474,9 +18943,22 @@
           <t>Trường phái đầu tư ưu tiên cổ phiếu của doanh nghiệp có tốc độ tăng trưởng doanh thu và lợi nhuận cao hơn mặt bằng chung, chấp nhận mua ở mức định giá cao vì kỳ vọng lợi nhuận tương lai sẽ bù đắp. Cổ phiếu tăng trưởng thường giữ lại lợi nhuận để tái đầu tư thay vì chia cổ tức tiền mặt cao, và có thể giảm giá mạnh khi kết quả kinh doanh không đạt kỳ vọng.</t>
         </is>
       </c>
-      <c r="G437" s="3" t="inlineStr"/>
-      <c r="H437" s="2" t="inlineStr"/>
-      <c r="I437" s="3" t="inlineStr">
+      <c r="G437" s="3" t="inlineStr">
+        <is>
+          <t>Growth investing is a type of investment strategy focused on capital appreciation. Those who follow this style, known as growth investors, invest in companies that exhibit signs of above-average growth, even if the share price appears expensive in terms of metrics such as price-to-earnings or price-to-book ratios. In typical usage, the term "growth investing" contrasts with the strategy known as value investing.</t>
+        </is>
+      </c>
+      <c r="H437" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Growth_investing</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J437" s="3" t="inlineStr">
         <is>
           <t>Đầu tư giá trị, Phân tích cơ bản, Tỷ suất sinh lời, Cổ phiếu chu kỳ</t>
         </is>
@@ -16507,9 +18989,22 @@
           <t>Chiến lược đầu tư mô phỏng một chỉ số thị trường (như VN30, VN-Index) thay vì cố gắng chọn cổ phiếu, thường thực hiện qua quỹ ETF hoặc quỹ chỉ số với chi phí thấp. Ngược lại, đầu tư chủ động là việc nhà đầu tư hoặc quỹ tự chọn cổ phiếu và thời điểm giao dịch để tìm cách vượt trội so với chỉ số tham chiếu. Nhiều nghiên cứu cho thấy phần lớn quỹ chủ động khó vượt chỉ số trong dài hạn sau khi trừ chi phí.</t>
         </is>
       </c>
-      <c r="G438" s="3" t="inlineStr"/>
-      <c r="H438" s="2" t="inlineStr"/>
-      <c r="I438" s="3" t="inlineStr">
+      <c r="G438" s="3" t="inlineStr">
+        <is>
+          <t>Passive management (also called passive investing) is an investing strategy that tracks a market-weighted index or portfolio. Passive management is most common on the equity market, where index funds track a stock market index, but it is becoming more common in other investment types, including bonds, commodities and hedge funds. There has been a substantial increase in passive investing over the last twenty years. The most popular method is to mimic the performance of an externally specified index by buying an index fund.</t>
+        </is>
+      </c>
+      <c r="H438" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Passive_management</t>
+        </is>
+      </c>
+      <c r="I438" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J438" s="3" t="inlineStr">
         <is>
           <t>Quỹ ETF, Chỉ số VN30, Đa dạng hóa danh mục, Review danh mục ETF</t>
         </is>
@@ -16542,7 +19037,8 @@
       </c>
       <c r="G439" s="3" t="inlineStr"/>
       <c r="H439" s="2" t="inlineStr"/>
-      <c r="I439" s="3" t="inlineStr">
+      <c r="I439" s="2" t="inlineStr"/>
+      <c r="J439" s="3" t="inlineStr">
         <is>
           <t>Giá trần, Giá tham chiếu, Biên độ dao động giá, Bán giải chấp</t>
         </is>
@@ -16573,9 +19069,22 @@
           <t>Mức giá làm cơ sở để tính giá trần và giá sàn trong phiên giao dịch. Trên HOSE và HNX, giá tham chiếu là giá đóng cửa của phiên liền trước; trên UPCoM là bình quân gia quyền các giá khớp lệnh liên tục của phiên liền trước. Vào ngày giao dịch không hưởng quyền (chia cổ tức, phát hành thêm), giá tham chiếu được điều chỉnh giảm tương ứng.</t>
         </is>
       </c>
-      <c r="G440" s="3" t="inlineStr"/>
-      <c r="H440" s="2" t="inlineStr"/>
-      <c r="I440" s="3" t="inlineStr">
+      <c r="G440" s="3" t="inlineStr">
+        <is>
+          <t>A reference price (RP) is the price that a purchaser announces that it is willing to pay for a good or service. It is used by high-volume purchasers to inform suppliers. RP requires consumers to have access to price and quality information, which is not general practice in many industries. Further, it does not help consumers with urgent needs, cognitive and/or other impairments. Reference pricing requires sufficient competition. Otherwise, consumers have no choice about providers, who in turn face less pricing pressure.</t>
+        </is>
+      </c>
+      <c r="H440" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Reference_price</t>
+        </is>
+      </c>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J440" s="3" t="inlineStr">
         <is>
           <t>Giá trần, Giá sàn, Biên độ dao động giá, Ngày giao dịch không hưởng quyền</t>
         </is>
@@ -16608,7 +19117,8 @@
       </c>
       <c r="G441" s="3" t="inlineStr"/>
       <c r="H441" s="2" t="inlineStr"/>
-      <c r="I441" s="3" t="inlineStr">
+      <c r="I441" s="2" t="inlineStr"/>
+      <c r="J441" s="3" t="inlineStr">
         <is>
           <t>Giá sàn, Giá tham chiếu, Biên độ dao động giá, Bước giá</t>
         </is>
@@ -16653,7 +19163,12 @@
           <t>https://vi.wikipedia.org/wiki/Giao_d%E1%BB%8Bch_k%C3%BD_qu%E1%BB%B9</t>
         </is>
       </c>
-      <c r="I442" s="3" t="inlineStr">
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J442" s="3" t="inlineStr">
         <is>
           <t>Call margin, Bán giải chấp, Công ty chứng khoán, Cảnh báo, kiểm soát, hạn chế giao dịch</t>
         </is>
@@ -16686,7 +19201,8 @@
       </c>
       <c r="G443" s="3" t="inlineStr"/>
       <c r="H443" s="2" t="inlineStr"/>
-      <c r="I443" s="3" t="inlineStr">
+      <c r="I443" s="2" t="inlineStr"/>
+      <c r="J443" s="3" t="inlineStr">
         <is>
           <t>Khớp lệnh liên tục, Room ngoại, Cổ đông lớn, Biên độ dao động giá</t>
         </is>
@@ -16723,7 +19239,8 @@
       </c>
       <c r="G444" s="3" t="inlineStr"/>
       <c r="H444" s="2" t="inlineStr"/>
-      <c r="I444" s="3" t="inlineStr">
+      <c r="I444" s="2" t="inlineStr"/>
+      <c r="J444" s="3" t="inlineStr">
         <is>
           <t>Bán khống, Chu kỳ thanh toán T+2, Nâng hạng thị trường, Sở Giao dịch Chứng khoán TP. Hồ Chí Minh</t>
         </is>
@@ -16758,9 +19275,22 @@
           <t>Hợp đồng chuẩn hóa cam kết mua hoặc bán giá trị chỉ số VN30 tại mức giá xác định vào ngày đáo hạn trong tương lai, thanh toán bằng tiền, giao dịch trên HNX với hệ số nhân 100.000 đồng/điểm chỉ số. Ngày đáo hạn là thứ Năm thứ ba của tháng đáo hạn; nhà đầu tư chỉ cần ký quỹ một phần giá trị hợp đồng, được mở vị thế mua (long) hoặc bán (short) và đóng vị thế ngay trong ngày. Mã giao dịch phổ biến có dạng VN30F1M (hợp đồng tháng gần nhất).</t>
         </is>
       </c>
-      <c r="G445" s="3" t="inlineStr"/>
-      <c r="H445" s="2" t="inlineStr"/>
-      <c r="I445" s="3" t="inlineStr">
+      <c r="G445" s="3" t="inlineStr">
+        <is>
+          <t>In finance, a stock market index future is a cash-settled futures contract on the value of a particular stock market index. The turnover for the global market in exchange-traded equity index futures is notionally valued, for 2008, by the Bank for International Settlements at US$130 trillion.</t>
+        </is>
+      </c>
+      <c r="H445" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Stock_market_index_future</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J445" s="3" t="inlineStr">
         <is>
           <t>Chứng khoán phái sinh, Chỉ số VN30, Bán khống, Giao dịch ký quỹ</t>
         </is>
@@ -16793,7 +19323,8 @@
       </c>
       <c r="G446" s="3" t="inlineStr"/>
       <c r="H446" s="2" t="inlineStr"/>
-      <c r="I446" s="3" t="inlineStr">
+      <c r="I446" s="2" t="inlineStr"/>
+      <c r="J446" s="3" t="inlineStr">
         <is>
           <t>Niêm yết, Thị trường UPCoM, Cảnh báo, kiểm soát, hạn chế giao dịch, Công bố thông tin</t>
         </is>
@@ -16826,7 +19357,8 @@
       </c>
       <c r="G447" s="3" t="inlineStr"/>
       <c r="H447" s="2" t="inlineStr"/>
-      <c r="I447" s="3" t="inlineStr">
+      <c r="I447" s="2" t="inlineStr"/>
+      <c r="J447" s="3" t="inlineStr">
         <is>
           <t>Thanh khoản, Khớp lệnh liên tục, Giao dịch thỏa thuận, Phân tích kỹ thuật</t>
         </is>
@@ -16859,7 +19391,8 @@
       </c>
       <c r="G448" s="3" t="inlineStr"/>
       <c r="H448" s="2" t="inlineStr"/>
-      <c r="I448" s="3" t="inlineStr">
+      <c r="I448" s="2" t="inlineStr"/>
+      <c r="J448" s="3" t="inlineStr">
         <is>
           <t>Room ngoại, Mua ròng/Bán ròng, Nâng hạng thị trường, Tổng công ty Lưu ký và Bù trừ Chứng khoán Việt Nam</t>
         </is>
@@ -16892,7 +19425,8 @@
       </c>
       <c r="G449" s="3" t="inlineStr"/>
       <c r="H449" s="2" t="inlineStr"/>
-      <c r="I449" s="3" t="inlineStr">
+      <c r="I449" s="2" t="inlineStr"/>
+      <c r="J449" s="3" t="inlineStr">
         <is>
           <t>Phiên khớp lệnh định kỳ, Lệnh giới hạn, Lệnh thị trường, Khối lượng khớp lệnh</t>
         </is>
@@ -16929,7 +19463,8 @@
       </c>
       <c r="G450" s="3" t="inlineStr"/>
       <c r="H450" s="2" t="inlineStr"/>
-      <c r="I450" s="3" t="inlineStr">
+      <c r="I450" s="2" t="inlineStr"/>
+      <c r="J450" s="3" t="inlineStr">
         <is>
           <t>Phiên khớp lệnh định kỳ, Lệnh ATO, Giá tham chiếu, Review danh mục ETF</t>
         </is>
@@ -16966,7 +19501,8 @@
       </c>
       <c r="G451" s="3" t="inlineStr"/>
       <c r="H451" s="2" t="inlineStr"/>
-      <c r="I451" s="3" t="inlineStr">
+      <c r="I451" s="2" t="inlineStr"/>
+      <c r="J451" s="3" t="inlineStr">
         <is>
           <t>Phiên khớp lệnh định kỳ, Lệnh ATC, Lệnh giới hạn</t>
         </is>
@@ -17001,9 +19537,22 @@
           <t>Lệnh mua hoặc bán chứng khoán tại một mức giá xác định hoặc tốt hơn, có hiệu lực từ khi nhập vào hệ thống đến hết ngày giao dịch hoặc đến khi bị hủy. Đây là loại lệnh phổ biến nhất, dùng được trong cả phiên định kỳ và liên tục trên HOSE, HNX, UPCoM; giá đặt phải nằm trong khoảng từ giá sàn đến giá trần và đúng bước giá.</t>
         </is>
       </c>
-      <c r="G452" s="3" t="inlineStr"/>
-      <c r="H452" s="2" t="inlineStr"/>
-      <c r="I452" s="3" t="inlineStr">
+      <c r="G452" s="3" t="inlineStr">
+        <is>
+          <t>Lệnh giao dịch chứng khoán hay còn gọi là đặt lệnh (Order) là hướng dẫn mua hoặc bán trên một địa điểm giao dịch như thị trường chứng khoán, thị trường trái phiếu, thị trường hàng hóa, thị trường phái sinh tài chính hoặc sàn giao dịch tiền điện tử. Những hướng dẫn này có thể đơn giản hoặc phức tạp và có thể được gửi tới nhà môi giới hoặc trực tiếp đến địa điểm giao dịch thông qua tiếp cận thị trường trực tiếp. Có một số hướng dẫn tiêu chuẩn cho các lệnh giao dịch như thế.</t>
+        </is>
+      </c>
+      <c r="H452" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/L%E1%BB%87nh_giao_d%E1%BB%8Bch_ch%E1%BB%A9ng_kho%C3%A1n</t>
+        </is>
+      </c>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J452" s="3" t="inlineStr">
         <is>
           <t>Lệnh thị trường, Khớp lệnh liên tục, Giá trần, Bước giá</t>
         </is>
@@ -17038,9 +19587,22 @@
           <t>Lệnh mua tại mức giá bán thấp nhất hoặc bán tại mức giá mua cao nhất đang có trên thị trường, không cần ghi giá cụ thể. Trên HOSE, lệnh MP chỉ được nhập trong phiên khớp lệnh liên tục, phần chưa khớp được chuyển thành lệnh giới hạn hoặc bị hủy theo quy định; HNX và UPCoM có các biến thể như MTL, MOK, MAK. Lệnh thị trường giúp khớp nhanh nhưng có thể khớp ở giá bất lợi khi thị trường biến động mạnh.</t>
         </is>
       </c>
-      <c r="G453" s="3" t="inlineStr"/>
-      <c r="H453" s="2" t="inlineStr"/>
-      <c r="I453" s="3" t="inlineStr">
+      <c r="G453" s="3" t="inlineStr">
+        <is>
+          <t>Lệnh giao dịch chứng khoán hay còn gọi là đặt lệnh (Order) là hướng dẫn mua hoặc bán trên một địa điểm giao dịch như thị trường chứng khoán, thị trường trái phiếu, thị trường hàng hóa, thị trường phái sinh tài chính hoặc sàn giao dịch tiền điện tử. Những hướng dẫn này có thể đơn giản hoặc phức tạp và có thể được gửi tới nhà môi giới hoặc trực tiếp đến địa điểm giao dịch thông qua tiếp cận thị trường trực tiếp. Có một số hướng dẫn tiêu chuẩn cho các lệnh giao dịch như thế.</t>
+        </is>
+      </c>
+      <c r="H453" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/L%E1%BB%87nh_giao_d%E1%BB%8Bch_ch%E1%BB%A9ng_kho%C3%A1n</t>
+        </is>
+      </c>
+      <c r="I453" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J453" s="3" t="inlineStr">
         <is>
           <t>Lệnh giới hạn, Khớp lệnh liên tục, Thanh khoản</t>
         </is>
@@ -17073,7 +19635,8 @@
       </c>
       <c r="G454" s="3" t="inlineStr"/>
       <c r="H454" s="2" t="inlineStr"/>
-      <c r="I454" s="3" t="inlineStr">
+      <c r="I454" s="2" t="inlineStr"/>
+      <c r="J454" s="3" t="inlineStr">
         <is>
           <t>Bước giá, Cổ tức bằng cổ phiếu, Cổ phiếu thưởng, Lệnh giới hạn</t>
         </is>
@@ -17106,7 +19669,8 @@
       </c>
       <c r="G455" s="3" t="inlineStr"/>
       <c r="H455" s="2" t="inlineStr"/>
-      <c r="I455" s="3" t="inlineStr">
+      <c r="I455" s="2" t="inlineStr"/>
+      <c r="J455" s="3" t="inlineStr">
         <is>
           <t>Trái phiếu, Trái phiếu doanh nghiệp, Tỷ suất sinh lời, Rủi ro hệ thống</t>
         </is>
@@ -17151,7 +19715,12 @@
           <t>https://vi.wikipedia.org/wiki/Mua_b%C3%A1n_v%C3%A0_s%C3%A1p_nh%E1%BA%ADp</t>
         </is>
       </c>
-      <c r="I456" s="3" t="inlineStr">
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J456" s="3" t="inlineStr">
         <is>
           <t>Cổ đông lớn, Phát hành riêng lẻ, Giao dịch thỏa thuận, Room ngoại</t>
         </is>
@@ -17184,7 +19753,8 @@
       </c>
       <c r="G457" s="3" t="inlineStr"/>
       <c r="H457" s="2" t="inlineStr"/>
-      <c r="I457" s="3" t="inlineStr">
+      <c r="I457" s="2" t="inlineStr"/>
+      <c r="J457" s="3" t="inlineStr">
         <is>
           <t>Khối ngoại, Giao dịch thỏa thuận, Review danh mục ETF, Thanh khoản</t>
         </is>
@@ -17217,7 +19787,8 @@
       </c>
       <c r="G458" s="3" t="inlineStr"/>
       <c r="H458" s="2" t="inlineStr"/>
-      <c r="I458" s="3" t="inlineStr">
+      <c r="I458" s="2" t="inlineStr"/>
+      <c r="J458" s="3" t="inlineStr">
         <is>
           <t>Khối ngoại, Room ngoại, Hệ thống KRX, Quỹ ETF</t>
         </is>
@@ -17252,9 +19823,22 @@
           <t>Ngày VSDC chốt danh sách người sở hữu chứng khoán để xác định ai được hưởng quyền như nhận cổ tức, cổ phiếu thưởng, quyền mua cổ phiếu phát hành thêm hoặc tham dự Đại hội đồng cổ đông. Nhà đầu tư có tên trong danh sách tại ngày này mới được hưởng quyền, kể cả khi đã bán cổ phiếu từ ngày giao dịch không hưởng quyền trở đi.</t>
         </is>
       </c>
-      <c r="G459" s="3" t="inlineStr"/>
-      <c r="H459" s="2" t="inlineStr"/>
-      <c r="I459" s="3" t="inlineStr">
+      <c r="G459" s="3" t="inlineStr">
+        <is>
+          <t>The ex-dividend date is an investment term involving the timing of payment of dividends on stocks of corporations, income trusts, and other financial holdings, both publicly and privately held. It coincides with the reinvestment date for shares held subject to a dividend reinvestment plan. The ex-date or ex-dividend date or ex-div day represents the date on or after which a security is traded without a previously declared dividend or distribution.</t>
+        </is>
+      </c>
+      <c r="H459" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ex-dividend_date</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J459" s="3" t="inlineStr">
         <is>
           <t>Ngày giao dịch không hưởng quyền, Tổng công ty Lưu ký và Bù trừ Chứng khoán Việt Nam, Đại hội đồng cổ đông, Quyền mua cổ phiếu</t>
         </is>
@@ -17289,9 +19873,22 @@
           <t>Ngày mà người mua cổ phiếu sẽ không còn được hưởng các quyền đi kèm như cổ tức, cổ phiếu thưởng, quyền mua, quyền dự họp. Với chu kỳ thanh toán T+2, ngày GDKHQ đứng trước ngày đăng ký cuối cùng một ngày làm việc; muốn được hưởng quyền, nhà đầu tư phải mua chậm nhất trong phiên liền trước ngày GDKHQ. Vào ngày này, giá tham chiếu được điều chỉnh giảm nếu quyền có giá trị kinh tế.</t>
         </is>
       </c>
-      <c r="G460" s="3" t="inlineStr"/>
-      <c r="H460" s="2" t="inlineStr"/>
-      <c r="I460" s="3" t="inlineStr">
+      <c r="G460" s="3" t="inlineStr">
+        <is>
+          <t>The ex-dividend date is an investment term involving the timing of payment of dividends on stocks of corporations, income trusts, and other financial holdings, both publicly and privately held. It coincides with the reinvestment date for shares held subject to a dividend reinvestment plan. The ex-date or ex-dividend date or ex-div day represents the date on or after which a security is traded without a previously declared dividend or distribution.</t>
+        </is>
+      </c>
+      <c r="H460" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ex-dividend_date</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J460" s="3" t="inlineStr">
         <is>
           <t>Ngày đăng ký cuối cùng, Chu kỳ thanh toán T+2, Giá tham chiếu, Cổ tức bằng tiền mặt</t>
         </is>
@@ -17324,7 +19921,8 @@
       </c>
       <c r="G461" s="3" t="inlineStr"/>
       <c r="H461" s="2" t="inlineStr"/>
-      <c r="I461" s="3" t="inlineStr">
+      <c r="I461" s="2" t="inlineStr"/>
+      <c r="J461" s="3" t="inlineStr">
         <is>
           <t>Cổ đông lớn, Công bố thông tin, Cổ phiếu ESOP, Ủy ban Chứng khoán Nhà nước</t>
         </is>
@@ -17355,9 +19953,22 @@
           <t>Hai khái niệm cơ bản của phân tích kỹ thuật: ngưỡng hỗ trợ là vùng giá mà lực mua đủ mạnh để ngăn đà giảm, giá thường bật lên khi chạm tới; ngưỡng kháng cự là vùng giá mà lực bán mạnh cản đà tăng. Khi giá vượt kháng cự với khối lượng lớn, vùng kháng cự cũ thường trở thành hỗ trợ mới và ngược lại. Các mốc điểm tròn của VN-Index như 1.200 hay 1.300 điểm thường đóng vai trò hỗ trợ, kháng cự tâm lý.</t>
         </is>
       </c>
-      <c r="G462" s="3" t="inlineStr"/>
-      <c r="H462" s="2" t="inlineStr"/>
-      <c r="I462" s="3" t="inlineStr">
+      <c r="G462" s="3" t="inlineStr">
+        <is>
+          <t>In stock market technical analysis, support and resistance are certain predetermined levels of the price of a security at which it is thought that the price will tend to stop and reverse. These levels are denoted by multiple touches of price without a breakthrough of the level.</t>
+        </is>
+      </c>
+      <c r="H462" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Support_and_resistance</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J462" s="3" t="inlineStr">
         <is>
           <t>Phân tích kỹ thuật, Khối lượng khớp lệnh, Thị trường giá lên, Thị trường giá xuống</t>
         </is>
@@ -17390,7 +20001,8 @@
       </c>
       <c r="G463" s="3" t="inlineStr"/>
       <c r="H463" s="2" t="inlineStr"/>
-      <c r="I463" s="3" t="inlineStr">
+      <c r="I463" s="2" t="inlineStr"/>
+      <c r="J463" s="3" t="inlineStr">
         <is>
           <t>Nhà đầu tư tổ chức, Trái phiếu doanh nghiệp, Phát hành riêng lẻ</t>
         </is>
@@ -17421,9 +20033,22 @@
           <t>Các pháp nhân đầu tư chứng khoán như quỹ đầu tư, công ty bảo hiểm, ngân hàng, bộ phận tự doanh của công ty chứng khoán, quỹ hưu trí, doanh nghiệp. Khác với nhà đầu tư cá nhân (chiếm hơn 80% giá trị giao dịch tại Việt Nam), nhà đầu tư tổ chức có vốn lớn, đầu tư dài hạn và ra quyết định dựa trên phân tích bài bản. Gia tăng tỷ trọng nhà đầu tư tổ chức giúp thị trường ổn định và chuyên nghiệp hơn.</t>
         </is>
       </c>
-      <c r="G464" s="3" t="inlineStr"/>
-      <c r="H464" s="2" t="inlineStr"/>
-      <c r="I464" s="3" t="inlineStr">
+      <c r="G464" s="3" t="inlineStr">
+        <is>
+          <t>An institutional investor is an entity that pools money to purchase securities, real property, and other investment assets or originate loans. Institutional investors include commercial banks, central banks, credit unions, government-linked companies, insurers, pension funds, sovereign wealth funds, charities, hedge funds, real estate investment trusts, investment advisors, endowments, and mutual funds. Operating companies which invest excess capital in these types of assets may also be included in the term.</t>
+        </is>
+      </c>
+      <c r="H464" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Institutional_investor</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J464" s="3" t="inlineStr">
         <is>
           <t>Nhà đầu tư chuyên nghiệp, Công ty quản lý quỹ, Khối ngoại, Nâng hạng thị trường</t>
         </is>
@@ -17464,7 +20089,12 @@
           <t>https://vi.wikipedia.org/wiki/Ni%C3%AAm_y%E1%BA%BFt</t>
         </is>
       </c>
-      <c r="I465" s="3" t="inlineStr">
+      <c r="I465" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J465" s="3" t="inlineStr">
         <is>
           <t>Hủy niêm yết, Phát hành lần đầu ra công chúng, Sở Giao dịch Chứng khoán TP. Hồ Chí Minh, Công bố thông tin</t>
         </is>
@@ -17505,7 +20135,12 @@
           <t>https://vi.wikipedia.org/wiki/Ph%C3%A2n_t%C3%ADch_c%C6%A1_b%E1%BA%A3n</t>
         </is>
       </c>
-      <c r="I466" s="3" t="inlineStr">
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J466" s="3" t="inlineStr">
         <is>
           <t>Phân tích kỹ thuật, Đầu tư giá trị, Đầu tư tăng trưởng, Rủi ro phi hệ thống</t>
         </is>
@@ -17546,7 +20181,12 @@
           <t>https://vi.wikipedia.org/wiki/Ph%C3%A2n_t%C3%ADch_k%E1%BB%B9_thu%E1%BA%ADt</t>
         </is>
       </c>
-      <c r="I467" s="3" t="inlineStr">
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J467" s="3" t="inlineStr">
         <is>
           <t>Phân tích cơ bản, Ngưỡng hỗ trợ và kháng cự, Khối lượng khớp lệnh, Thị trường giá lên</t>
         </is>
@@ -17591,7 +20231,12 @@
           <t>https://vi.wikipedia.org/wiki/Ph%C3%A1t_h%C3%A0nh_c%C3%B4ng_khai_l%E1%BA%A7n_%C4%91%E1%BA%A7u</t>
         </is>
       </c>
-      <c r="I468" s="3" t="inlineStr">
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J468" s="3" t="inlineStr">
         <is>
           <t>Thị trường sơ cấp, Niêm yết, Ủy ban Chứng khoán Nhà nước, Phát hành thêm cổ phiếu</t>
         </is>
@@ -17622,9 +20267,22 @@
           <t>Hình thức chào bán chứng khoán cho dưới 100 nhà đầu tư (không kể nhà đầu tư chuyên nghiệp) và không dùng phương tiện thông tin đại chúng; với công ty đại chúng, đối tượng mua chỉ gồm nhà đầu tư chiến lược và nhà đầu tư chuyên nghiệp. Cổ phiếu phát hành riêng lẻ bị hạn chế chuyển nhượng 3 năm với nhà đầu tư chiến lược và 1 năm với nhà đầu tư chuyên nghiệp. Giá phát hành riêng lẻ cần được xem xét kỹ vì nếu thấp hơn thị giá sẽ gây thiệt thòi cho cổ đông hiện hữu.</t>
         </is>
       </c>
-      <c r="G469" s="3" t="inlineStr"/>
-      <c r="H469" s="2" t="inlineStr"/>
-      <c r="I469" s="3" t="inlineStr">
+      <c r="G469" s="3" t="inlineStr">
+        <is>
+          <t>Private placement or non-public offering is a funding round of securities which are sold not through a public offering, but rather through a private offering, mostly to a small number of chosen investors. Generally, these investors include friends and family, accredited investors, and institutional investors. Placement agents help find investors. PIPE (Private Investment in Public Equity) deals are one type of private placement. SEDA (Standby Equity Distribution Agreement) is also a form of private placement.</t>
+        </is>
+      </c>
+      <c r="H469" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Private_placement</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J469" s="3" t="inlineStr">
         <is>
           <t>Phát hành thêm cổ phiếu, Nhà đầu tư chuyên nghiệp, Tỷ lệ free-float, Trái phiếu doanh nghiệp</t>
         </is>
@@ -17655,9 +20313,22 @@
           <t>Việc doanh nghiệp đã có cổ phiếu lưu hành phát hành thêm cổ phiếu để tăng vốn, dưới các hình thức: chào bán cho cổ đông hiện hữu (kèm quyền mua), chào bán ra công chúng, phát hành riêng lẻ, trả cổ tức bằng cổ phiếu, cổ phiếu thưởng hoặc ESOP. Phát hành có thu tiền giúp bổ sung vốn kinh doanh nhưng làm tăng số cổ phiếu, gây pha loãng lợi ích cổ đông nếu hiệu quả sử dụng vốn không tương xứng. Phương án phát hành phải được Đại hội đồng cổ đông thông qua.</t>
         </is>
       </c>
-      <c r="G470" s="3" t="inlineStr"/>
-      <c r="H470" s="2" t="inlineStr"/>
-      <c r="I470" s="3" t="inlineStr">
+      <c r="G470" s="3" t="inlineStr">
+        <is>
+          <t>A seasoned equity offering (SEO) or capital increase is a new equity issued by an already publicly traded company. Seasoned offerings may involve shares sold by existing shareholders (non-dilutive), new shares (dilutive), or both. If the seasoned equity offering is made by an issuer that meets certain regulatory criteria, it may be a shelf offering.</t>
+        </is>
+      </c>
+      <c r="H470" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Seasoned_equity_offering</t>
+        </is>
+      </c>
+      <c r="I470" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J470" s="3" t="inlineStr">
         <is>
           <t>Quyền mua cổ phiếu, Phát hành riêng lẻ, Cổ phiếu ESOP, Thị trường sơ cấp</t>
         </is>
@@ -17690,7 +20361,8 @@
       </c>
       <c r="G471" s="3" t="inlineStr"/>
       <c r="H471" s="2" t="inlineStr"/>
-      <c r="I471" s="3" t="inlineStr">
+      <c r="I471" s="2" t="inlineStr"/>
+      <c r="J471" s="3" t="inlineStr">
         <is>
           <t>Công ty chứng khoán, Thuế thu nhập từ chuyển nhượng chứng khoán, Giao dịch ký quỹ</t>
         </is>
@@ -17723,7 +20395,8 @@
       </c>
       <c r="G472" s="3" t="inlineStr"/>
       <c r="H472" s="2" t="inlineStr"/>
-      <c r="I472" s="3" t="inlineStr">
+      <c r="I472" s="2" t="inlineStr"/>
+      <c r="J472" s="3" t="inlineStr">
         <is>
           <t>Lệnh ATO, Lệnh ATC, Khớp lệnh liên tục, Giá tham chiếu</t>
         </is>
@@ -17758,9 +20431,22 @@
           <t>Quỹ đầu tư thụ động mô phỏng biến động của một chỉ số tham chiếu (như VN30, VNDiamond, VNFinLead), có chứng chỉ quỹ niêm yết và giao dịch trên sàn như cổ phiếu. Nhà đầu tư lớn có thể hoán đổi lô cổ phiếu cơ cấu lấy lô chứng chỉ quỹ và ngược lại, giúp giá ETF bám sát giá trị tài sản ròng. Ví dụ: E1VFVN30, FUEVFVND, FUESSVFL; dòng tiền ETF nội và ngoại tác động mạnh đến cổ phiếu VN30 trong các kỳ review.</t>
         </is>
       </c>
-      <c r="G473" s="3" t="inlineStr"/>
-      <c r="H473" s="2" t="inlineStr"/>
-      <c r="I473" s="3" t="inlineStr">
+      <c r="G473" s="3" t="inlineStr">
+        <is>
+          <t>Quỹ hoán đổi danh mục (tiếng Anh: Exchange-traded fund) là một quỹ đầu tư mô phỏng biến động của chỉ số chứng khoán hoặc trái phiếu. Quỹ hoán đổi danh mục thường do các sở giao dịch chứng khoán niêm yết, tương tự như một dạng cổ phiếu. Đây được xem là một phương thức đầu tư thụ động. Bên cạnh một số ưu điểm thì quỹ này cũng tồn tại khá nhiều rủi ro.</t>
+        </is>
+      </c>
+      <c r="H473" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Qu%E1%BB%B9_ho%C3%A1n_%C4%91%E1%BB%95i_danh_m%E1%BB%A5c</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J473" s="3" t="inlineStr">
         <is>
           <t>Đầu tư thụ động, Review danh mục ETF, Chỉ số VN30, Chứng chỉ quỹ</t>
         </is>
@@ -17791,9 +20477,22 @@
           <t>Quỹ đầu tư chứng khoán cho phép nhà đầu tư mua thêm hoặc bán lại chứng chỉ quỹ cho chính công ty quản lý quỹ vào các ngày giao dịch định kỳ, theo giá trị tài sản ròng (NAV) trên mỗi đơn vị quỹ. Quy mô quỹ mở thay đổi liên tục theo dòng tiền vào ra; ngược lại, quỹ đóng chỉ phát hành một lần và nhà đầu tư phải mua bán chứng chỉ quỹ trên sàn. Quỹ mở phù hợp với nhà đầu tư cá nhân muốn ủy thác cho chuyên gia quản lý.</t>
         </is>
       </c>
-      <c r="G474" s="3" t="inlineStr"/>
-      <c r="H474" s="2" t="inlineStr"/>
-      <c r="I474" s="3" t="inlineStr">
+      <c r="G474" s="3" t="inlineStr">
+        <is>
+          <t>Quỹ đầu tư mở là một quỹ đầu tư tập thể cho phép phát hành thêm và mua lại cổ phiếu đã phát hành bất cứ lúc nào. Nhà đầu tư có thể mua cổ phiếu của những quỹ như vậy trực tiếp từ công ty quản lý quỹ, hoặc thông qua một hãng môi giới. Quỹ đầu tư mở khá phổ biến ở hầu hết các nước phát triển, tuy nhiên thuật ngữ và quy tắc hoạt động có thể hơi khác nhau. Ví dụ: ở Mỹ người ta gọi nó là mutual fund (quỹ tương hỗ), ở Anh là Unit trusts (đơn vị ủy thác đầu tư) hoặc OEIC (công ty đầu tư mở rộng), còn hầu hết các nước châu Âu gọi nó là SICAV (công ty đầu tư không cố định vốn).</t>
+        </is>
+      </c>
+      <c r="H474" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Qu%E1%BB%B9_%C4%91%E1%BA%A7u_t%C6%B0_m%E1%BB%9F</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J474" s="3" t="inlineStr">
         <is>
           <t>Chứng chỉ quỹ, Công ty quản lý quỹ, Quỹ ETF, Đa dạng hóa danh mục</t>
         </is>
@@ -17824,9 +20523,22 @@
           <t>Quyền ưu tiên cho cổ đông hiện hữu được mua cổ phiếu phát hành thêm theo tỷ lệ sở hữu và mức giá chào bán (thường thấp hơn giá thị trường). Quyền mua được phân bổ cho cổ đông có tên tại ngày đăng ký cuối cùng; trong thời hạn quy định, cổ đông có thể thực hiện quyền, chuyển nhượng quyền (chỉ một lần) hoặc bỏ qua. Nếu không thực hiện quyền, tỷ lệ sở hữu của cổ đông sẽ bị pha loãng.</t>
         </is>
       </c>
-      <c r="G475" s="3" t="inlineStr"/>
-      <c r="H475" s="2" t="inlineStr"/>
-      <c r="I475" s="3" t="inlineStr">
+      <c r="G475" s="3" t="inlineStr">
+        <is>
+          <t>A pre-emption right, right of pre-emption, or first option to buy is a contractual right to acquire certain property newly coming into existence before it can be offered to any other person or entity. It comes from the Latin verb emo, emere, emi, emptum, to buy or purchase, plus the inseparable preposition pre, before. A right to acquire existing property in preference to any other person is usually referred to as a right of first refusal.</t>
+        </is>
+      </c>
+      <c r="H475" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Pre-emption_right</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J475" s="3" t="inlineStr">
         <is>
           <t>Phát hành thêm cổ phiếu, Ngày đăng ký cuối cùng, Ngày giao dịch không hưởng quyền, Cổ phiếu phổ thông</t>
         </is>
@@ -17859,7 +20571,8 @@
       </c>
       <c r="G476" s="3" t="inlineStr"/>
       <c r="H476" s="2" t="inlineStr"/>
-      <c r="I476" s="3" t="inlineStr">
+      <c r="I476" s="2" t="inlineStr"/>
+      <c r="J476" s="3" t="inlineStr">
         <is>
           <t>Quỹ ETF, Chỉ số VN30, Chỉ số VNDiamond, Lệnh ATC, Tỷ lệ free-float</t>
         </is>
@@ -17896,7 +20609,8 @@
       </c>
       <c r="G477" s="3" t="inlineStr"/>
       <c r="H477" s="2" t="inlineStr"/>
-      <c r="I477" s="3" t="inlineStr">
+      <c r="I477" s="2" t="inlineStr"/>
+      <c r="J477" s="3" t="inlineStr">
         <is>
           <t>Khối ngoại, Chỉ số VNDiamond, Giao dịch thỏa thuận, Nâng hạng thị trường</t>
         </is>
@@ -17927,9 +20641,22 @@
           <t>Rủi ro tác động lên toàn bộ thị trường, xuất phát từ các yếu tố chung như lãi suất, lạm phát, tỷ giá, thay đổi chính sách, khủng hoảng kinh tế hay biến động địa chính trị. Rủi ro hệ thống không thể loại bỏ bằng đa dạng hóa danh mục, chỉ có thể hạn chế bằng phân bổ tài sản hoặc phòng ngừa (ví dụ bán hợp đồng tương lai chỉ số). Mức độ nhạy cảm của một cổ phiếu với rủi ro hệ thống được đo bằng hệ số beta.</t>
         </is>
       </c>
-      <c r="G478" s="3" t="inlineStr"/>
-      <c r="H478" s="2" t="inlineStr"/>
-      <c r="I478" s="3" t="inlineStr">
+      <c r="G478" s="3" t="inlineStr">
+        <is>
+          <t>In finance and economics, systematic risk (in economics often called aggregate risk or undiversifiable risk) is vulnerability to events which affect aggregate outcomes such as broad market returns, total economy-wide resource holdings, or aggregate income. In many contexts, events like earthquakes, epidemics and major weather catastrophes pose aggregate risks that affect not only the distribution but also the total amount of resources. That is why it is also known as contingent risk, unplanned risk or risk events.</t>
+        </is>
+      </c>
+      <c r="H478" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Systematic_risk</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J478" s="3" t="inlineStr">
         <is>
           <t>Rủi ro phi hệ thống, Đa dạng hóa danh mục, Hợp đồng tương lai chỉ số, Thị trường giá xuống</t>
         </is>
@@ -17962,7 +20689,8 @@
       </c>
       <c r="G479" s="3" t="inlineStr"/>
       <c r="H479" s="2" t="inlineStr"/>
-      <c r="I479" s="3" t="inlineStr">
+      <c r="I479" s="2" t="inlineStr"/>
+      <c r="J479" s="3" t="inlineStr">
         <is>
           <t>Rủi ro hệ thống, Đa dạng hóa danh mục, Phân tích cơ bản</t>
         </is>
@@ -18007,7 +20735,12 @@
           <t>https://vi.wikipedia.org/wiki/S%E1%BB%9F_Giao_d%E1%BB%8Bch_Ch%E1%BB%A9ng_kho%C3%A1n_H%C3%A0_N%E1%BB%99i</t>
         </is>
       </c>
-      <c r="I480" s="3" t="inlineStr">
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J480" s="3" t="inlineStr">
         <is>
           <t>Chỉ số HNX-Index, Thị trường UPCoM, Chứng khoán phái sinh, Trái phiếu doanh nghiệp</t>
         </is>
@@ -18052,7 +20785,12 @@
           <t>https://vi.wikipedia.org/wiki/S%E1%BB%9F_Giao_d%E1%BB%8Bch_Ch%E1%BB%A9ng_kho%C3%A1n_Th%C3%A0nh_ph%E1%BB%91_H%E1%BB%93_Ch%C3%AD_Minh</t>
         </is>
       </c>
-      <c r="I481" s="3" t="inlineStr">
+      <c r="I481" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J481" s="3" t="inlineStr">
         <is>
           <t>Chỉ số VN-Index, Chỉ số VN30, Biên độ dao động giá, Niêm yết</t>
         </is>
@@ -18089,7 +20827,8 @@
       </c>
       <c r="G482" s="3" t="inlineStr"/>
       <c r="H482" s="2" t="inlineStr"/>
-      <c r="I482" s="3" t="inlineStr">
+      <c r="I482" s="2" t="inlineStr"/>
+      <c r="J482" s="3" t="inlineStr">
         <is>
           <t>Sở Giao dịch Chứng khoán TP. Hồ Chí Minh, Sở Giao dịch Chứng khoán Hà Nội, Thị trường UPCoM, Ủy ban Chứng khoán Nhà nước</t>
         </is>
@@ -18130,7 +20869,12 @@
           <t>https://vi.wikipedia.org/wiki/T%C3%A0i_kho%E1%BA%A3n_ch%E1%BB%A9ng_kho%C3%A1n</t>
         </is>
       </c>
-      <c r="I483" s="3" t="inlineStr">
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J483" s="3" t="inlineStr">
         <is>
           <t>Công ty chứng khoán, Tổng công ty Lưu ký và Bù trừ Chứng khoán Việt Nam, Giao dịch ký quỹ, Khối ngoại</t>
         </is>
@@ -18161,9 +20905,22 @@
           <t>Khả năng mua hoặc bán một chứng khoán nhanh chóng với khối lượng lớn mà không làm giá thay đổi đáng kể. Thanh khoản thường đo bằng khối lượng và giá trị giao dịch bình quân phiên; cổ phiếu VN30 có thanh khoản cao, trong khi nhiều cổ phiếu nhỏ trên UPCoM có thể nhiều phiên không có giao dịch. Ở cấp độ thị trường, thanh khoản thị trường (tổng giá trị giao dịch mỗi phiên) phản ánh dòng tiền và mức độ sôi động.</t>
         </is>
       </c>
-      <c r="G484" s="3" t="inlineStr"/>
-      <c r="H484" s="2" t="inlineStr"/>
-      <c r="I484" s="3" t="inlineStr">
+      <c r="G484" s="3" t="inlineStr">
+        <is>
+          <t>Liquidity is a concept in economics involving the convertibility of assets and obligations. It can include: Market liquidity, the ease with which an asset can be sold Accounting liquidity, the ability to meet cash obligations when due Funding liquidity, the availability of credit to finance the purchase of financial asset Liquid capital, the amount of money that a firm holds Liquidity risk, the risk that an asset will have impaired market liquidity</t>
+        </is>
+      </c>
+      <c r="H484" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Liquidity</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J484" s="3" t="inlineStr">
         <is>
           <t>Khối lượng khớp lệnh, Cổ phiếu vốn hóa lớn, Tỷ lệ free-float, Cổ phiếu penny</t>
         </is>
@@ -18204,7 +20961,12 @@
           <t>https://vi.wikipedia.org/wiki/Th%E1%BB%8B_tr%C6%B0%E1%BB%9Dng_ch%E1%BB%A9ng_kho%C3%A1n</t>
         </is>
       </c>
-      <c r="I485" s="3" t="inlineStr">
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J485" s="3" t="inlineStr">
         <is>
           <t>Thị trường sơ cấp, Thị trường thứ cấp, Ủy ban Chứng khoán Nhà nước, Sở Giao dịch Chứng khoán Việt Nam</t>
         </is>
@@ -18235,9 +20997,22 @@
           <t>Giai đoạn giá chứng khoán tăng kéo dài, thường được nhận diện khi chỉ số tăng từ 20% trở lên so với đáy gần nhất, đi kèm tâm lý lạc quan, thanh khoản cao và dòng tiền mới gia nhập. Biểu tượng là con bò tót (bull) húc sừng lên; xu hướng tăng thể hiện qua các đỉnh và đáy sau cao hơn đỉnh, đáy trước. Ví dụ VN-Index giai đoạn 2020-2021 tăng từ khoảng 660 điểm lên trên 1.500 điểm.</t>
         </is>
       </c>
-      <c r="G486" s="3" t="inlineStr"/>
-      <c r="H486" s="2" t="inlineStr"/>
-      <c r="I486" s="3" t="inlineStr">
+      <c r="G486" s="3" t="inlineStr">
+        <is>
+          <t>Xu hướng thị trường (thuật ngữ tiếng Anh: Market trend) là xu thế của một thị trường tài chính di chuyển theo một hướng cụ thể qua thời gian. Các xu hướng này được phân loại thành trường kỳ cho các khung thời gian dài hạn, chính cho các khung thời gian trung hạn, và phụ cho các khung thời gian ngắn hạn. Các thương nhân xác định các xu hướng thị trường bằng cách dùng phân tích kỹ thuật, một khung thời gian đặc trưng các xu hướng thị trường như các xu thế giá cả có thể dự đoán được trong thị trường khi giá cả đạt tới các ngưỡng hỗ trợ và kháng cự, thay đổi theo thời gian.</t>
+        </is>
+      </c>
+      <c r="H486" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Xu_h%C6%B0%E1%BB%9Bng_th%E1%BB%8B_tr%C6%B0%E1%BB%9Dng</t>
+        </is>
+      </c>
+      <c r="I486" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J486" s="3" t="inlineStr">
         <is>
           <t>Thị trường giá xuống, Chỉ số VN-Index, Phân tích kỹ thuật, Thanh khoản</t>
         </is>
@@ -18268,9 +21043,22 @@
           <t>Giai đoạn giá chứng khoán giảm kéo dài, thường được nhận diện khi chỉ số giảm từ 20% trở lên so với đỉnh gần nhất, đi kèm tâm lý bi quan và thanh khoản suy giảm. Biểu tượng là con gấu (bear) vồ xuống; xu hướng giảm thể hiện qua các đỉnh và đáy sau thấp hơn trước. Ví dụ năm 2022, VN-Index giảm từ khoảng 1.530 điểm xuống dưới 900 điểm, kèm làn sóng call margin và bán giải chấp.</t>
         </is>
       </c>
-      <c r="G487" s="3" t="inlineStr"/>
-      <c r="H487" s="2" t="inlineStr"/>
-      <c r="I487" s="3" t="inlineStr">
+      <c r="G487" s="3" t="inlineStr">
+        <is>
+          <t>Xu hướng thị trường (thuật ngữ tiếng Anh: Market trend) là xu thế của một thị trường tài chính di chuyển theo một hướng cụ thể qua thời gian. Các xu hướng này được phân loại thành trường kỳ cho các khung thời gian dài hạn, chính cho các khung thời gian trung hạn, và phụ cho các khung thời gian ngắn hạn. Các thương nhân xác định các xu hướng thị trường bằng cách dùng phân tích kỹ thuật, một khung thời gian đặc trưng các xu hướng thị trường như các xu thế giá cả có thể dự đoán được trong thị trường khi giá cả đạt tới các ngưỡng hỗ trợ và kháng cự, thay đổi theo thời gian.</t>
+        </is>
+      </c>
+      <c r="H487" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Xu_h%C6%B0%E1%BB%9Bng_th%E1%BB%8B_tr%C6%B0%E1%BB%9Dng</t>
+        </is>
+      </c>
+      <c r="I487" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J487" s="3" t="inlineStr">
         <is>
           <t>Thị trường giá lên, Call margin, Bán giải chấp, Cổ phiếu phòng thủ</t>
         </is>
@@ -18311,7 +21099,12 @@
           <t>https://vi.wikipedia.org/wiki/Th%E1%BB%8B_tr%C6%B0%E1%BB%9Dng_ch%E1%BB%A9ng_kho%C3%A1n_s%C6%A1_c%E1%BA%A5p</t>
         </is>
       </c>
-      <c r="I488" s="3" t="inlineStr">
+      <c r="I488" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J488" s="3" t="inlineStr">
         <is>
           <t>Thị trường thứ cấp, Phát hành lần đầu ra công chúng, Phát hành thêm cổ phiếu, Phát hành riêng lẻ</t>
         </is>
@@ -18352,7 +21145,12 @@
           <t>https://vi.wikipedia.org/wiki/Th%E1%BB%8B_tr%C6%B0%E1%BB%9Dng_ch%E1%BB%A9ng_kho%C3%A1n_th%E1%BB%A9_c%E1%BA%A5p</t>
         </is>
       </c>
-      <c r="I489" s="3" t="inlineStr">
+      <c r="I489" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J489" s="3" t="inlineStr">
         <is>
           <t>Thị trường sơ cấp, Sở Giao dịch Chứng khoán TP. Hồ Chí Minh, Sở Giao dịch Chứng khoán Hà Nội, Thanh khoản</t>
         </is>
@@ -18389,7 +21187,8 @@
       </c>
       <c r="G490" s="3" t="inlineStr"/>
       <c r="H490" s="2" t="inlineStr"/>
-      <c r="I490" s="3" t="inlineStr">
+      <c r="I490" s="2" t="inlineStr"/>
+      <c r="J490" s="3" t="inlineStr">
         <is>
           <t>Sở Giao dịch Chứng khoán Hà Nội, Hủy niêm yết, Biên độ dao động giá, Giá tham chiếu</t>
         </is>
@@ -18422,7 +21221,8 @@
       </c>
       <c r="G491" s="3" t="inlineStr"/>
       <c r="H491" s="2" t="inlineStr"/>
-      <c r="I491" s="3" t="inlineStr">
+      <c r="I491" s="2" t="inlineStr"/>
+      <c r="J491" s="3" t="inlineStr">
         <is>
           <t>Phí giao dịch chứng khoán, Cổ tức bằng tiền mặt, Cổ tức bằng cổ phiếu, Công ty chứng khoán</t>
         </is>
@@ -18459,7 +21259,8 @@
       </c>
       <c r="G492" s="3" t="inlineStr"/>
       <c r="H492" s="2" t="inlineStr"/>
-      <c r="I492" s="3" t="inlineStr">
+      <c r="I492" s="2" t="inlineStr"/>
+      <c r="J492" s="3" t="inlineStr">
         <is>
           <t>Chu kỳ thanh toán T+2, Ngày đăng ký cuối cùng, Tài khoản chứng khoán, Khối ngoại</t>
         </is>
@@ -18500,7 +21301,12 @@
           <t>https://vi.wikipedia.org/wiki/Tr%C3%A1i_phi%E1%BA%BFu</t>
         </is>
       </c>
-      <c r="I493" s="3" t="inlineStr">
+      <c r="I493" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J493" s="3" t="inlineStr">
         <is>
           <t>Trái phiếu doanh nghiệp, Trái phiếu chuyển đổi, Lợi suất trái phiếu, Cổ phiếu</t>
         </is>
@@ -18535,9 +21341,22 @@
           <t>Trái phiếu do Bộ Tài chính phát hành thay mặt Chính phủ để huy động vốn cho ngân sách và đầu tư công, chủ yếu qua đấu thầu tại Sở Giao dịch Chứng khoán Hà Nội (HNX); người mua chính là ngân hàng, công ty bảo hiểm và Bảo hiểm xã hội. Lợi suất TPCP kỳ hạn 10 năm được dùng làm lãi suất phi rủi ro khi định giá cổ phiếu.</t>
         </is>
       </c>
-      <c r="G494" s="3" t="inlineStr"/>
-      <c r="H494" s="2" t="inlineStr"/>
-      <c r="I494" s="3" t="inlineStr">
+      <c r="G494" s="3" t="inlineStr">
+        <is>
+          <t>Trái phiếu chính phủ, công trái hay công khố phiếu là trái phiếu được phát hành bởi chính phủ một quốc gia. Trái phiếu chính phủ có thể được phát hành bằng đồng tiền nước đó hoặc bằng ngoại tệ, tiếng Anh gọi là sovereign bond).</t>
+        </is>
+      </c>
+      <c r="H494" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/Tr%C3%A1i_phi%E1%BA%BFu_ch%C3%ADnh_ph%E1%BB%A7</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J494" s="3" t="inlineStr">
         <is>
           <t>Trái phiếu, Lợi suất trái phiếu, Lãi suất phi rủi ro</t>
         </is>
@@ -18578,7 +21397,12 @@
           <t>https://vi.wikipedia.org/wiki/Tr%C3%A1i_phi%E1%BA%BFu_chuy%E1%BB%83n_%C4%91%E1%BB%95i</t>
         </is>
       </c>
-      <c r="I495" s="3" t="inlineStr">
+      <c r="I495" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J495" s="3" t="inlineStr">
         <is>
           <t>Trái phiếu doanh nghiệp, Cổ phiếu phổ thông, Phát hành thêm cổ phiếu, Trái phiếu</t>
         </is>
@@ -18623,7 +21447,12 @@
           <t>https://vi.wikipedia.org/wiki/Tr%C3%A1i_phi%E1%BA%BFu_doanh_nghi%E1%BB%87p</t>
         </is>
       </c>
-      <c r="I496" s="3" t="inlineStr">
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J496" s="3" t="inlineStr">
         <is>
           <t>Trái phiếu, Nhà đầu tư chuyên nghiệp, Phát hành riêng lẻ, Lợi suất trái phiếu</t>
         </is>
@@ -18656,7 +21485,8 @@
       </c>
       <c r="G497" s="3" t="inlineStr"/>
       <c r="H497" s="2" t="inlineStr"/>
-      <c r="I497" s="3" t="inlineStr">
+      <c r="I497" s="2" t="inlineStr"/>
+      <c r="J497" s="3" t="inlineStr">
         <is>
           <t>Vốn hóa thị trường, Chỉ số VN30, Cổ đông lớn, Review danh mục ETF</t>
         </is>
@@ -18687,9 +21517,22 @@
           <t>Tỷ lệ cổ phiếu có thể giao dịch tự do trên thị trường, tức tổng số cổ phiếu lưu hành trừ phần do Nhà nước, cổ đông chiến lược, cổ đông lớn, người nội bộ nắm giữ và cổ phiếu bị hạn chế chuyển nhượng. HOSE và các nhà cung cấp chỉ số dùng free float để chọn và tính tỷ trọng cổ phiếu trong VN30; free float thấp thường đi kèm thanh khoản kém.</t>
         </is>
       </c>
-      <c r="G498" s="3" t="inlineStr"/>
-      <c r="H498" s="2" t="inlineStr"/>
-      <c r="I498" s="3" t="inlineStr">
+      <c r="G498" s="3" t="inlineStr">
+        <is>
+          <t>In the context of stock markets, the public float or free float represents the portion of shares of a corporation that are in the hands of public investors as opposed to shares held by promoters, company officers, controlling interest investors, or governments. This number is sometimes seen as a better way of calculating market capitalization, because it provides a more accurate reflection (than entire market capitalization) of what public investors consider the company to be worth. In this context, the float may refer to all the shares outstanding that can be publicly traded.</t>
+        </is>
+      </c>
+      <c r="H498" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Public_float</t>
+        </is>
+      </c>
+      <c r="I498" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="J498" s="3" t="inlineStr">
         <is>
           <t>Chỉ số VN30, Vốn hóa thị trường, Cổ đông lớn, Review danh mục ETF</t>
         </is>
@@ -18720,9 +21563,22 @@
           <t>Tỷ lệ phần trăm lãi (hoặc lỗ) thu được trên số vốn đầu tư trong một khoảng thời gian; với cổ phiếu, bằng (chênh lệch giá + cổ tức nhận được) / giá mua. Lợi nhuận kỳ vọng là tỷ suất sinh lời trung bình nhà đầu tư dự tính đạt được, thường phải cao hơn lãi suất phi rủi ro để bù đắp rủi ro gánh chịu. Để so sánh các khoản đầu tư có thời gian khác nhau, người ta quy đổi về tỷ suất sinh lời bình quân năm.</t>
         </is>
       </c>
-      <c r="G499" s="3" t="inlineStr"/>
-      <c r="H499" s="2" t="inlineStr"/>
-      <c r="I499" s="3" t="inlineStr">
+      <c r="G499" s="3" t="inlineStr">
+        <is>
+          <t>Trong tài chính, lợi nhuận là lãi có được từ một khoản đầu tư. Nó bao gồm bất kỳ thay đổi nào về giá trị của khoản đầu tư và/hoặc dòng tiền mà nhà đầu tư nhận được từ khoản đầu tư, chẳng hạn như thanh toán lãi hoặc cổ tức. Nó có thể được đo bằng thuật ngữ tuyệt đối (ví dụ: đô la) hoặc theo tỷ lệ phần trăm của số tiền đầu tư. Cái sau cũng được gọi là thời gian giữ lại. Khoản lỗ thay vì lợi nhuận được mô tả là lợi nhuận âm, giả sử là số tiền đầu tư lớn hơn 0. Tỷ lệ hoàn vốn là lợi nhuận của một khoản đầu tư trong một khoảng thời gian, được biểu thị bằng tỷ lệ của khoản đầu tư ban đầu.</t>
+        </is>
+      </c>
+      <c r="H499" s="4" t="inlineStr">
+        <is>
+          <t>https://vi.wikipedia.org/wiki/T%E1%BB%B7_l%E1%BB%87_ho%C3%A0n_v%E1%BB%91n</t>
+        </is>
+      </c>
+      <c r="I499" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J499" s="3" t="inlineStr">
         <is>
           <t>Rủi ro hệ thống, Lợi suất trái phiếu, Cổ tức bằng tiền mặt, Đầu tư tăng trưởng</t>
         </is>
@@ -18767,7 +21623,12 @@
           <t>https://vi.wikipedia.org/wiki/%E1%BB%A6y_ban_Ch%E1%BB%A9ng_kho%C3%A1n_Nh%C3%A0_n%C6%B0%E1%BB%9Bc</t>
         </is>
       </c>
-      <c r="I500" s="3" t="inlineStr">
+      <c r="I500" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J500" s="3" t="inlineStr">
         <is>
           <t>Sở Giao dịch Chứng khoán Việt Nam, Công ty chứng khoán, Công ty quản lý quỹ, Công bố thông tin</t>
         </is>
@@ -18808,14 +21669,19 @@
           <t>https://vi.wikipedia.org/wiki/Gi%C3%A1_tr%E1%BB%8B_v%E1%BB%91n_h%C3%B3a_th%E1%BB%8B_tr%C6%B0%E1%BB%9Dng</t>
         </is>
       </c>
-      <c r="I501" s="3" t="inlineStr">
+      <c r="I501" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J501" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu vốn hóa lớn, Tỷ lệ free-float, Chỉ số VN-Index, Chỉ số VN30</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I501"/>
+  <autoFilter ref="A1:J501"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
@@ -18823,143 +21689,292 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H348" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H365" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H367" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H382" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H415" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H417" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H418" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H428" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H436" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H465" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H466" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H467" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H468" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H480" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H481" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H483" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H485" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H488" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H489" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H493" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H495" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H500" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H501" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H277" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H348" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H362" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H363" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H365" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H366" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H367" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H380" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H381" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H382" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H388" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H404" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H406" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H414" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H415" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H417" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H418" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H428" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H431" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H434" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H436" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H438" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H440" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H445" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H452" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H453" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H460" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H462" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H465" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H466" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H467" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H468" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H469" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H470" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H473" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H474" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H475" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H478" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H480" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H481" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H483" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H484" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H485" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H486" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H487" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H488" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H489" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H493" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H494" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H495" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H498" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H499" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H500" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H501" r:id="rId292"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18987,7 +22002,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cột 'Theo Wikipedia tiếng Việt': đoạn mở đầu bài viết tương ứng trên vi.wikipedia.org,</t>
+          <t>Cột 'Trích Wikipedia': đoạn mở đầu bài viết tương ứng trên vi.wikipedia.org (không có thì en.wikipedia.org, nguyên văn),</t>
         </is>
       </c>
     </row>
